--- a/documentation/Automated Testing CFSuite.xlsx
+++ b/documentation/Automated Testing CFSuite.xlsx
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -475,6 +475,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,14 +823,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG175"/>
+  <dimension ref="A1:AH176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="4"/>
     <col width="55" customWidth="1" min="5" max="7"/>
-    <col width="40" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="42" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -1078,7 +1083,12 @@
           <t>Notes/Comments</t>
         </is>
       </c>
-      <c r="AG3" s="44" t="inlineStr">
+      <c r="AG3" s="46" t="inlineStr">
+        <is>
+          <t>Target Automation Reference</t>
+        </is>
+      </c>
+      <c r="AH3" s="44" t="inlineStr">
         <is>
           <t>Automation Reference</t>
         </is>
@@ -1141,6 +1151,11 @@
       <c r="AD4" s="23" t="n"/>
       <c r="AE4" s="24" t="n"/>
       <c r="AF4" s="25" t="n"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-001</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="41" t="inlineStr">
@@ -1174,6 +1189,11 @@
           <t>Customer 1. Warning should be displayed if exact match FN + LN 2. Warning should come up before user creates the record with matches to avoid duplicates before they get created. Business 1. Warning should be exact match on company name field 2. Warning message come up before record is created</t>
         </is>
       </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-002</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="105" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
@@ -1207,6 +1227,11 @@
           <t>1. Known Address lookup is working for Customer, Business and Employee</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-003</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="315" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
@@ -1240,6 +1265,11 @@
           <t>1. Can select residentual and postal address from picklist</t>
         </is>
       </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-004</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="255" customHeight="1">
       <c r="A8" s="40" t="inlineStr">
@@ -1273,6 +1303,11 @@
           <t>1.Check to see alert banner on customer record</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-005</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="225" customHeight="1">
       <c r="A9" s="41" t="inlineStr">
@@ -1306,6 +1341,11 @@
           <t>1. check need a permission set to update sync with NAR on a customer record to Yes 2. Test for all customer record types</t>
         </is>
       </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-006</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="225" customHeight="1">
       <c r="A10" s="40" t="inlineStr">
@@ -1339,6 +1379,11 @@
           <t>1. check need a permission set to update alert flags customer record 2. Test for all customer record types</t>
         </is>
       </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-007</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="255" customHeight="1">
       <c r="A11" s="41" t="inlineStr">
@@ -1372,6 +1417,11 @@
           <t>1. Update Customer fields, and observe history log updated, update Customer History 2. Confirm its turned on for all customer records types 3. Confirmation from customer on the 20 selected fields to track</t>
         </is>
       </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-008</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="165" customHeight="1">
       <c r="A12" s="40" t="inlineStr">
@@ -1405,6 +1455,11 @@
           <t>1. Community member records can be merged if if user has the permission 2. Community member records cannot be merged if the user does not have the permission. Note : Only CC should merge the customer records</t>
         </is>
       </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-009</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="210" customHeight="1">
       <c r="A13" s="41" t="inlineStr">
@@ -1438,6 +1493,11 @@
           <t>1.Check emails, tasks,call logs all under activity widget</t>
         </is>
       </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-010</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="195" customHeight="1">
       <c r="A14" s="40" t="inlineStr">
@@ -1471,6 +1531,11 @@
           <t>1. Cases are visible against the customer customer page</t>
         </is>
       </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-011</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="180" customHeight="1">
       <c r="A15" s="41" t="inlineStr">
@@ -1504,6 +1569,11 @@
           <t>Chatter posts appear in the history</t>
         </is>
       </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-012</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="225" customHeight="1">
       <c r="A16" s="40" t="inlineStr">
@@ -1537,6 +1607,11 @@
           <t>1.Cross-check the listed related records on the compact layout on customer record</t>
         </is>
       </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-013</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="165" customHeight="1">
       <c r="A17" s="41" t="inlineStr">
@@ -1566,6 +1641,11 @@
           <t>1. Suppressed field can be marked as 'Yes' if the user has appropriate permissions 2. Alert banner is seen when customer is a supressed customer.</t>
         </is>
       </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-014</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="195" customHeight="1">
       <c r="A18" s="40" t="inlineStr">
@@ -1593,6 +1673,11 @@
       <c r="G18" s="40" t="inlineStr">
         <is>
           <t>1. Event log displays the user has viewed customer record and the time it was viewed.</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-015</t>
         </is>
       </c>
     </row>
@@ -1650,6 +1735,11 @@
           <t>CommunitiesSelfRegController creates Contact and User records; Password_Reset_Token record generated; confirmation page shown; cfsuite1__CFSuite_User_Setting__c record created on first login</t>
         </is>
       </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-016</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="210" customHeight="1">
       <c r="A21" s="43" t="inlineStr">
@@ -1688,6 +1778,11 @@
       <c r="G21" s="43" t="inlineStr">
         <is>
           <t>LightningLoginFormController authenticates user; session is created; community home page loads within 5 seconds</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-017</t>
         </is>
       </c>
     </row>
@@ -1729,6 +1824,11 @@
       <c r="G22" s="43" t="inlineStr">
         <is>
           <t>Login form shows 'Invalid credentials' or equivalent error; no authentication session created; login attempt counter incremented if applicable</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-018</t>
         </is>
       </c>
     </row>
@@ -1773,6 +1873,11 @@
           <t>LightningForgotPasswordController creates a Password_Reset_Token record; reset email dispatched via Message Queue; confirmation message rendered on page</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-019</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="195" customHeight="1">
       <c r="A24" s="43" t="inlineStr">
@@ -1811,6 +1916,11 @@
       <c r="G24" s="43" t="inlineStr">
         <is>
           <t>GoogleOpenIdRegistrationHandler creates/matches Contact and User; user lands on community home page; cfsuite1__CFSuite_User_Setting__c record created</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-020</t>
         </is>
       </c>
     </row>
@@ -1856,6 +1966,11 @@
           <t>Cfsuite_MyProfileController / CommunityUserUpdateContactHelperClass updates Contact record; CFSuite_User_Setting__c reflects any profile preference changes; changes visible immediately on reload</t>
         </is>
       </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-021</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="270" customHeight="1">
       <c r="A26" s="43" t="inlineStr">
@@ -1895,6 +2010,11 @@
       <c r="G26" s="43" t="inlineStr">
         <is>
           <t>NotificationPreferencesController persists choice; cfsuite1__Advise_Your_Preferred_Contact__c on future cases pre-populated with user preference</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-022</t>
         </is>
       </c>
     </row>
@@ -1940,6 +2060,11 @@
           <t>ChangePasswordController / UpdatePasswordControllerQueryHelperClass updates Salesforce community user password; old password no longer works; new password authenticates successfully</t>
         </is>
       </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-023</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="210" customHeight="1">
       <c r="A28" s="43" t="inlineStr">
@@ -1982,6 +2107,11 @@
           <t>CreateCustomerController creates Account and Contact; CustomerTriggerHandler fires; duplicate check via CustomerTriggerOperation; Contact email matches entered value</t>
         </is>
       </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-024</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="360" customHeight="1">
       <c r="A29" s="43" t="inlineStr">
@@ -2024,6 +2154,11 @@
           <t>CustomerTriggerOperationMergeTest scenario: merged Account retains all Cases; Property_Customer__c lookups updated; community user updated to master Contact; no orphaned records</t>
         </is>
       </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-025</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="165" customHeight="1">
       <c r="A30" s="43" t="inlineStr">
@@ -2066,6 +2201,11 @@
           <t>cfsuite1__Property_Customer__c record created with lookup to both Property and Account/Contact; PropertyCustomerTriggerHandler fires; Has_Agent field on Property updated if agent role set</t>
         </is>
       </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-026</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="225" customHeight="1">
       <c r="A31" s="43" t="inlineStr">
@@ -2107,6 +2247,11 @@
           <t>NavigationProcessController returns correct nav items for authenticated user; restricted pages not shown (Restricted_Page_Access=true); user display name renders in header</t>
         </is>
       </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-027</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="225" customHeight="1">
       <c r="A32" s="43" t="inlineStr">
@@ -2145,6 +2290,11 @@
       <c r="G32" s="43" t="inlineStr">
         <is>
           <t>RedirectController detects unauthorised access; user redirected to error page; no Case record partially created; cfsuite1__CFSuite_Restricted_Page_Access__c lookup checked</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-028</t>
         </is>
       </c>
     </row>
@@ -2186,6 +2336,11 @@
       <c r="G33" s="43" t="inlineStr">
         <is>
           <t>ProgressIndicatorController returns correct steps and current index; LWC renders active step highlighted; completed/pending steps visually distinct; ProgressIndicatorControllerRates used for rates cases</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-029</t>
         </is>
       </c>
     </row>
@@ -2234,6 +2389,16 @@
           <t>Create case button is on customer page layout and when creating case the customer details come through and a basic case can get created</t>
         </is>
       </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-001</t>
+        </is>
+      </c>
+      <c r="AH35" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-001 (robot/tests/requests/CFSUITE-SR-001_create_case_with_location.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="135" customHeight="1">
       <c r="A36" s="41" t="inlineStr">
@@ -2267,6 +2432,11 @@
           <t>a. can view a popup to display deflection content when a category selection is made that does not create a case.</t>
         </is>
       </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-002</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="135" customHeight="1">
       <c r="A37" s="40" t="inlineStr">
@@ -2300,6 +2470,16 @@
           <t>a. can add customer during request b. can add an existing customer c. can goto customer request and create request, and customer is auto added to the request form</t>
         </is>
       </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-003</t>
+        </is>
+      </c>
+      <c r="AH37" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-003 (robot/tests/requests/CFSUITE-SR-003_create_case_from_account.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="135" customHeight="1">
       <c r="A38" s="41" t="inlineStr">
@@ -2333,6 +2513,11 @@
           <t>a. when case assigned to user, user is notified by email they are the new owner b. if owner is manually updated, then user if notified they are now the owner c. all members of queues need to be notified when a new wo is assigned to that queue</t>
         </is>
       </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-004</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="180" customHeight="1">
       <c r="A39" s="40" t="inlineStr">
@@ -2364,6 +2549,11 @@
       <c r="G39" s="40" t="inlineStr">
         <is>
           <t>a. popular categories config is working b. tool tips can be updated c. smart search tags can be updated</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-005</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2585,11 @@
           <t>a. verify address comes up when moving pin b. verify address can be searched in the map</t>
         </is>
       </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-006</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="120" customHeight="1">
       <c r="A41" s="40" t="inlineStr">
@@ -2428,6 +2623,11 @@
           <t>Warning issued to the user that the chosen address is outside of Council</t>
         </is>
       </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-007</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="135" customHeight="1">
       <c r="A42" s="41" t="inlineStr">
@@ -2461,6 +2661,11 @@
           <t>Once a category is selected knowledge section will be visible; lists all the knowledge articles corresponding to selected category.</t>
         </is>
       </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-008</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="40" t="inlineStr">
@@ -2494,6 +2699,11 @@
           <t>Owner of the case automatically assigned a. spot check and verify against Master Request workbook (complete 4 spot checks)</t>
         </is>
       </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-009</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="41" t="inlineStr">
@@ -2527,9 +2737,14 @@
           <t>"Due Date" follows the formula that takes into account the number of days provided by the "SLA" field, and excludes weekends and public holidays. For example, if SLA = 5, and Creation Date is 29/11/2018 then the "Due Date" should show 6/12/2018</t>
         </is>
       </c>
-      <c r="AG44" s="45" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-004 (robot/tests/requests/CFSUITE-SR-004_calculate_request_due_date.robot)</t>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-010</t>
+        </is>
+      </c>
+      <c r="AH44" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-010 (robot/tests/requests/CFSUITE-SR-010_calculate_request_due_date.robot)</t>
         </is>
       </c>
     </row>
@@ -2563,6 +2778,16 @@
       <c r="G45" s="40" t="inlineStr">
         <is>
           <t>All required fields populated; adhoc case created Following fields will be auto-populated: - Customer Name - Location - Notification method = no notification - Case Origin = - Category "Parent Case" field populated with the case number of the original case</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-011</t>
+        </is>
+      </c>
+      <c r="AH45" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-011 (robot/tests/requests/CFSUITE-SR-011_create_child_case.robot)</t>
         </is>
       </c>
     </row>
@@ -2594,6 +2819,16 @@
           <t>a. verify that parent case is closed with reason incorrect category b. verify correct emails are going out to customer Or if set up to correct the case Category rather than duplicate (Controlled by Custom Setting) a. Verify that the request category is changed b. Verify that emails are going to the customer</t>
         </is>
       </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-012</t>
+        </is>
+      </c>
+      <c r="AH46" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-012 (robot/tests/requests/CFSUITE-SR-012_recategorise_case.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="40" t="inlineStr">
@@ -2623,9 +2858,14 @@
           <t>a. verify emergency status can be updated b. verify when updated on case</t>
         </is>
       </c>
-      <c r="AG47" s="45" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-005 (robot/tests/requests/CFSUITE-SR-005_flag_request_as_emergency.robot)</t>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-013</t>
+        </is>
+      </c>
+      <c r="AH47" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-013 (robot/tests/requests/CFSUITE-SR-013_flag_request_as_emergency.robot)</t>
         </is>
       </c>
     </row>
@@ -2661,9 +2901,14 @@
           <t>Verify for all case categories.</t>
         </is>
       </c>
-      <c r="AG48" s="45" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-006 (robot/tests/requests/CFSUITE-SR-006_due_date_visible_highlights.robot)</t>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-014</t>
+        </is>
+      </c>
+      <c r="AH48" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-014 (robot/tests/requests/CFSUITE-SR-014_due_date_visible_highlights.robot)</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2942,16 @@
       <c r="G49" s="40" t="inlineStr">
         <is>
           <t>Verify for all case categories.</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-015</t>
+        </is>
+      </c>
+      <c r="AH49" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-015 (robot/tests/requests/CFSUITE-SR-015_update_sla_and_due_date_when_assigned.robot)</t>
         </is>
       </c>
     </row>
@@ -2724,6 +2979,11 @@
       <c r="E50" s="41" t="n"/>
       <c r="F50" s="41" t="n"/>
       <c r="G50" s="41" t="n"/>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-016</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="72" customHeight="1">
       <c r="A51" s="40" t="inlineStr">
@@ -2755,6 +3015,11 @@
       <c r="G51" s="40" t="inlineStr">
         <is>
           <t>1. Warning message is displayed on customer when preferred notification method is email or mobile and they don’t have that information on customer record 1. Warning message is displayed on case when notification method is email or mobile and they don’t have that information on customer record</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-017</t>
         </is>
       </c>
     </row>
@@ -2782,6 +3047,11 @@
       <c r="E52" s="41" t="n"/>
       <c r="F52" s="41" t="n"/>
       <c r="G52" s="41" t="n"/>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-018</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="40" t="inlineStr">
@@ -2811,6 +3081,11 @@
       </c>
       <c r="F53" s="40" t="n"/>
       <c r="G53" s="40" t="n"/>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-019</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="41" t="inlineStr">
@@ -2836,6 +3111,11 @@
       <c r="E54" s="41" t="n"/>
       <c r="F54" s="41" t="n"/>
       <c r="G54" s="41" t="n"/>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-020</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="40" t="inlineStr">
@@ -2861,6 +3141,11 @@
       <c r="E55" s="40" t="n"/>
       <c r="F55" s="40" t="n"/>
       <c r="G55" s="40" t="n"/>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-021</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="41" t="inlineStr">
@@ -2886,6 +3171,11 @@
       <c r="E56" s="41" t="n"/>
       <c r="F56" s="41" t="n"/>
       <c r="G56" s="41" t="n"/>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-022</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="40" t="inlineStr">
@@ -2911,6 +3201,11 @@
       <c r="E57" s="40" t="n"/>
       <c r="F57" s="40" t="n"/>
       <c r="G57" s="40" t="n"/>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-023</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="41" t="inlineStr">
@@ -2936,6 +3231,11 @@
       <c r="E58" s="41" t="n"/>
       <c r="F58" s="41" t="n"/>
       <c r="G58" s="41" t="n"/>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-024</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="40" t="inlineStr">
@@ -2961,6 +3261,11 @@
       <c r="E59" s="40" t="n"/>
       <c r="F59" s="40" t="n"/>
       <c r="G59" s="40" t="n"/>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-025</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="41" t="inlineStr">
@@ -2986,6 +3291,11 @@
       <c r="E60" s="41" t="n"/>
       <c r="F60" s="41" t="n"/>
       <c r="G60" s="41" t="n"/>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-026</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="40" t="inlineStr">
@@ -3011,6 +3321,11 @@
       <c r="E61" s="40" t="n"/>
       <c r="F61" s="40" t="n"/>
       <c r="G61" s="40" t="n"/>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-027</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="41" t="inlineStr">
@@ -3036,6 +3351,11 @@
       <c r="E62" s="41" t="n"/>
       <c r="F62" s="41" t="n"/>
       <c r="G62" s="41" t="n"/>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-028</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="40" t="inlineStr">
@@ -3061,6 +3381,11 @@
       <c r="E63" s="40" t="n"/>
       <c r="F63" s="40" t="n"/>
       <c r="G63" s="40" t="n"/>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-029</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="41" t="inlineStr">
@@ -3086,6 +3411,11 @@
       <c r="E64" s="41" t="n"/>
       <c r="F64" s="41" t="n"/>
       <c r="G64" s="41" t="n"/>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-030</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="40" t="inlineStr">
@@ -3111,6 +3441,11 @@
       <c r="E65" s="40" t="n"/>
       <c r="F65" s="40" t="n"/>
       <c r="G65" s="40" t="n"/>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-031</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="41" t="inlineStr">
@@ -3136,6 +3471,11 @@
       <c r="E66" s="41" t="n"/>
       <c r="F66" s="41" t="n"/>
       <c r="G66" s="41" t="n"/>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-032</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="40" t="inlineStr">
@@ -3165,6 +3505,11 @@
       </c>
       <c r="F67" s="40" t="n"/>
       <c r="G67" s="40" t="n"/>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-033</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="41" t="inlineStr">
@@ -3194,6 +3539,16 @@
       </c>
       <c r="F68" s="41" t="n"/>
       <c r="G68" s="41" t="n"/>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-034</t>
+        </is>
+      </c>
+      <c r="AH68" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-034 (robot/tests/requests/CFSUITE-SR-034_assign_case.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="40" t="inlineStr">
@@ -3223,9 +3578,14 @@
       </c>
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="40" t="n"/>
-      <c r="AG69" s="45" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-007 (robot/tests/requests/CFSUITE-SR-007_link_interested_parties.robot)</t>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-035</t>
+        </is>
+      </c>
+      <c r="AH69" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-035 (robot/tests/requests/CFSUITE-SR-035_link_interested_parties.robot)</t>
         </is>
       </c>
     </row>
@@ -3257,6 +3617,16 @@
       </c>
       <c r="F70" s="41" t="n"/>
       <c r="G70" s="41" t="n"/>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-036</t>
+        </is>
+      </c>
+      <c r="AH70" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-036 (robot/tests/requests/CFSUITE-SR-036_provide_reason_for_due_date_change.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="96" customHeight="1">
       <c r="A71" s="40" t="inlineStr">
@@ -3290,6 +3660,11 @@
           <t>Check that email are generated as per business requirements Check that task is created on the Contact Center Agent Task Queue</t>
         </is>
       </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-037</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="84" customHeight="1">
       <c r="A72" s="41" t="inlineStr">
@@ -3323,9 +3698,14 @@
           <t>Key fields (up to 20) are tracked on listed records</t>
         </is>
       </c>
-      <c r="AG72" s="45" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-008 (robot/tests/requests/CFSUITE-SR-008_track_request_history.robot)</t>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-038</t>
+        </is>
+      </c>
+      <c r="AH72" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-038 (robot/tests/requests/CFSUITE-SR-038_track_request_history.robot)</t>
         </is>
       </c>
     </row>
@@ -3357,6 +3737,16 @@
       </c>
       <c r="F73" s="40" t="n"/>
       <c r="G73" s="40" t="n"/>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-039</t>
+        </is>
+      </c>
+      <c r="AH73" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-039 (robot/tests/requests/CFSUITE-SR-039_provide_reason_for_closing.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="41" t="inlineStr">
@@ -3386,6 +3776,16 @@
       </c>
       <c r="F74" s="41" t="n"/>
       <c r="G74" s="41" t="n"/>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-040</t>
+        </is>
+      </c>
+      <c r="AH74" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-040 (robot/tests/requests/CFSUITE-SR-040_other_close_reason_requires_comment.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="40" t="inlineStr">
@@ -3415,6 +3815,11 @@
       </c>
       <c r="F75" s="40" t="n"/>
       <c r="G75" s="40" t="n"/>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-041</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="41" t="inlineStr">
@@ -3444,6 +3849,11 @@
       </c>
       <c r="F76" s="41" t="n"/>
       <c r="G76" s="41" t="n"/>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-042</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="40" t="inlineStr">
@@ -3473,6 +3883,16 @@
       </c>
       <c r="F77" s="40" t="n"/>
       <c r="G77" s="40" t="n"/>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-043</t>
+        </is>
+      </c>
+      <c r="AH77" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-043 (robot/tests/requests/CFSUITE-SR-043_flag_request_with_alert_warning.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="41" t="inlineStr">
@@ -3502,6 +3922,11 @@
       </c>
       <c r="F78" s="41" t="n"/>
       <c r="G78" s="41" t="n"/>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-044</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="40" t="inlineStr">
@@ -3531,6 +3956,16 @@
       </c>
       <c r="F79" s="40" t="n"/>
       <c r="G79" s="40" t="n"/>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-045</t>
+        </is>
+      </c>
+      <c r="AH79" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-045 (robot/tests/requests/CFSUITE-SR-045_provide_comment_when_closing.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="41" t="inlineStr">
@@ -3556,6 +3991,16 @@
       <c r="E80" s="41" t="n"/>
       <c r="F80" s="41" t="n"/>
       <c r="G80" s="41" t="n"/>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-046</t>
+        </is>
+      </c>
+      <c r="AH80" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-046 (robot/tests/requests/CFSUITE-SR-046_create_tasks_on_case.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="40" t="inlineStr">
@@ -3587,6 +4032,16 @@
       <c r="G81" s="40" t="inlineStr">
         <is>
           <t>1. Ability to include a custom on hold reason and custom close reason. 2. Ability to view this custom text in the on hold and close email or sms</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-047</t>
+        </is>
+      </c>
+      <c r="AH81" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-047 (robot/tests/requests/CFSUITE-SR-047_custom_on_hold_and_close_reasons.robot)</t>
         </is>
       </c>
     </row>
@@ -3614,6 +4069,11 @@
       <c r="E82" s="41" t="n"/>
       <c r="F82" s="41" t="n"/>
       <c r="G82" s="41" t="n"/>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-048</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="60" customHeight="1">
       <c r="A83" s="40" t="inlineStr">
@@ -3639,6 +4099,11 @@
       <c r="E83" s="40" t="n"/>
       <c r="F83" s="40" t="n"/>
       <c r="G83" s="40" t="n"/>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-049</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="41" t="inlineStr">
@@ -3664,6 +4129,16 @@
       </c>
       <c r="F84" s="41" t="n"/>
       <c r="G84" s="41" t="n"/>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-050</t>
+        </is>
+      </c>
+      <c r="AH84" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-050 (robot/tests/requests/CFSUITE-SR-050_path_and_guidance_for_success.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="40" t="inlineStr">
@@ -3689,6 +4164,11 @@
       <c r="E85" s="40" t="n"/>
       <c r="F85" s="40" t="n"/>
       <c r="G85" s="40" t="n"/>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-051</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="41" t="inlineStr">
@@ -3714,6 +4194,11 @@
       <c r="E86" s="41" t="n"/>
       <c r="F86" s="41" t="n"/>
       <c r="G86" s="41" t="n"/>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-052</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="60" customHeight="1">
       <c r="A87" s="40" t="inlineStr">
@@ -3739,6 +4224,11 @@
       <c r="E87" s="40" t="n"/>
       <c r="F87" s="40" t="n"/>
       <c r="G87" s="40" t="n"/>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-053</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="41" t="inlineStr">
@@ -3764,6 +4254,11 @@
       <c r="E88" s="41" t="n"/>
       <c r="F88" s="41" t="n"/>
       <c r="G88" s="41" t="n"/>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-054</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="40" t="inlineStr">
@@ -3789,6 +4284,11 @@
       <c r="E89" s="40" t="n"/>
       <c r="F89" s="40" t="n"/>
       <c r="G89" s="40" t="n"/>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-055</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="41" t="inlineStr">
@@ -3814,6 +4314,11 @@
       <c r="E90" s="41" t="n"/>
       <c r="F90" s="41" t="n"/>
       <c r="G90" s="41" t="n"/>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-056</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="40" t="inlineStr">
@@ -3839,6 +4344,11 @@
       <c r="E91" s="40" t="n"/>
       <c r="F91" s="40" t="n"/>
       <c r="G91" s="40" t="n"/>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-057</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="60" customHeight="1">
       <c r="A92" s="41" t="inlineStr">
@@ -3864,6 +4374,11 @@
       <c r="E92" s="41" t="n"/>
       <c r="F92" s="41" t="n"/>
       <c r="G92" s="41" t="n"/>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-058</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="40" t="inlineStr">
@@ -3885,6 +4400,11 @@
       <c r="E93" s="40" t="n"/>
       <c r="F93" s="40" t="n"/>
       <c r="G93" s="40" t="n"/>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-059</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="41" t="inlineStr">
@@ -3910,6 +4430,11 @@
       <c r="E94" s="41" t="n"/>
       <c r="F94" s="41" t="n"/>
       <c r="G94" s="41" t="n"/>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-060</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="40" t="inlineStr">
@@ -3935,6 +4460,11 @@
       <c r="E95" s="40" t="n"/>
       <c r="F95" s="40" t="n"/>
       <c r="G95" s="40" t="n"/>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-061</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="41" t="inlineStr">
@@ -3968,6 +4498,11 @@
           <t>1. Cases configured to be restricted (e.g. public health requests) are visiblity only to selected groups provided access to these records.</t>
         </is>
       </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-062</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="40" t="inlineStr">
@@ -3999,6 +4534,11 @@
       <c r="G97" s="40" t="inlineStr">
         <is>
           <t>1. Log available to view users who have viewed restricted category records</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-063</t>
         </is>
       </c>
     </row>
@@ -4026,6 +4566,11 @@
       <c r="E98" s="41" t="n"/>
       <c r="F98" s="41" t="n"/>
       <c r="G98" s="41" t="n"/>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-064</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="40" t="inlineStr">
@@ -4055,6 +4600,11 @@
       </c>
       <c r="F99" s="40" t="n"/>
       <c r="G99" s="40" t="n"/>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-065</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="41" t="inlineStr">
@@ -4080,6 +4630,11 @@
       <c r="E100" s="41" t="n"/>
       <c r="F100" s="41" t="n"/>
       <c r="G100" s="41" t="n"/>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-066</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="40" t="inlineStr">
@@ -4105,6 +4660,16 @@
       <c r="E101" s="40" t="n"/>
       <c r="F101" s="40" t="n"/>
       <c r="G101" s="40" t="n"/>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-067</t>
+        </is>
+      </c>
+      <c r="AH101" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-067 (robot/tests/requests/CFSUITE-SR-067_enforce_comment_closing_complaint.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="41" t="inlineStr">
@@ -4130,6 +4695,11 @@
       <c r="E102" s="41" t="n"/>
       <c r="F102" s="41" t="n"/>
       <c r="G102" s="41" t="n"/>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-068</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="40" t="inlineStr">
@@ -4155,6 +4725,11 @@
       <c r="E103" s="40" t="n"/>
       <c r="F103" s="40" t="n"/>
       <c r="G103" s="40" t="n"/>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-069</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="41" t="inlineStr">
@@ -4180,6 +4755,11 @@
       <c r="E104" s="41" t="n"/>
       <c r="F104" s="41" t="n"/>
       <c r="G104" s="41" t="n"/>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-070</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="40" t="inlineStr">
@@ -4205,6 +4785,11 @@
       <c r="E105" s="40" t="n"/>
       <c r="F105" s="40" t="n"/>
       <c r="G105" s="40" t="n"/>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-071</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="41" t="inlineStr">
@@ -4230,6 +4815,11 @@
       <c r="E106" s="41" t="n"/>
       <c r="F106" s="41" t="n"/>
       <c r="G106" s="41" t="n"/>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-072</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="40" t="inlineStr">
@@ -4255,6 +4845,11 @@
       <c r="E107" s="40" t="n"/>
       <c r="F107" s="40" t="n"/>
       <c r="G107" s="40" t="n"/>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-073</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="41" t="inlineStr">
@@ -4280,6 +4875,11 @@
       <c r="E108" s="41" t="n"/>
       <c r="F108" s="41" t="n"/>
       <c r="G108" s="41" t="n"/>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-074</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="60" customHeight="1">
       <c r="A109" s="40" t="inlineStr">
@@ -4309,6 +4909,11 @@
       </c>
       <c r="F109" s="40" t="n"/>
       <c r="G109" s="40" t="n"/>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-075</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="41" t="inlineStr">
@@ -4338,6 +4943,11 @@
       </c>
       <c r="F110" s="41" t="n"/>
       <c r="G110" s="41" t="n"/>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-076</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="40" t="inlineStr">
@@ -4367,6 +4977,11 @@
       </c>
       <c r="F111" s="40" t="n"/>
       <c r="G111" s="40" t="n"/>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-077</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="48" customHeight="1">
       <c r="A112" s="41" t="inlineStr">
@@ -4396,6 +5011,11 @@
       </c>
       <c r="F112" s="41" t="n"/>
       <c r="G112" s="41" t="n"/>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-078</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="60" customHeight="1">
       <c r="A113" s="40" t="inlineStr">
@@ -4425,6 +5045,11 @@
       </c>
       <c r="F113" s="40" t="n"/>
       <c r="G113" s="40" t="n"/>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-079</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="72" customHeight="1">
       <c r="A114" s="41" t="inlineStr">
@@ -4458,6 +5083,11 @@
           <t>a. Address displayed in the search bar that is located above the map; displayed info includes street number, street name, suburb, state and postcode</t>
         </is>
       </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-080</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="48" customHeight="1">
       <c r="A115" s="40" t="inlineStr">
@@ -4489,6 +5119,16 @@
       <c r="G115" s="40" t="inlineStr">
         <is>
           <t>Green "Follow" button vanished and replaced with the following text: "You are now following: [case number]"</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-081</t>
+        </is>
+      </c>
+      <c r="AH115" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-081 (robot/tests/requests/CFSUITE-SR-081_community_follow_case.robot)</t>
         </is>
       </c>
     </row>
@@ -4520,6 +5160,11 @@
           <t>Warning message provided along with the number of potential duplicated</t>
         </is>
       </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-082</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="48" customHeight="1">
       <c r="A117" s="40" t="inlineStr">
@@ -4549,6 +5194,11 @@
       </c>
       <c r="F117" s="40" t="n"/>
       <c r="G117" s="40" t="n"/>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-083</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="48" customHeight="1">
       <c r="A118" s="41" t="inlineStr">
@@ -4578,6 +5228,11 @@
       </c>
       <c r="F118" s="41" t="n"/>
       <c r="G118" s="41" t="n"/>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-084</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="40" t="inlineStr">
@@ -4607,6 +5262,11 @@
           <t>When Sync with NAR is "yes " you can't Edit name and Address</t>
         </is>
       </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-085</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="41" t="inlineStr">
@@ -4640,6 +5300,16 @@
           <t>See acceptance criteria in source EPT</t>
         </is>
       </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-086</t>
+        </is>
+      </c>
+      <c r="AH120" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-086 (robot/tests/requests/CFSUITE-SR-086_customer_portal_login.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="40" t="inlineStr">
@@ -4665,6 +5335,11 @@
       </c>
       <c r="F121" s="40" t="n"/>
       <c r="G121" s="40" t="n"/>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-087</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="60" customHeight="1">
       <c r="A122" s="41" t="inlineStr">
@@ -4694,42 +5369,84 @@
       </c>
       <c r="F122" s="41" t="n"/>
       <c r="G122" s="41" t="n"/>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-088</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="42" t="inlineStr">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Additional - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Clone Case</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ability to clone an existing case as a starting point for a new one. Cloned case carries category and reason fields.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cloned case opens with the parent's fields pre-filled and can be saved as a new case.</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-089</t>
+        </is>
+      </c>
+      <c r="AH123" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-089 (robot/tests/requests/CFSUITE-SR-089_clone_case.robot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="84" customHeight="1">
+      <c r="A124" s="42" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B123" s="42" t="n"/>
-      <c r="C123" s="42" t="n"/>
-      <c r="D123" s="42" t="n"/>
-      <c r="E123" s="42" t="n"/>
-      <c r="F123" s="42" t="n"/>
-      <c r="G123" s="42" t="n"/>
-    </row>
-    <row r="124" ht="84" customHeight="1">
-      <c r="A124" s="43" t="inlineStr">
+      <c r="B124" s="42" t="n"/>
+      <c r="C124" s="42" t="n"/>
+      <c r="D124" s="42" t="n"/>
+      <c r="E124" s="42" t="n"/>
+      <c r="F124" s="42" t="n"/>
+      <c r="G124" s="42" t="n"/>
+    </row>
+    <row r="125" ht="72" customHeight="1">
+      <c r="A125" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B124" s="43" t="inlineStr">
+      <c r="B125" s="43" t="inlineStr">
         <is>
           <t>PROP-006</t>
         </is>
       </c>
-      <c r="C124" s="43" t="inlineStr">
+      <c r="C125" s="43" t="inlineStr">
         <is>
           <t>Submit New Service Request - Map Form Type</t>
         </is>
       </c>
-      <c r="D124" s="43" t="inlineStr">
+      <c r="D125" s="43" t="inlineStr">
         <is>
           <t>Case is created with correct category, location pin, and linked to the logged-in contact</t>
         </is>
       </c>
-      <c r="E124" s="43" t="inlineStr">
+      <c r="E125" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request' or equivalent
@@ -4740,39 +5457,44 @@
 7. Verify confirmation/receipt page shown with case number</t>
         </is>
       </c>
-      <c r="F124" s="43" t="inlineStr">
+      <c r="F125" s="43" t="inlineStr">
         <is>
           <t>Category: Road Repairs and Maintenance - Pothole, Location: pin on valid street</t>
         </is>
       </c>
-      <c r="G124" s="43" t="inlineStr">
+      <c r="G125" s="43" t="inlineStr">
         <is>
           <t>Case record created with correct RecordType, cfsuite1__CFSuite_Request_Flow__c lookup populated, geolocation captured; CommunityUserInsertCaseHelperClass executes without error; case number displayed to user</t>
         </is>
       </c>
-    </row>
-    <row r="125" ht="72" customHeight="1">
-      <c r="A125" s="43" t="inlineStr">
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-090</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="84" customHeight="1">
+      <c r="A126" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B125" s="43" t="inlineStr">
+      <c r="B126" s="43" t="inlineStr">
         <is>
           <t>PROP-007</t>
         </is>
       </c>
-      <c r="C125" s="43" t="inlineStr">
+      <c r="C126" s="43" t="inlineStr">
         <is>
           <t>Submit New Service Request - Salesforce Flow Form Type</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D126" s="43" t="inlineStr">
         <is>
           <t>Case is created via the configured Salesforce Flow, all flow-collected fields mapped to Case</t>
         </is>
       </c>
-      <c r="E125" s="43" t="inlineStr">
+      <c r="E126" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category with Form Type = Flow
@@ -4781,39 +5503,44 @@
 5. Verify case created with correct category and flow-mapped field values</t>
         </is>
       </c>
-      <c r="F125" s="43" t="inlineStr">
+      <c r="F126" s="43" t="inlineStr">
         <is>
           <t>Category: Animals - Dog - Barking (or any Flow-type category), flow fields as required</t>
         </is>
       </c>
-      <c r="G125" s="43" t="inlineStr">
+      <c r="G126" s="43" t="inlineStr">
         <is>
           <t>RequestSubmissionFlow Apex class executes; Case record created; cfsuite1__Animal_Description__c or appropriate description field populated; confirmation number shown</t>
         </is>
       </c>
-    </row>
-    <row r="126" ht="84" customHeight="1">
-      <c r="A126" s="43" t="inlineStr">
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-091</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B126" s="43" t="inlineStr">
+      <c r="B127" s="43" t="inlineStr">
         <is>
           <t>PROP-008</t>
         </is>
       </c>
-      <c r="C126" s="43" t="inlineStr">
+      <c r="C127" s="43" t="inlineStr">
         <is>
           <t>Submit Service Request - Duplicate Detection</t>
         </is>
       </c>
-      <c r="D126" s="43" t="inlineStr">
+      <c r="D127" s="43" t="inlineStr">
         <is>
           <t>When a duplicate open request exists for the same location and category, a warning or duplicate flag is set</t>
         </is>
       </c>
-      <c r="E126" s="43" t="inlineStr">
+      <c r="E127" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Submit a request for 'Road Repairs - Pothole' at a specific address
@@ -4822,39 +5549,44 @@
 5. Verify the second case is flagged as a duplicate or a warning presented</t>
         </is>
       </c>
-      <c r="F126" s="43" t="inlineStr">
+      <c r="F127" s="43" t="inlineStr">
         <is>
           <t>Same category and map pin location as an existing open case</t>
         </is>
       </c>
-      <c r="G126" s="43" t="inlineStr">
+      <c r="G127" s="43" t="inlineStr">
         <is>
           <t>cfsuite1__Duplicate__c picklist on Case set to 'Yes' or 'Potential'; GuestUserRetrieveDupCaseHelperClass fires; user sees duplicate warning in UI</t>
         </is>
       </c>
-    </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="43" t="inlineStr">
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-092</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="72" customHeight="1">
+      <c r="A128" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B127" s="43" t="inlineStr">
+      <c r="B128" s="43" t="inlineStr">
         <is>
           <t>PROP-009</t>
         </is>
       </c>
-      <c r="C127" s="43" t="inlineStr">
+      <c r="C128" s="43" t="inlineStr">
         <is>
           <t>Guest User Service Request Submission</t>
         </is>
       </c>
-      <c r="D127" s="43" t="inlineStr">
+      <c r="D128" s="43" t="inlineStr">
         <is>
           <t>Unauthenticated (guest) user can submit a service request; contact created or matched</t>
         </is>
       </c>
-      <c r="E127" s="43" t="inlineStr">
+      <c r="E128" s="43" t="inlineStr">
         <is>
           <t>1. Browse to community portal without logging in
 2. Select a category that allows guest submission
@@ -4863,39 +5595,44 @@
 5. Verify case is created and confirmation shown</t>
         </is>
       </c>
-      <c r="F127" s="43" t="inlineStr">
+      <c r="F128" s="43" t="inlineStr">
         <is>
           <t>guestFirstName=Guest, guestLastName=User, email=guesttest+001@test.com, address=123 Main St</t>
         </is>
       </c>
-      <c r="G127" s="43" t="inlineStr">
+      <c r="G128" s="43" t="inlineStr">
         <is>
           <t>GuestUserHelperClass and GuestUserInsertContactHelperClass execute; Case created without a linked community User; ContactId populated from matched or new Contact</t>
         </is>
       </c>
-    </row>
-    <row r="128" ht="72" customHeight="1">
-      <c r="A128" s="43" t="inlineStr">
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-093</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B128" s="43" t="inlineStr">
+      <c r="B129" s="43" t="inlineStr">
         <is>
           <t>PROP-010</t>
         </is>
       </c>
-      <c r="C128" s="43" t="inlineStr">
+      <c r="C129" s="43" t="inlineStr">
         <is>
           <t>File Attachment Upload on Request Submission</t>
         </is>
       </c>
-      <c r="D128" s="43" t="inlineStr">
+      <c r="D129" s="43" t="inlineStr">
         <is>
           <t>Photo/document attached to submitted case is stored and visible on case detail</t>
         </is>
       </c>
-      <c r="E128" s="43" t="inlineStr">
+      <c r="E129" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Start a new service request
@@ -4905,39 +5642,44 @@
 6. Verify the attachment is listed</t>
         </is>
       </c>
-      <c r="F128" s="43" t="inlineStr">
+      <c r="F129" s="43" t="inlineStr">
         <is>
           <t>File: test-photo.jpg (under 5MB), Category: Parks and Reserves - Vandalism</t>
         </is>
       </c>
-      <c r="G128" s="43" t="inlineStr">
+      <c r="G129" s="43" t="inlineStr">
         <is>
           <t>ContentVersion record created and linked to Case via ContentDocumentLink; CommunityUserCaseAttachmentsHelperClass executes without error; file visible in community case detail</t>
         </is>
       </c>
-    </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="43" t="inlineStr">
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-094</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="72" customHeight="1">
+      <c r="A130" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B129" s="43" t="inlineStr">
+      <c r="B130" s="43" t="inlineStr">
         <is>
           <t>PROP-011</t>
         </is>
       </c>
-      <c r="C129" s="43" t="inlineStr">
+      <c r="C130" s="43" t="inlineStr">
         <is>
           <t>View My Submitted Requests List</t>
         </is>
       </c>
-      <c r="D129" s="43" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>Logged-in user sees a list of all their previously submitted requests with status and date</t>
         </is>
       </c>
-      <c r="E129" s="43" t="inlineStr">
+      <c r="E130" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Requests' section
@@ -4945,39 +5687,44 @@
 4. Verify each row shows case number, subject, status, and creation date</t>
         </is>
       </c>
-      <c r="F129" s="43" t="inlineStr">
+      <c r="F130" s="43" t="inlineStr">
         <is>
           <t>User must have at least 2 existing case submissions</t>
         </is>
       </c>
-      <c r="G129" s="43" t="inlineStr">
+      <c r="G130" s="43" t="inlineStr">
         <is>
           <t>MyRequestRecordListPageController returns cases for the contact; list renders with case number, subject, status columns; pagination present if more than 10 records</t>
         </is>
       </c>
-    </row>
-    <row r="130" ht="72" customHeight="1">
-      <c r="A130" s="43" t="inlineStr">
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-095</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="84" customHeight="1">
+      <c r="A131" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B130" s="43" t="inlineStr">
+      <c r="B131" s="43" t="inlineStr">
         <is>
           <t>PROP-012</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
+      <c r="C131" s="43" t="inlineStr">
         <is>
           <t>View Case Detail from My Requests</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D131" s="43" t="inlineStr">
         <is>
           <t>User can click a case and see full detail including description, location, status, and any updates</t>
         </is>
       </c>
-      <c r="E130" s="43" t="inlineStr">
+      <c r="E131" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Requests'
@@ -4986,39 +5733,44 @@
 5. Verify any case notes/comments visible to community are shown</t>
         </is>
       </c>
-      <c r="F130" s="43" t="inlineStr">
+      <c r="F131" s="43" t="inlineStr">
         <is>
           <t>Existing case with at least one community-visible note</t>
         </is>
       </c>
-      <c r="G130" s="43" t="inlineStr">
+      <c r="G131" s="43" t="inlineStr">
         <is>
           <t>CommunityUserCaseDetailHelperClass returns full case data; ProgressIndicatorController shows current case status stage; attachments section present</t>
         </is>
       </c>
-    </row>
-    <row r="131" ht="84" customHeight="1">
-      <c r="A131" s="43" t="inlineStr">
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-096</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B131" s="43" t="inlineStr">
+      <c r="B132" s="43" t="inlineStr">
         <is>
           <t>PROP-013</t>
         </is>
       </c>
-      <c r="C131" s="43" t="inlineStr">
+      <c r="C132" s="43" t="inlineStr">
         <is>
           <t>Follow / Unfollow a Public Request on Map</t>
         </is>
       </c>
-      <c r="D131" s="43" t="inlineStr">
+      <c r="D132" s="43" t="inlineStr">
         <is>
           <t>User can follow another user's public request and have it appear in their followed requests list</t>
         </is>
       </c>
-      <c r="E131" s="43" t="inlineStr">
+      <c r="E132" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to the community map
@@ -5029,39 +5781,44 @@
 7. Click 'Unfollow' and verify it is removed</t>
         </is>
       </c>
-      <c r="F131" s="43" t="inlineStr">
+      <c r="F132" s="43" t="inlineStr">
         <is>
           <t>Existing public case created by a different contact</t>
         </is>
       </c>
-      <c r="G131" s="43" t="inlineStr">
+      <c r="G132" s="43" t="inlineStr">
         <is>
           <t>CommunityUserFollowedCaseHelperClass creates/deletes EntitySubscription or Interested_Parties record; case appears/disappears from followed list; MyFollowedRequestController returns correct list</t>
         </is>
       </c>
-    </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="43" t="inlineStr">
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-097</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B132" s="43" t="inlineStr">
+      <c r="B133" s="43" t="inlineStr">
         <is>
           <t>PROP-014</t>
         </is>
       </c>
-      <c r="C132" s="43" t="inlineStr">
+      <c r="C133" s="43" t="inlineStr">
         <is>
           <t>Community Map Loads with Active Request Pins</t>
         </is>
       </c>
-      <c r="D132" s="43" t="inlineStr">
+      <c r="D133" s="43" t="inlineStr">
         <is>
           <t>Map component renders with pins for all public open cases; pins show correct category icon</t>
         </is>
       </c>
-      <c r="E132" s="43" t="inlineStr">
+      <c r="E133" s="43" t="inlineStr">
         <is>
           <t>1. Log in (or browse as guest) to community portal
 2. Navigate to the community map page
@@ -5070,39 +5827,44 @@
 5. Click a pin and verify popup shows case summary</t>
         </is>
       </c>
-      <c r="F132" s="43" t="inlineStr">
+      <c r="F133" s="43" t="inlineStr">
         <is>
           <t>Org must have at least 5 public open cases with geolocation</t>
         </is>
       </c>
-      <c r="G132" s="43" t="inlineStr">
+      <c r="G133" s="43" t="inlineStr">
         <is>
           <t>AOMapCaseQueryHelperClass returns cases with coordinates; cf_MapContentController serves map data; pins rendered with cfsuite1__Pin_Image__c icon; no JS console errors</t>
         </is>
       </c>
-    </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="43" t="inlineStr">
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-098</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="48" customHeight="1">
+      <c r="A134" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B133" s="43" t="inlineStr">
+      <c r="B134" s="43" t="inlineStr">
         <is>
           <t>PROP-015</t>
         </is>
       </c>
-      <c r="C133" s="43" t="inlineStr">
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>Category Filter on Community Map</t>
         </is>
       </c>
-      <c r="D133" s="43" t="inlineStr">
+      <c r="D134" s="43" t="inlineStr">
         <is>
           <t>Selecting a category filter updates the map to show only pins matching that category</t>
         </is>
       </c>
-      <c r="E133" s="43" t="inlineStr">
+      <c r="E134" s="43" t="inlineStr">
         <is>
           <t>1. Navigate to community map
 2. Note total number of pins displayed
@@ -5111,39 +5873,44 @@
 5. Clear the filter and verify all pins return</t>
         </is>
       </c>
-      <c r="F133" s="43" t="inlineStr">
+      <c r="F134" s="43" t="inlineStr">
         <is>
           <t>Org has cases in multiple categories with geolocation set</t>
         </is>
       </c>
-      <c r="G133" s="43" t="inlineStr">
+      <c r="G134" s="43" t="inlineStr">
         <is>
           <t>Map re-queries with category filter; pin count changes to match filtered set; clearing filter restores full pin set</t>
         </is>
       </c>
-    </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="43" t="inlineStr">
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-099</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="96" customHeight="1">
+      <c r="A135" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B134" s="43" t="inlineStr">
+      <c r="B135" s="43" t="inlineStr">
         <is>
           <t>PROP-016</t>
         </is>
       </c>
-      <c r="C134" s="43" t="inlineStr">
+      <c r="C135" s="43" t="inlineStr">
         <is>
           <t>Address Search on Community Map</t>
         </is>
       </c>
-      <c r="D134" s="43" t="inlineStr">
+      <c r="D135" s="43" t="inlineStr">
         <is>
           <t>Searching for an address pans the map to that location</t>
         </is>
       </c>
-      <c r="E134" s="43" t="inlineStr">
+      <c r="E135" s="43" t="inlineStr">
         <is>
           <t>1. Navigate to community map
 2. Enter a valid suburb or street address in the search bar
@@ -5151,39 +5918,44 @@
 4. Verify map centres on the searched address</t>
         </is>
       </c>
-      <c r="F134" s="43" t="inlineStr">
+      <c r="F135" s="43" t="inlineStr">
         <is>
           <t>searchAddress=1 Main Street [configured council suburb]</t>
         </is>
       </c>
-      <c r="G134" s="43" t="inlineStr">
+      <c r="G135" s="43" t="inlineStr">
         <is>
           <t>Address search component calls geocoding (ArcGIS or Google Maps API); map viewport pans and zooms to matched location; nearby pins visible</t>
         </is>
       </c>
-    </row>
-    <row r="135" ht="96" customHeight="1">
-      <c r="A135" s="43" t="inlineStr">
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="72" customHeight="1">
+      <c r="A136" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B135" s="43" t="inlineStr">
+      <c r="B136" s="43" t="inlineStr">
         <is>
           <t>PROP-027</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
+      <c r="C136" s="43" t="inlineStr">
         <is>
           <t>Create New Case (Internal Staff)</t>
         </is>
       </c>
-      <c r="D135" s="43" t="inlineStr">
+      <c r="D136" s="43" t="inlineStr">
         <is>
           <t>Internal staff user creates a new case record with all required fields; case number auto-generated</t>
         </is>
       </c>
-      <c r="E135" s="43" t="inlineStr">
+      <c r="E136" s="43" t="inlineStr">
         <is>
           <t>1. Log in as internal staff user
 2. Navigate to Cases and click 'New'
@@ -5194,39 +5966,44 @@
 7. Verify case is created with auto-generated case number</t>
         </is>
       </c>
-      <c r="F135" s="43" t="inlineStr">
+      <c r="F136" s="43" t="inlineStr">
         <is>
           <t>Subject=Test pothole report, Category=Road Repairs and Maintenance - Pothole, Contact=existing test contact</t>
         </is>
       </c>
-      <c r="G135" s="43" t="inlineStr">
+      <c r="G136" s="43" t="inlineStr">
         <is>
           <t>Case record created; CaseTriggerHandler fires; Work Order creation triggered if Request Flow mapping exists; case number formatted correctly (e.g. 00001234)</t>
         </is>
       </c>
-    </row>
-    <row r="136" ht="72" customHeight="1">
-      <c r="A136" s="43" t="inlineStr">
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-101</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="96" customHeight="1">
+      <c r="A137" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B136" s="43" t="inlineStr">
+      <c r="B137" s="43" t="inlineStr">
         <is>
           <t>PROP-028</t>
         </is>
       </c>
-      <c r="C136" s="43" t="inlineStr">
+      <c r="C137" s="43" t="inlineStr">
         <is>
           <t>Case Auto-Assignment via Request Flow</t>
         </is>
       </c>
-      <c r="D136" s="43" t="inlineStr">
+      <c r="D137" s="43" t="inlineStr">
         <is>
           <t>On case save, the case is automatically assigned to the correct queue/user based on the Request Flow Case Assignment configuration</t>
         </is>
       </c>
-      <c r="E136" s="43" t="inlineStr">
+      <c r="E137" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a category that has a Case Assignment Request Flow record
 2. Save the case
@@ -5234,39 +6011,44 @@
 4. Verify Department and Team fields are populated per the Work Order Mapping</t>
         </is>
       </c>
-      <c r="F136" s="43" t="inlineStr">
+      <c r="F137" s="43" t="inlineStr">
         <is>
           <t>Category with active Case Assignment Request Flow record configured</t>
         </is>
       </c>
-      <c r="G136" s="43" t="inlineStr">
+      <c r="G137" s="43" t="inlineStr">
         <is>
           <t>CaseTriggerOperation fires assignment logic; Case OwnerId matches configured queue/user; cfsuite1__Department__c and cfsuite1__Team__c set per mapping</t>
         </is>
       </c>
-    </row>
-    <row r="137" ht="96" customHeight="1">
-      <c r="A137" s="43" t="inlineStr">
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="84" customHeight="1">
+      <c r="A138" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B137" s="43" t="inlineStr">
+      <c r="B138" s="43" t="inlineStr">
         <is>
           <t>PROP-029</t>
         </is>
       </c>
-      <c r="C137" s="43" t="inlineStr">
+      <c r="C138" s="43" t="inlineStr">
         <is>
           <t>Case Status Transition - Close Case</t>
         </is>
       </c>
-      <c r="D137" s="43" t="inlineStr">
+      <c r="D138" s="43" t="inlineStr">
         <is>
           <t>Staff closes a case with a close reason; case status updates and closure notification sent</t>
         </is>
       </c>
-      <c r="E137" s="43" t="inlineStr">
+      <c r="E138" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing open case
 2. Change Status to 'Closed'
@@ -5277,39 +6059,44 @@
 7. Verify closure email notification dispatched (check Message Queue)</t>
         </is>
       </c>
-      <c r="F137" s="43" t="inlineStr">
+      <c r="F138" s="43" t="inlineStr">
         <is>
           <t>closeReason=Work Complete, completionComment=Works carried out on 01/05/2026</t>
         </is>
       </c>
-      <c r="G137" s="43" t="inlineStr">
+      <c r="G138" s="43" t="inlineStr">
         <is>
           <t>Case Status=Closed; CaseTriggerOperation fires close logic; CommsEventHandler queues notification; Message_Queue__c record created for customer notification</t>
         </is>
       </c>
-    </row>
-    <row r="138" ht="84" customHeight="1">
-      <c r="A138" s="43" t="inlineStr">
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-103</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B138" s="43" t="inlineStr">
+      <c r="B139" s="43" t="inlineStr">
         <is>
           <t>PROP-030</t>
         </is>
       </c>
-      <c r="C138" s="43" t="inlineStr">
+      <c r="C139" s="43" t="inlineStr">
         <is>
           <t>Add Case Note Visible to Community</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
+      <c r="D139" s="43" t="inlineStr">
         <is>
           <t>Staff adds a case note; note is visible in the community portal case detail</t>
         </is>
       </c>
-      <c r="E138" s="43" t="inlineStr">
+      <c r="E139" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing case
 2. Add a new Case Note / Chatter post with visibility set to community
@@ -5319,39 +6106,44 @@
 6. Verify the note is visible</t>
         </is>
       </c>
-      <c r="F138" s="43" t="inlineStr">
+      <c r="F139" s="43" t="inlineStr">
         <is>
           <t>noteText=Your request is currently being assessed by our roads team.</t>
         </is>
       </c>
-      <c r="G138" s="43" t="inlineStr">
+      <c r="G139" s="43" t="inlineStr">
         <is>
           <t>FeedItem created with appropriate visibility; FeedItemTriggerHandler executes; community user sees note in case detail; no error in FeedItemInsertHelperClass</t>
         </is>
       </c>
-    </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="43" t="inlineStr">
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="72" customHeight="1">
+      <c r="A140" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B139" s="43" t="inlineStr">
+      <c r="B140" s="43" t="inlineStr">
         <is>
           <t>PROP-031</t>
         </is>
       </c>
-      <c r="C139" s="43" t="inlineStr">
+      <c r="C140" s="43" t="inlineStr">
         <is>
           <t>Duplicate Case Detection and Linking</t>
         </is>
       </c>
-      <c r="D139" s="43" t="inlineStr">
+      <c r="D140" s="43" t="inlineStr">
         <is>
           <t>When staff creates a case matching an existing open case by category and location, duplicate flag is set and linked</t>
         </is>
       </c>
-      <c r="E139" s="43" t="inlineStr">
+      <c r="E140" s="43" t="inlineStr">
         <is>
           <t>1. Create a case for 'Illegal Dumping' at a specific address
 2. Create a second case with same category and nearby address
@@ -5359,39 +6151,44 @@
 4. Verify the two cases are linked</t>
         </is>
       </c>
-      <c r="F139" s="43" t="inlineStr">
+      <c r="F140" s="43" t="inlineStr">
         <is>
           <t>Two cases with same category and address within duplicate-detection threshold</t>
         </is>
       </c>
-      <c r="G139" s="43" t="inlineStr">
+      <c r="G140" s="43" t="inlineStr">
         <is>
           <t>CaseTriggerOperation duplicate detection fires; cfsuite1__Duplicate__c field populated; parent/child case relationship established</t>
         </is>
       </c>
-    </row>
-    <row r="140" ht="72" customHeight="1">
-      <c r="A140" s="43" t="inlineStr">
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="84" customHeight="1">
+      <c r="A141" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B140" s="43" t="inlineStr">
+      <c r="B141" s="43" t="inlineStr">
         <is>
           <t>PROP-032</t>
         </is>
       </c>
-      <c r="C140" s="43" t="inlineStr">
+      <c r="C141" s="43" t="inlineStr">
         <is>
           <t>Work Order Auto-Creation from Case</t>
         </is>
       </c>
-      <c r="D140" s="43" t="inlineStr">
+      <c r="D141" s="43" t="inlineStr">
         <is>
           <t>When a case with a category that has Create_Work_Order=true is saved, a Work Order is automatically created</t>
         </is>
       </c>
-      <c r="E140" s="43" t="inlineStr">
+      <c r="E141" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a category mapped to a Work Order Mapping Request Flow record with Create_Work_Order=true
 2. Save the case
@@ -5399,39 +6196,44 @@
 4. Verify a Work Order record has been created with the correct category, queue, and record type</t>
         </is>
       </c>
-      <c r="F140" s="43" t="inlineStr">
+      <c r="F141" s="43" t="inlineStr">
         <is>
           <t>Category with Work Order Mapping record: Create_Work_Order=true, WO_Record_Type_Developer_Name populated</t>
         </is>
       </c>
-      <c r="G140" s="43" t="inlineStr">
+      <c r="G141" s="43" t="inlineStr">
         <is>
           <t>WorkOrderHandler creates WorkOrder record; WO linked to Case; cfsuite1__Work_Order_Category__c, cfsuite1__Work_Order_Queue__c populated; WorkOrderMilestoneHelperClass assigns entitlement process if configured</t>
         </is>
       </c>
-    </row>
-    <row r="141" ht="84" customHeight="1">
-      <c r="A141" s="43" t="inlineStr">
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-106</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="72" customHeight="1">
+      <c r="A142" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B141" s="43" t="inlineStr">
+      <c r="B142" s="43" t="inlineStr">
         <is>
           <t>PROP-033</t>
         </is>
       </c>
-      <c r="C141" s="43" t="inlineStr">
+      <c r="C142" s="43" t="inlineStr">
         <is>
           <t>Work Order Status Update Triggers Case Update</t>
         </is>
       </c>
-      <c r="D141" s="43" t="inlineStr">
+      <c r="D142" s="43" t="inlineStr">
         <is>
           <t>When a Work Order is set to 'Completed', the parent Case status is updated per the Request Flow mapping</t>
         </is>
       </c>
-      <c r="E141" s="43" t="inlineStr">
+      <c r="E142" s="43" t="inlineStr">
         <is>
           <t>1. Open a Work Order linked to a Case via a Work Order Mapping record
 2. Change Work Order Status to 'Completed'
@@ -5440,39 +6242,44 @@
 5. Verify Case Status has updated per the New_Status on the Request Flow mapping</t>
         </is>
       </c>
-      <c r="F141" s="43" t="inlineStr">
+      <c r="F142" s="43" t="inlineStr">
         <is>
           <t>Work Order with parent Case and active Work Order Mapping with New_Status and Update_Case=true</t>
         </is>
       </c>
-      <c r="G141" s="43" t="inlineStr">
+      <c r="G142" s="43" t="inlineStr">
         <is>
           <t>WorkOrderTriggerHandler fires; CaseTriggerOperation updates parent case status; Case status matches cfsuite1__New_Status__c from Work Order Mapping record</t>
         </is>
       </c>
-    </row>
-    <row r="142" ht="72" customHeight="1">
-      <c r="A142" s="43" t="inlineStr">
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-107</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="84" customHeight="1">
+      <c r="A143" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B142" s="43" t="inlineStr">
+      <c r="B143" s="43" t="inlineStr">
         <is>
           <t>PROP-034</t>
         </is>
       </c>
-      <c r="C142" s="43" t="inlineStr">
+      <c r="C143" s="43" t="inlineStr">
         <is>
           <t>Work Order Hazard Flag - Emergency SLA Assignment</t>
         </is>
       </c>
-      <c r="D142" s="43" t="inlineStr">
+      <c r="D143" s="43" t="inlineStr">
         <is>
           <t>Marking a work order as a hazard applies the Hazard SLA defined in the Request Flow mapping</t>
         </is>
       </c>
-      <c r="E142" s="43" t="inlineStr">
+      <c r="E143" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing Work Order linked to a category with a Hazard_SLA configured
 2. Set the Hazard flag to true
@@ -5480,39 +6287,44 @@
 4. Verify the SLA on the Work Order has been updated to the Hazard SLA value</t>
         </is>
       </c>
-      <c r="F142" s="43" t="inlineStr">
+      <c r="F143" s="43" t="inlineStr">
         <is>
           <t>Work Order category with Hazard_SLA field populated in Request Flow</t>
         </is>
       </c>
-      <c r="G142" s="43" t="inlineStr">
+      <c r="G143" s="43" t="inlineStr">
         <is>
           <t>WorkOrderUpdateHelperClass applies hazard SLA; EntitlementId updated on Work Order; milestone timestamps recalculated by WorkOrderMilestoneHelperClass</t>
         </is>
       </c>
-    </row>
-    <row r="143" ht="84" customHeight="1">
-      <c r="A143" s="43" t="inlineStr">
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-108</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B143" s="43" t="inlineStr">
+      <c r="B144" s="43" t="inlineStr">
         <is>
           <t>PROP-038</t>
         </is>
       </c>
-      <c r="C143" s="43" t="inlineStr">
+      <c r="C144" s="43" t="inlineStr">
         <is>
           <t>Add Interested Party to a Case</t>
         </is>
       </c>
-      <c r="D143" s="43" t="inlineStr">
+      <c r="D144" s="43" t="inlineStr">
         <is>
           <t>An interested party contact can be added to a case and receives notifications about that case</t>
         </is>
       </c>
-      <c r="E143" s="43" t="inlineStr">
+      <c r="E144" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing Case (internal view)
 2. Navigate to the Interested Parties related list
@@ -5523,152 +6335,172 @@
 7. Verify an email notification is sent to the interested party</t>
         </is>
       </c>
-      <c r="F143" s="43" t="inlineStr">
+      <c r="F144" s="43" t="inlineStr">
         <is>
           <t>Contact: existing test contact not the case requester</t>
         </is>
       </c>
-      <c r="G143" s="43" t="inlineStr">
+      <c r="G144" s="43" t="inlineStr">
         <is>
           <t>cfsuite1__Interested_Parties__c record created linked to Case and Contact; CommsEventHandler dispatches notification to interested party on case update; Message_Queue__c record created</t>
         </is>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="42" t="inlineStr">
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-109</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="48" customHeight="1">
+      <c r="A145" s="42" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B144" s="42" t="n"/>
-      <c r="C144" s="42" t="n"/>
-      <c r="D144" s="42" t="n"/>
-      <c r="E144" s="42" t="n"/>
-      <c r="F144" s="42" t="n"/>
-      <c r="G144" s="42" t="n"/>
-    </row>
-    <row r="145" ht="48" customHeight="1">
-      <c r="A145" s="40" t="inlineStr">
+      <c r="B145" s="42" t="n"/>
+      <c r="C145" s="42" t="n"/>
+      <c r="D145" s="42" t="n"/>
+      <c r="E145" s="42" t="n"/>
+      <c r="F145" s="42" t="n"/>
+      <c r="G145" s="42" t="n"/>
+    </row>
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="40" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B145" s="40" t="inlineStr">
+      <c r="B146" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-077</t>
         </is>
       </c>
-      <c r="C145" s="40" t="inlineStr">
+      <c r="C146" s="40" t="inlineStr">
         <is>
           <t>Automated email notifications</t>
         </is>
       </c>
-      <c r="D145" s="40" t="inlineStr">
+      <c r="D146" s="40" t="inlineStr">
         <is>
           <t>Ability to send automated emails on Case status updates to: . Customer submitting a request . An interested party Both receiving their own unique email template</t>
         </is>
       </c>
-      <c r="E145" s="40" t="n"/>
-      <c r="F145" s="40" t="n"/>
-      <c r="G145" s="40" t="inlineStr">
+      <c r="E146" s="40" t="n"/>
+      <c r="F146" s="40" t="n"/>
+      <c r="G146" s="40" t="inlineStr">
         <is>
           <t>Customer and Interested party receive the correct email templates</t>
         </is>
       </c>
-    </row>
-    <row r="146" ht="36" customHeight="1">
-      <c r="A146" s="41" t="inlineStr">
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="41" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B146" s="41" t="inlineStr">
+      <c r="B147" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-078</t>
         </is>
       </c>
-      <c r="C146" s="41" t="inlineStr">
+      <c r="C147" s="41" t="inlineStr">
         <is>
           <t>Automated SMS notification</t>
         </is>
       </c>
-      <c r="D146" s="41" t="inlineStr">
+      <c r="D147" s="41" t="inlineStr">
         <is>
           <t>Ability to send automated SMS on Case status updates to: . Customer submitting a request . An interested party Both receiving their own unique SMS template</t>
         </is>
       </c>
-      <c r="E146" s="41" t="n"/>
-      <c r="F146" s="41" t="n"/>
-      <c r="G146" s="41" t="inlineStr">
+      <c r="E147" s="41" t="n"/>
+      <c r="F147" s="41" t="n"/>
+      <c r="G147" s="41" t="inlineStr">
         <is>
           <t>Customer and Interested party receive the correct sms templates</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="40" t="inlineStr">
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="40" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B147" s="40" t="inlineStr">
+      <c r="B148" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-079</t>
         </is>
       </c>
-      <c r="C147" s="40" t="inlineStr">
+      <c r="C148" s="40" t="inlineStr">
         <is>
           <t>Ad hoc email and SMS notifications</t>
         </is>
       </c>
-      <c r="D147" s="40" t="n"/>
-      <c r="E147" s="40" t="inlineStr">
+      <c r="D148" s="40" t="n"/>
+      <c r="E148" s="40" t="inlineStr">
         <is>
           <t>Create a case with your own customer record. Add a interested party. Move the case through the statuses.</t>
         </is>
       </c>
-      <c r="F147" s="40" t="n"/>
-      <c r="G147" s="40" t="inlineStr">
+      <c r="F148" s="40" t="n"/>
+      <c r="G148" s="40" t="inlineStr">
         <is>
           <t>Email is received SMS is received Intereaction for both are recorded in the activity timeline</t>
         </is>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="42" t="inlineStr">
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="42" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B148" s="42" t="n"/>
-      <c r="C148" s="42" t="n"/>
-      <c r="D148" s="42" t="n"/>
-      <c r="E148" s="42" t="n"/>
-      <c r="F148" s="42" t="n"/>
-      <c r="G148" s="42" t="n"/>
-    </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="43" t="inlineStr">
+      <c r="B149" s="42" t="n"/>
+      <c r="C149" s="42" t="n"/>
+      <c r="D149" s="42" t="n"/>
+      <c r="E149" s="42" t="n"/>
+      <c r="F149" s="42" t="n"/>
+      <c r="G149" s="42" t="n"/>
+    </row>
+    <row r="150" ht="72" customHeight="1">
+      <c r="A150" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B149" s="43" t="inlineStr">
+      <c r="B150" s="43" t="inlineStr">
         <is>
           <t>PROP-020</t>
         </is>
       </c>
-      <c r="C149" s="43" t="inlineStr">
+      <c r="C150" s="43" t="inlineStr">
         <is>
           <t>View Inbox Messages</t>
         </is>
       </c>
-      <c r="D149" s="43" t="inlineStr">
+      <c r="D150" s="43" t="inlineStr">
         <is>
           <t>User sees a list of incoming messages/notifications in their community inbox</t>
         </is>
       </c>
-      <c r="E149" s="43" t="inlineStr">
+      <c r="E150" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Inbox'
@@ -5677,39 +6509,44 @@
 5. Verify message content renders correctly</t>
         </is>
       </c>
-      <c r="F149" s="43" t="inlineStr">
+      <c r="F150" s="43" t="inlineStr">
         <is>
           <t>User must have at least one cfsuite1__CFSuite_Inbox_Message__c record</t>
         </is>
       </c>
-      <c r="G149" s="43" t="inlineStr">
+      <c r="G150" s="43" t="inlineStr">
         <is>
           <t>cfsuite_MyInboxController / MyInboxControllerQueryHelperClass returns messages for logged-in user; unread count badge displays correctly; message body renders HTML content</t>
         </is>
       </c>
-    </row>
-    <row r="150" ht="72" customHeight="1">
-      <c r="A150" s="43" t="inlineStr">
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="72" customHeight="1">
+      <c r="A151" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B150" s="43" t="inlineStr">
+      <c r="B151" s="43" t="inlineStr">
         <is>
           <t>PROP-021</t>
         </is>
       </c>
-      <c r="C150" s="43" t="inlineStr">
+      <c r="C151" s="43" t="inlineStr">
         <is>
           <t>Message Folder Organisation</t>
         </is>
       </c>
-      <c r="D150" s="43" t="inlineStr">
+      <c r="D151" s="43" t="inlineStr">
         <is>
           <t>Messages can be moved between folders and folder counts update accordingly</t>
         </is>
       </c>
-      <c r="E150" s="43" t="inlineStr">
+      <c r="E151" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Inbox'
@@ -5718,39 +6555,44 @@
 5. Verify message appears in target folder and is removed from Inbox</t>
         </is>
       </c>
-      <c r="F150" s="43" t="inlineStr">
+      <c r="F151" s="43" t="inlineStr">
         <is>
           <t>At least one existing inbox message; at least two folders available</t>
         </is>
       </c>
-      <c r="G150" s="43" t="inlineStr">
+      <c r="G151" s="43" t="inlineStr">
         <is>
           <t>CFSuiteMessageFolderController updates cfsuite1__CFSuite_Message_Folder__c lookup on message; folder message counts reflect change</t>
         </is>
       </c>
-    </row>
-    <row r="151" ht="72" customHeight="1">
-      <c r="A151" s="43" t="inlineStr">
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B151" s="43" t="inlineStr">
+      <c r="B152" s="43" t="inlineStr">
         <is>
           <t>PROP-039</t>
         </is>
       </c>
-      <c r="C151" s="43" t="inlineStr">
+      <c r="C152" s="43" t="inlineStr">
         <is>
           <t>Customer Email Notification on Case Creation</t>
         </is>
       </c>
-      <c r="D151" s="43" t="inlineStr">
+      <c r="D152" s="43" t="inlineStr">
         <is>
           <t>When a case is created with a contact email, an acknowledgement email is sent to the customer</t>
         </is>
       </c>
-      <c r="E151" s="43" t="inlineStr">
+      <c r="E152" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a Contact that has a valid email address
 2. Save the case
@@ -5759,39 +6601,44 @@
 5. Verify recipient email matches contact email</t>
         </is>
       </c>
-      <c r="F151" s="43" t="inlineStr">
+      <c r="F152" s="43" t="inlineStr">
         <is>
           <t>Case with Contact email=test@testcouncil.gov.au, Enable_Staff_Notifications_Create=true on Request Flow</t>
         </is>
       </c>
-      <c r="G151" s="43" t="inlineStr">
+      <c r="G152" s="43" t="inlineStr">
         <is>
           <t>CommsEventHandler fires on case create; Message_Queue__c record created with correct recipient; ScheduleMessageProcessing dispatches email; no error in CommsSettingsEvaluator</t>
         </is>
       </c>
-    </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" s="43" t="inlineStr">
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="72" customHeight="1">
+      <c r="A153" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B152" s="43" t="inlineStr">
+      <c r="B153" s="43" t="inlineStr">
         <is>
           <t>PROP-040</t>
         </is>
       </c>
-      <c r="C152" s="43" t="inlineStr">
+      <c r="C153" s="43" t="inlineStr">
         <is>
           <t>SMS Notification Sent on Case Status Change</t>
         </is>
       </c>
-      <c r="D152" s="43" t="inlineStr">
+      <c r="D153" s="43" t="inlineStr">
         <is>
           <t>When a case is updated and the customer has SMS notification preference, an SMS is queued</t>
         </is>
       </c>
-      <c r="E152" s="43" t="inlineStr">
+      <c r="E153" s="43" t="inlineStr">
         <is>
           <t>1. Create/find a case where the contact has a mobile number and notification preference = Phone
 2. Update the case status
@@ -5799,39 +6646,44 @@
 4. Verify SMS content includes case number and new status</t>
         </is>
       </c>
-      <c r="F152" s="43" t="inlineStr">
+      <c r="F153" s="43" t="inlineStr">
         <is>
           <t>Contact with MobilePhone populated, case cfsuite1__Advise_Your_Preferred_Contact__c=Phone</t>
         </is>
       </c>
-      <c r="G152" s="43" t="inlineStr">
+      <c r="G153" s="43" t="inlineStr">
         <is>
           <t>SMSMessageUtility creates SMS message in Message_Queue__c; SMSMessageTriggerHandler executes; SmsInfo object populated with correct mobile number and case reference</t>
         </is>
       </c>
-    </row>
-    <row r="153" ht="72" customHeight="1">
-      <c r="A153" s="43" t="inlineStr">
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B153" s="43" t="inlineStr">
+      <c r="B154" s="43" t="inlineStr">
         <is>
           <t>PROP-041</t>
         </is>
       </c>
-      <c r="C153" s="43" t="inlineStr">
+      <c r="C154" s="43" t="inlineStr">
         <is>
           <t>Emergency Notification - After Hours</t>
         </is>
       </c>
-      <c r="D153" s="43" t="inlineStr">
+      <c r="D154" s="43" t="inlineStr">
         <is>
           <t>A case flagged as Emergency triggers an after-hours notification to the configured recipient</t>
         </is>
       </c>
-      <c r="E153" s="43" t="inlineStr">
+      <c r="E154" s="43" t="inlineStr">
         <is>
           <t>1. Create a case with category where Emergency_Notification=Yes on Request Flow
 2. Save the case
@@ -5839,210 +6691,240 @@
 4. Check Message Queue for after-hours alert record</t>
         </is>
       </c>
-      <c r="F153" s="43" t="inlineStr">
+      <c r="F154" s="43" t="inlineStr">
         <is>
           <t>Category with Emergency_Notification=Yes and Notify_After_Hours email configured</t>
         </is>
       </c>
-      <c r="G153" s="43" t="inlineStr">
+      <c r="G154" s="43" t="inlineStr">
         <is>
           <t>EmergencyCommsSettingEvaluator fires; after-hours email queued in Message_Queue__c; notification clearly identified as emergency; contact details included in message</t>
         </is>
       </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="42" t="inlineStr">
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" s="42" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B154" s="42" t="n"/>
-      <c r="C154" s="42" t="n"/>
-      <c r="D154" s="42" t="n"/>
-      <c r="E154" s="42" t="n"/>
-      <c r="F154" s="42" t="n"/>
-      <c r="G154" s="42" t="n"/>
-    </row>
-    <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="40" t="inlineStr">
+      <c r="B155" s="42" t="n"/>
+      <c r="C155" s="42" t="n"/>
+      <c r="D155" s="42" t="n"/>
+      <c r="E155" s="42" t="n"/>
+      <c r="F155" s="42" t="n"/>
+      <c r="G155" s="42" t="n"/>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B155" s="40" t="inlineStr">
+      <c r="B156" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-109</t>
         </is>
       </c>
-      <c r="C155" s="40" t="inlineStr">
+      <c r="C156" s="40" t="inlineStr">
         <is>
           <t>Personalised Councillor Interface</t>
         </is>
       </c>
-      <c r="D155" s="40" t="inlineStr">
+      <c r="D156" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to have a personalised councillor interface when logging into the portal</t>
         </is>
       </c>
-      <c r="E155" s="40" t="n"/>
-      <c r="F155" s="40" t="n"/>
-      <c r="G155" s="40" t="inlineStr">
+      <c r="E156" s="40" t="n"/>
+      <c r="F156" s="40" t="n"/>
+      <c r="G156" s="40" t="inlineStr">
         <is>
           <t>1. Councillor sees additional functionality such as All Questions and My questions</t>
         </is>
       </c>
-    </row>
-    <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="41" t="inlineStr">
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" s="41" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B156" s="41" t="inlineStr">
+      <c r="B157" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-110</t>
         </is>
       </c>
-      <c r="C156" s="41" t="inlineStr">
+      <c r="C157" s="41" t="inlineStr">
         <is>
           <t>Standard Request Portal Features for councillor</t>
         </is>
       </c>
-      <c r="D156" s="41" t="inlineStr">
+      <c r="D157" s="41" t="inlineStr">
         <is>
           <t>The Councillor portal shall include all the standard features available in the CFSuite Request portal</t>
         </is>
       </c>
-      <c r="E156" s="41" t="n"/>
-      <c r="F156" s="41" t="n"/>
-      <c r="G156" s="41" t="inlineStr">
+      <c r="E157" s="41" t="n"/>
+      <c r="F157" s="41" t="n"/>
+      <c r="G157" s="41" t="inlineStr">
         <is>
           <t>1. Councillor sees Standard portal functionality</t>
         </is>
       </c>
-    </row>
-    <row r="157" ht="24" customHeight="1">
-      <c r="A157" s="40" t="inlineStr">
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1">
+      <c r="A158" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B157" s="40" t="inlineStr">
+      <c r="B158" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-111</t>
         </is>
       </c>
-      <c r="C157" s="40" t="inlineStr">
+      <c r="C158" s="40" t="inlineStr">
         <is>
           <t>Submit Councillor Questions</t>
         </is>
       </c>
-      <c r="D157" s="40" t="inlineStr">
+      <c r="D158" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to submit councillor questions through the portal</t>
         </is>
       </c>
-      <c r="E157" s="40" t="n"/>
-      <c r="F157" s="40" t="n"/>
-      <c r="G157" s="40" t="inlineStr">
+      <c r="E158" s="40" t="n"/>
+      <c r="F158" s="40" t="n"/>
+      <c r="G158" s="40" t="inlineStr">
         <is>
           <t>1. Check the Councillor Question is created correctly</t>
         </is>
       </c>
-    </row>
-    <row r="158" ht="36" customHeight="1">
-      <c r="A158" s="41" t="inlineStr">
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="41" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B158" s="41" t="inlineStr">
+      <c r="B159" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-112</t>
         </is>
       </c>
-      <c r="C158" s="41" t="inlineStr">
+      <c r="C159" s="41" t="inlineStr">
         <is>
           <t>View and Filter All Councillor Questions</t>
         </is>
       </c>
-      <c r="D158" s="41" t="inlineStr">
+      <c r="D159" s="41" t="inlineStr">
         <is>
           <t>Ability for Councillors to view the questions and answers of councillor questions for: a. Their own questions b. All other councillor questions</t>
         </is>
       </c>
-      <c r="E158" s="41" t="n"/>
-      <c r="F158" s="41" t="n"/>
-      <c r="G158" s="41" t="inlineStr">
+      <c r="E159" s="41" t="n"/>
+      <c r="F159" s="41" t="n"/>
+      <c r="G159" s="41" t="inlineStr">
         <is>
           <t>1. Check that you can see other councillor's requests 2. Check you can filter on the All Questions by Councillor and Status</t>
         </is>
       </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="40" t="inlineStr">
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B159" s="40" t="inlineStr">
+      <c r="B160" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-113</t>
         </is>
       </c>
-      <c r="C159" s="40" t="inlineStr">
+      <c r="C160" s="40" t="inlineStr">
         <is>
           <t>Log a request for on behalf of resident</t>
         </is>
       </c>
-      <c r="D159" s="40" t="inlineStr">
+      <c r="D160" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to log a request on behalf of a resident</t>
         </is>
       </c>
-      <c r="E159" s="40" t="n"/>
-      <c r="F159" s="40" t="n"/>
-      <c r="G159" s="40" t="inlineStr">
+      <c r="E160" s="40" t="n"/>
+      <c r="F160" s="40" t="n"/>
+      <c r="G160" s="40" t="inlineStr">
         <is>
           <t>1. Check the request is created with the additional information about who requested it.</t>
         </is>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="42" t="inlineStr">
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="84" customHeight="1">
+      <c r="A161" s="42" t="inlineStr">
         <is>
           <t>Proposed - Councillor Portal</t>
         </is>
       </c>
-      <c r="B160" s="42" t="n"/>
-      <c r="C160" s="42" t="n"/>
-      <c r="D160" s="42" t="n"/>
-      <c r="E160" s="42" t="n"/>
-      <c r="F160" s="42" t="n"/>
-      <c r="G160" s="42" t="n"/>
-    </row>
-    <row r="161" ht="84" customHeight="1">
-      <c r="A161" s="43" t="inlineStr">
+      <c r="B161" s="42" t="n"/>
+      <c r="C161" s="42" t="n"/>
+      <c r="D161" s="42" t="n"/>
+      <c r="E161" s="42" t="n"/>
+      <c r="F161" s="42" t="n"/>
+      <c r="G161" s="42" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="inlineStr">
         <is>
           <t>Proposed - Councillor Portal</t>
         </is>
       </c>
-      <c r="B161" s="43" t="inlineStr">
+      <c r="B162" s="43" t="inlineStr">
         <is>
           <t>PROP-049</t>
         </is>
       </c>
-      <c r="C161" s="43" t="inlineStr">
+      <c r="C162" s="43" t="inlineStr">
         <is>
           <t>Create Councillor Question Case</t>
         </is>
       </c>
-      <c r="D161" s="43" t="inlineStr">
+      <c r="D162" s="43" t="inlineStr">
         <is>
           <t>A case with Record Type 'Councillor Question' is created and routed to the correct queue</t>
         </is>
       </c>
-      <c r="E161" s="43" t="inlineStr">
+      <c r="E162" s="43" t="inlineStr">
         <is>
           <t>1. Log in as internal staff
 2. Create a new Case
@@ -6053,157 +6935,182 @@
 7. Verify case visible in Councillor Question list view</t>
         </is>
       </c>
-      <c r="F161" s="43" t="inlineStr">
+      <c r="F162" s="43" t="inlineStr">
         <is>
           <t>Subject=Councillor query about drainage on Elm St, Contact=test councillor contact</t>
         </is>
       </c>
-      <c r="G161" s="43" t="inlineStr">
+      <c r="G162" s="43" t="inlineStr">
         <is>
           <t>Case RecordType=Councillor_Question; CaseTriggerOperation assigns to configured queue; case appears in Councillor Question list view; notification sent to responsible officer</t>
         </is>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="42" t="inlineStr">
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>CFSUITE-CP-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="24" customHeight="1">
+      <c r="A163" s="42" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B162" s="42" t="n"/>
-      <c r="C162" s="42" t="n"/>
-      <c r="D162" s="42" t="n"/>
-      <c r="E162" s="42" t="n"/>
-      <c r="F162" s="42" t="n"/>
-      <c r="G162" s="42" t="n"/>
-    </row>
-    <row r="163" ht="24" customHeight="1">
-      <c r="A163" s="40" t="inlineStr">
+      <c r="B163" s="42" t="n"/>
+      <c r="C163" s="42" t="n"/>
+      <c r="D163" s="42" t="n"/>
+      <c r="E163" s="42" t="n"/>
+      <c r="F163" s="42" t="n"/>
+      <c r="G163" s="42" t="n"/>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="40" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B163" s="40" t="inlineStr">
+      <c r="B164" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-120</t>
         </is>
       </c>
-      <c r="C163" s="40" t="inlineStr">
+      <c r="C164" s="40" t="inlineStr">
         <is>
           <t>Create Knowledge Article</t>
         </is>
       </c>
-      <c r="D163" s="40" t="n"/>
-      <c r="E163" s="40" t="inlineStr">
+      <c r="D164" s="40" t="n"/>
+      <c r="E164" s="40" t="inlineStr">
         <is>
           <t>https://scribehow.com/shared/Configure_a_Dynamic_Knowledge_Article__jX58ZzIuQdetSLJFfS5JAg</t>
         </is>
       </c>
-      <c r="F163" s="40" t="n"/>
-      <c r="G163" s="40" t="n"/>
-    </row>
-    <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="41" t="inlineStr">
+      <c r="F164" s="40" t="n"/>
+      <c r="G164" s="40" t="n"/>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="24" customHeight="1">
+      <c r="A165" s="41" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B164" s="41" t="inlineStr">
+      <c r="B165" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-121</t>
         </is>
       </c>
-      <c r="C164" s="41" t="inlineStr">
+      <c r="C165" s="41" t="inlineStr">
         <is>
           <t>View knowledge articles when creating requests</t>
         </is>
       </c>
-      <c r="D164" s="41" t="n"/>
-      <c r="E164" s="41" t="inlineStr">
+      <c r="D165" s="41" t="n"/>
+      <c r="E165" s="41" t="inlineStr">
         <is>
           <t>https://scribehow.com/shared/Configure_a_Dynamic_Knowledge_Article__jX58ZzIuQdetSLJFfS5JAg</t>
         </is>
       </c>
-      <c r="F164" s="41" t="n"/>
-      <c r="G164" s="41" t="n"/>
-    </row>
-    <row r="165" ht="24" customHeight="1">
-      <c r="A165" s="40" t="inlineStr">
+      <c r="F165" s="41" t="n"/>
+      <c r="G165" s="41" t="n"/>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" s="40" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B165" s="40" t="inlineStr">
+      <c r="B166" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-122</t>
         </is>
       </c>
-      <c r="C165" s="40" t="inlineStr">
+      <c r="C166" s="40" t="inlineStr">
         <is>
           <t>Create salesforce users through active directory</t>
         </is>
       </c>
-      <c r="D165" s="40" t="n"/>
-      <c r="E165" s="40" t="n"/>
-      <c r="F165" s="40" t="n"/>
-      <c r="G165" s="40" t="n"/>
-    </row>
-    <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="41" t="inlineStr">
+      <c r="D166" s="40" t="n"/>
+      <c r="E166" s="40" t="n"/>
+      <c r="F166" s="40" t="n"/>
+      <c r="G166" s="40" t="n"/>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="41" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B166" s="41" t="inlineStr">
+      <c r="B167" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-123</t>
         </is>
       </c>
-      <c r="C166" s="41" t="inlineStr">
+      <c r="C167" s="41" t="inlineStr">
         <is>
           <t>Create admin accounts with MFA</t>
         </is>
       </c>
-      <c r="D166" s="41" t="n"/>
-      <c r="E166" s="41" t="n"/>
-      <c r="F166" s="41" t="n"/>
-      <c r="G166" s="41" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="42" t="inlineStr">
+      <c r="D167" s="41" t="n"/>
+      <c r="E167" s="41" t="n"/>
+      <c r="F167" s="41" t="n"/>
+      <c r="G167" s="41" t="n"/>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="72" customHeight="1">
+      <c r="A168" s="42" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B167" s="42" t="n"/>
-      <c r="C167" s="42" t="n"/>
-      <c r="D167" s="42" t="n"/>
-      <c r="E167" s="42" t="n"/>
-      <c r="F167" s="42" t="n"/>
-      <c r="G167" s="42" t="n"/>
-    </row>
-    <row r="168" ht="72" customHeight="1">
-      <c r="A168" s="43" t="inlineStr">
+      <c r="B168" s="42" t="n"/>
+      <c r="C168" s="42" t="n"/>
+      <c r="D168" s="42" t="n"/>
+      <c r="E168" s="42" t="n"/>
+      <c r="F168" s="42" t="n"/>
+      <c r="G168" s="42" t="n"/>
+    </row>
+    <row r="169" ht="72" customHeight="1">
+      <c r="A169" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B168" s="43" t="inlineStr">
+      <c r="B169" s="43" t="inlineStr">
         <is>
           <t>PROP-035</t>
         </is>
       </c>
-      <c r="C168" s="43" t="inlineStr">
+      <c r="C169" s="43" t="inlineStr">
         <is>
           <t>Display Category Visible in Community</t>
         </is>
       </c>
-      <c r="D168" s="43" t="inlineStr">
+      <c r="D169" s="43" t="inlineStr">
         <is>
           <t>A Display Category Request Flow record with Is_Hidden_From_Community=false appears in the community category list</t>
         </is>
       </c>
-      <c r="E168" s="43" t="inlineStr">
+      <c r="E169" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request'
@@ -6211,39 +7118,44 @@
 4. Verify categories with Is_Hidden_From_Community=true do NOT appear</t>
         </is>
       </c>
-      <c r="F168" s="43" t="inlineStr">
+      <c r="F169" s="43" t="inlineStr">
         <is>
           <t>At least one Display Category record with Is_Hidden_From_Community=false and one with =true</t>
         </is>
       </c>
-      <c r="G168" s="43" t="inlineStr">
+      <c r="G169" s="43" t="inlineStr">
         <is>
           <t>CommunityUserRequestFlowHelperClass filters correctly; hidden categories absent from list; category icons (Pin_Image) render from static resource</t>
         </is>
       </c>
-    </row>
-    <row r="169" ht="72" customHeight="1">
-      <c r="A169" s="43" t="inlineStr">
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B169" s="43" t="inlineStr">
+      <c r="B170" s="43" t="inlineStr">
         <is>
           <t>PROP-036</t>
         </is>
       </c>
-      <c r="C169" s="43" t="inlineStr">
+      <c r="C170" s="43" t="inlineStr">
         <is>
           <t>Category Search / Filter in Community</t>
         </is>
       </c>
-      <c r="D169" s="43" t="inlineStr">
+      <c r="D170" s="43" t="inlineStr">
         <is>
           <t>User can search for a category by keyword and results filter to matching categories</t>
         </is>
       </c>
-      <c r="E169" s="43" t="inlineStr">
+      <c r="E170" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request'
@@ -6252,39 +7164,44 @@
 5. Clear the search and verify full category list returns</t>
         </is>
       </c>
-      <c r="F169" s="43" t="inlineStr">
+      <c r="F170" s="43" t="inlineStr">
         <is>
           <t>searchTerm=dog (should match multiple Animals categories)</t>
         </is>
       </c>
-      <c r="G169" s="43" t="inlineStr">
+      <c r="G170" s="43" t="inlineStr">
         <is>
           <t>Category search filters against category Name and cfsuite1__Search_Tag__c field; results update in real-time or on submit; no search returns full list</t>
         </is>
       </c>
-    </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" s="43" t="inlineStr">
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B170" s="43" t="inlineStr">
+      <c r="B171" s="43" t="inlineStr">
         <is>
           <t>PROP-037</t>
         </is>
       </c>
-      <c r="C170" s="43" t="inlineStr">
+      <c r="C171" s="43" t="inlineStr">
         <is>
           <t>Deflection Journey - Category with Deflection Text</t>
         </is>
       </c>
-      <c r="D170" s="43" t="inlineStr">
+      <c r="D171" s="43" t="inlineStr">
         <is>
           <t>Selecting a category with Form_Type=Deflection shows informational text instead of a submission form</t>
         </is>
       </c>
-      <c r="E170" s="43" t="inlineStr">
+      <c r="E171" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category configured with Form_Type=Deflection
@@ -6292,39 +7209,44 @@
 4. Verify no case is created</t>
         </is>
       </c>
-      <c r="F170" s="43" t="inlineStr">
+      <c r="F171" s="43" t="inlineStr">
         <is>
           <t>A Display Category with Form_Type=Deflection and Deflection_Text populated</t>
         </is>
       </c>
-      <c r="G170" s="43" t="inlineStr">
+      <c r="G171" s="43" t="inlineStr">
         <is>
           <t>LWC renders Deflection_Text__c content; no Case record created; user presented with alternate resolution information (e.g. external link or phone number)</t>
         </is>
       </c>
-    </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" s="43" t="inlineStr">
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="48" customHeight="1">
+      <c r="A172" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B171" s="43" t="inlineStr">
+      <c r="B172" s="43" t="inlineStr">
         <is>
           <t>PROP-050</t>
         </is>
       </c>
-      <c r="C171" s="43" t="inlineStr">
+      <c r="C172" s="43" t="inlineStr">
         <is>
           <t>Knowledge Article Surfaced in Community Category Journey</t>
         </is>
       </c>
-      <c r="D171" s="43" t="inlineStr">
+      <c r="D172" s="43" t="inlineStr">
         <is>
           <t>Relevant knowledge articles are presented to community users during the category journey before submission</t>
         </is>
       </c>
-      <c r="E171" s="43" t="inlineStr">
+      <c r="E172" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category that has linked CFSuite_Article records
@@ -6332,39 +7254,44 @@
 4. Click an article link and verify it opens the full article</t>
         </is>
       </c>
-      <c r="F171" s="43" t="inlineStr">
+      <c r="F172" s="43" t="inlineStr">
         <is>
           <t>Category with linked cfsuite1__CFSuite_Article__c records</t>
         </is>
       </c>
-      <c r="G171" s="43" t="inlineStr">
+      <c r="G172" s="43" t="inlineStr">
         <is>
           <t>KnowledgeController returns articles matching the selected category; articles rendered in community LWC component; article click navigates correctly; deflection rate trackable</t>
         </is>
       </c>
-    </row>
-    <row r="172" ht="48" customHeight="1">
-      <c r="A172" s="43" t="inlineStr">
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="84" customHeight="1">
+      <c r="A173" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B172" s="43" t="inlineStr">
+      <c r="B173" s="43" t="inlineStr">
         <is>
           <t>PROP-051</t>
         </is>
       </c>
-      <c r="C172" s="43" t="inlineStr">
+      <c r="C173" s="43" t="inlineStr">
         <is>
           <t>Dynamic Banner Displays on Community Home</t>
         </is>
       </c>
-      <c r="D172" s="43" t="inlineStr">
+      <c r="D173" s="43" t="inlineStr">
         <is>
           <t>Active dynamic banner content is displayed on the community portal home page</t>
         </is>
       </c>
-      <c r="E172" s="43" t="inlineStr">
+      <c r="E173" s="43" t="inlineStr">
         <is>
           <t>1. Ensure at least one active banner is configured
 2. Log in (or browse as guest) to community portal home page
@@ -6372,39 +7299,44 @@
 4. Verify expired or inactive banners are NOT shown</t>
         </is>
       </c>
-      <c r="F172" s="43" t="inlineStr">
+      <c r="F173" s="43" t="inlineStr">
         <is>
           <t>Active banner record in community settings</t>
         </is>
       </c>
-      <c r="G172" s="43" t="inlineStr">
+      <c r="G173" s="43" t="inlineStr">
         <is>
           <t>DynamicBannerController returns active banner(s); banner renders in designated LWC slot on home page; expired banners filtered out by date</t>
         </is>
       </c>
-    </row>
-    <row r="173" ht="84" customHeight="1">
-      <c r="A173" s="43" t="inlineStr">
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="84" customHeight="1">
+      <c r="A174" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B173" s="43" t="inlineStr">
+      <c r="B174" s="43" t="inlineStr">
         <is>
           <t>PROP-056</t>
         </is>
       </c>
-      <c r="C173" s="43" t="inlineStr">
+      <c r="C174" s="43" t="inlineStr">
         <is>
           <t>CFSuite Settings - Integration Settings Persist</t>
         </is>
       </c>
-      <c r="D173" s="43" t="inlineStr">
+      <c r="D174" s="43" t="inlineStr">
         <is>
           <t>Admin can update CFSuite integration settings and the values are reflected in system behaviour</t>
         </is>
       </c>
-      <c r="E173" s="43" t="inlineStr">
+      <c r="E174" s="43" t="inlineStr">
         <is>
           <t>1. Log in as system administrator
 2. Navigate to CFSuite Integration Settings (cfsuite1__CFSuiteIntegrationSettings__c)
@@ -6413,39 +7345,44 @@
 5. Verify the CFSuiteIntegrationSettings Apex class returns the updated value</t>
         </is>
       </c>
-      <c r="F173" s="43" t="inlineStr">
+      <c r="F174" s="43" t="inlineStr">
         <is>
           <t>Any non-critical integration setting field</t>
         </is>
       </c>
-      <c r="G173" s="43" t="inlineStr">
+      <c r="G174" s="43" t="inlineStr">
         <is>
           <t>CFSuiteSettings / CFSuiteSettingsUtility Apex classes read updated value; no caching issues; setting change does not require org restart</t>
         </is>
       </c>
-    </row>
-    <row r="174" ht="84" customHeight="1">
-      <c r="A174" s="43" t="inlineStr">
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="72" customHeight="1">
+      <c r="A175" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B174" s="43" t="inlineStr">
+      <c r="B175" s="43" t="inlineStr">
         <is>
           <t>PROP-057</t>
         </is>
       </c>
-      <c r="C174" s="43" t="inlineStr">
+      <c r="C175" s="43" t="inlineStr">
         <is>
           <t>Batch Settings - Entitlement Update Scheduled Job</t>
         </is>
       </c>
-      <c r="D174" s="43" t="inlineStr">
+      <c r="D175" s="43" t="inlineStr">
         <is>
           <t>The scheduled entitlement update batch job runs successfully and updates overdue entitlements</t>
         </is>
       </c>
-      <c r="E174" s="43" t="inlineStr">
+      <c r="E175" s="43" t="inlineStr">
         <is>
           <t>1. Log in as system administrator
 2. Verify ScheduleEntitlementUpdate is scheduled via Scheduled Jobs
@@ -6454,39 +7391,44 @@
 5. Verify no Apex errors in the job log</t>
         </is>
       </c>
-      <c r="F174" s="43" t="inlineStr">
+      <c r="F175" s="43" t="inlineStr">
         <is>
           <t>Cases with milestone-driven entitlement processes and overdue milestones</t>
         </is>
       </c>
-      <c r="G174" s="43" t="inlineStr">
+      <c r="G175" s="43" t="inlineStr">
         <is>
           <t>ScheduleEntitlementUpdate batch executes without Apex exceptions; CaseMilestone IsCompleted updated for resolved cases; Batch_Settings__c configuration respected (batch size)</t>
         </is>
       </c>
-    </row>
-    <row r="175" ht="72" customHeight="1">
-      <c r="A175" s="43" t="inlineStr">
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B175" s="43" t="inlineStr">
+      <c r="B176" s="43" t="inlineStr">
         <is>
           <t>PROP-058</t>
         </is>
       </c>
-      <c r="C175" s="43" t="inlineStr">
+      <c r="C176" s="43" t="inlineStr">
         <is>
           <t>MLG Community Link - Cross-Org Case Visibility</t>
         </is>
       </c>
-      <c r="D175" s="43" t="inlineStr">
+      <c r="D176" s="43" t="inlineStr">
         <is>
           <t>A case shared via MLG Community Link is visible to the linked partner council portal user</t>
         </is>
       </c>
-      <c r="E175" s="43" t="inlineStr">
+      <c r="E176" s="43" t="inlineStr">
         <is>
           <t>1. Create a case in the primary council org
 2. Create a CFSuite_MLG_Community_Link__c record linking the case to a partner council
@@ -6495,14 +7437,19 @@
 5. Verify case detail (but not restricted fields) is accessible</t>
         </is>
       </c>
-      <c r="F175" s="43" t="inlineStr">
+      <c r="F176" s="43" t="inlineStr">
         <is>
           <t>Two council orgs configured with MLG integration; test case in primary org</t>
         </is>
       </c>
-      <c r="G175" s="43" t="inlineStr">
+      <c r="G176" s="43" t="inlineStr">
         <is>
           <t>CommunityUserMLGQueryHelperClass returns linked cases; cfsuite1__CFSuite_MLG_Community_Link__c record drives visibility; confidential fields suppressed in cross-org view</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>CFSUITE-CA-012</t>
         </is>
       </c>
     </row>
@@ -6515,11 +7462,29 @@
     <mergeCell ref="H1:T1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG44" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG47" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG48" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG69" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG72" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH35" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH37" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH44" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH45" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH46" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH47" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH48" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH49" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH68" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH69" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH70" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH72" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH73" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH74" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH77" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH79" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH80" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH81" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH84" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH101" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH115" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH120" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH123" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documentation/Automated Testing CFSuite.xlsx
+++ b/documentation/Automated Testing CFSuite.xlsx
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -479,6 +479,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH176"/>
+  <dimension ref="A1:AH226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2345,179 +2348,159 @@
       </c>
     </row>
     <row r="34" ht="35.25" customHeight="1">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Proposed - Authentication &amp; User Management</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PROP-067-AU</t>
+        </is>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>Merging duplicate customers consolidates property customer links</t>
+        </is>
+      </c>
+      <c r="D34" s="48" t="inlineStr">
+        <is>
+          <t>Two duplicate customer accounts each linked to the same property via Property_Customer records. Merging the customers consolidates the property_customer relationships.
+Source: Release 3.154 (26354, 36188)</t>
+        </is>
+      </c>
+      <c r="G34" s="48" t="inlineStr">
+        <is>
+          <t>After merge into the customer with the portal account, only one Property_Customer record remains for that property; the count reflects accurately after refresh.</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-030</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="135" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Proposed - Authentication &amp; User Management</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PROP-068-AU</t>
+        </is>
+      </c>
+      <c r="C35" s="48" t="inlineStr">
+        <is>
+          <t>Display Business Address New Customer setting controls visibility</t>
+        </is>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>Custom setting 'Display Business Address New Customer' controls whether the address section is visible when creating a new Business customer.
+Source: Release 3.154 (40339)</t>
+        </is>
+      </c>
+      <c r="G35" s="48" t="inlineStr">
+        <is>
+          <t>Setting = Yes: address section visible. Setting = No: address section hidden.</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-031</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-001_create_case_with_location.robot</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="135" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Proposed - Authentication &amp; User Management</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PROP-069-AU</t>
+        </is>
+      </c>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>Update password via My Profile - forgot password link</t>
+        </is>
+      </c>
+      <c r="D36" s="48" t="inlineStr">
+        <is>
+          <t>Logged-in community user navigates to My Profile &gt; Account and password &gt; Update Password; clicking the forgotten password link sends a reset email; the link works to reset the password.
+Source: Release 3.154 (36043) / 3.151</t>
+        </is>
+      </c>
+      <c r="G36" s="48" t="inlineStr">
+        <is>
+          <t>Reset email received; following the link allows password change; user can log in with new password.</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="135" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Proposed - Authentication &amp; User Management</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PROP-070-AU</t>
+        </is>
+      </c>
+      <c r="C37" s="48" t="inlineStr">
+        <is>
+          <t>Update password via My Profile - current/new/confirm</t>
+        </is>
+      </c>
+      <c r="D37" s="48" t="inlineStr">
+        <is>
+          <t>Logged-in community user changes their password using the Current/New/Confirm fields on the My Profile screen.
+Source: Release 3.154 (36043)</t>
+        </is>
+      </c>
+      <c r="G37" s="48" t="inlineStr">
+        <is>
+          <t>Submitting valid current + matching new/confirm fields shows the success message and returns to My Profile; mismatched or wrong current password shows the appropriate error.</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>CFSUITE-AU-033</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-003_create_case_from_account.robot</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="135" customHeight="1">
+      <c r="A38" s="42" t="inlineStr">
         <is>
           <t>Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="42" t="n"/>
-    </row>
-    <row r="35" ht="135" customHeight="1">
-      <c r="A35" s="40" t="inlineStr">
-        <is>
-          <t>Service Requests &amp; Case Management</t>
-        </is>
-      </c>
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>CoM-Test-015</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Create Request with Accurate Routing</t>
-        </is>
-      </c>
-      <c r="D35" s="40" t="inlineStr">
-        <is>
-          <t>Ability to create request type categories with reasons and subreason to support accurate routing Ability to add a file on first case creation page Ability to view the team and team members the request will be routed to Ability to add a Question to the request flow</t>
-        </is>
-      </c>
-      <c r="E35" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Create_Request_with_Accurate_Routing___BQBH33jRYCfMq2WyWuV9g</t>
-        </is>
-      </c>
-      <c r="F35" s="40" t="n"/>
-      <c r="G35" s="40" t="inlineStr">
-        <is>
-          <t>Create case button is on customer page layout and when creating case the customer details come through and a basic case can get created</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-001</t>
-        </is>
-      </c>
-      <c r="AH35" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-001 (robot/tests/requests/CFSUITE-SR-001_create_case_with_location.robot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="135" customHeight="1">
-      <c r="A36" s="41" t="inlineStr">
-        <is>
-          <t>Service Requests &amp; Case Management</t>
-        </is>
-      </c>
-      <c r="B36" s="41" t="inlineStr">
-        <is>
-          <t>CoM-Test-016</t>
-        </is>
-      </c>
-      <c r="C36" s="41" t="inlineStr">
-        <is>
-          <t>Deflection when creating a request category</t>
-        </is>
-      </c>
-      <c r="D36" s="41" t="inlineStr">
-        <is>
-          <t>Ability to have a category, reason, subreason to be configured to create a deflection page.</t>
-        </is>
-      </c>
-      <c r="E36" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/How_to_Set_Up_an_Internal_Deflection__zwMaJq04TbGVZq043bt_1g</t>
-        </is>
-      </c>
-      <c r="F36" s="41" t="n"/>
-      <c r="G36" s="41" t="inlineStr">
-        <is>
-          <t>a. can view a popup to display deflection content when a category selection is made that does not create a case.</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="135" customHeight="1">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>Service Requests &amp; Case Management</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>CoM-Test-017</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Match Rquest to Existing Customer or Create New one</t>
-        </is>
-      </c>
-      <c r="D37" s="40" t="inlineStr">
-        <is>
-          <t>1. Ability to match requests to existing customers or create new ones 2. Ability to create request from the community member record which will auto link the community member to the request</t>
-        </is>
-      </c>
-      <c r="E37" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Match_Request_to_Existing_Customer_or_Create_new_one__0wECFc9rSPONm-K6BaMfHw</t>
-        </is>
-      </c>
-      <c r="F37" s="40" t="n"/>
-      <c r="G37" s="40" t="inlineStr">
-        <is>
-          <t>a. can add customer during request b. can add an existing customer c. can goto customer request and create request, and customer is auto added to the request form</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-003</t>
-        </is>
-      </c>
-      <c r="AH37" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-003 (robot/tests/requests/CFSUITE-SR-003_create_case_from_account.robot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="135" customHeight="1">
-      <c r="A38" s="41" t="inlineStr">
-        <is>
-          <t>Service Requests &amp; Case Management</t>
-        </is>
-      </c>
-      <c r="B38" s="41" t="inlineStr">
-        <is>
-          <t>CoM-Test-018</t>
-        </is>
-      </c>
-      <c r="C38" s="41" t="inlineStr">
-        <is>
-          <t>Send E-mail to Request Owner when Case is Created and Ownership Changes</t>
-        </is>
-      </c>
-      <c r="D38" s="41" t="inlineStr">
-        <is>
-          <t>Ability to send an email to a request owner (internal staff) when the request is created and on change of ownership</t>
-        </is>
-      </c>
-      <c r="E38" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Send_automated_emails_on_Case_status_updates__V31q4CETSb-LcCWIlJhtbA</t>
-        </is>
-      </c>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="41" t="inlineStr">
-        <is>
-          <t>a. when case assigned to user, user is notified by email they are the new owner b. if owner is manually updated, then user if notified they are now the owner c. all members of queues need to be notified when a new wo is assigned to that queue</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-004</t>
-        </is>
-      </c>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="42" t="n"/>
     </row>
     <row r="39" ht="180" customHeight="1">
       <c r="A39" s="40" t="inlineStr">
@@ -2527,33 +2510,38 @@
       </c>
       <c r="B39" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-019</t>
+          <t>CoM-Test-015</t>
         </is>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
-          <t>Find Correct Request Categories</t>
+          <t>Create Request with Accurate Routing</t>
         </is>
       </c>
       <c r="D39" s="40" t="inlineStr">
         <is>
-          <t>Ability to easily find correct request categories by: . Allowing popular requests (Ignore) . Tool tips . SmartSearch tags</t>
+          <t>Ability to create request type categories with reasons and subreason to support accurate routing Ability to add a file on first case creation page Ability to view the team and team members the request will be routed to Ability to add a Question to the request flow</t>
         </is>
       </c>
       <c r="E39" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Find_Correct_Request_Categories__sx5OFbdqQcmacGmzZAkztQ</t>
+          <t>https://scribehow.com/shared/Create_Request_with_Accurate_Routing___BQBH33jRYCfMq2WyWuV9g</t>
         </is>
       </c>
       <c r="F39" s="40" t="n"/>
       <c r="G39" s="40" t="inlineStr">
         <is>
-          <t>a. popular categories config is working b. tool tips can be updated c. smart search tags can be updated</t>
+          <t>Create case button is on customer page layout and when creating case the customer details come through and a basic case can get created</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-005</t>
+          <t>CFSUITE-SR-001</t>
+        </is>
+      </c>
+      <c r="AH39" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-001 (robot/tests/requests/CFSUITE-SR-001_create_case_with_location.robot)</t>
         </is>
       </c>
     </row>
@@ -2565,29 +2553,33 @@
       </c>
       <c r="B40" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-020</t>
+          <t>CoM-Test-016</t>
         </is>
       </c>
       <c r="C40" s="41" t="inlineStr">
         <is>
-          <t>Select Request Location</t>
+          <t>Deflection when creating a request category</t>
         </is>
       </c>
       <c r="D40" s="41" t="inlineStr">
         <is>
-          <t>Ability to select a request location by: . Dropping a pin using GIS map . Searching for request location</t>
-        </is>
-      </c>
-      <c r="E40" s="41" t="n"/>
+          <t>Ability to have a category, reason, subreason to be configured to create a deflection page.</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/How_to_Set_Up_an_Internal_Deflection__zwMaJq04TbGVZq043bt_1g</t>
+        </is>
+      </c>
       <c r="F40" s="41" t="n"/>
       <c r="G40" s="41" t="inlineStr">
         <is>
-          <t>a. verify address comes up when moving pin b. verify address can be searched in the map</t>
+          <t>a. can view a popup to display deflection content when a category selection is made that does not create a case.</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-006</t>
+          <t>CFSUITE-SR-002</t>
         </is>
       </c>
     </row>
@@ -2599,33 +2591,38 @@
       </c>
       <c r="B41" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-021</t>
+          <t>CoM-Test-017</t>
         </is>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
-          <t>Flag Requests Being Beyond Council Boundary</t>
+          <t>Match Rquest to Existing Customer or Create New one</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>Ability to flag requests being created where location is not within Customer boundary</t>
+          <t>1. Ability to match requests to existing customers or create new ones 2. Ability to create request from the community member record which will auto link the community member to the request</t>
         </is>
       </c>
       <c r="E41" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Flag_Requests_Being_Beyond_Council_Boundary__WtO2TTq2R6uuoAmIuRPJwQ</t>
+          <t>https://scribehow.com/shared/Match_Request_to_Existing_Customer_or_Create_new_one__0wECFc9rSPONm-K6BaMfHw</t>
         </is>
       </c>
       <c r="F41" s="40" t="n"/>
       <c r="G41" s="40" t="inlineStr">
         <is>
-          <t>Warning issued to the user that the chosen address is outside of Council</t>
+          <t>a. can add customer during request b. can add an existing customer c. can goto customer request and create request, and customer is auto added to the request form</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-007</t>
+          <t>CFSUITE-SR-003</t>
+        </is>
+      </c>
+      <c r="AH41" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-003 (robot/tests/requests/CFSUITE-SR-003_create_case_from_account.robot)</t>
         </is>
       </c>
     </row>
@@ -2637,33 +2634,33 @@
       </c>
       <c r="B42" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-022</t>
+          <t>CoM-Test-018</t>
         </is>
       </c>
       <c r="C42" s="41" t="inlineStr">
         <is>
-          <t>Display Knowledge articles specific to Request Categories</t>
+          <t>Send E-mail to Request Owner when Case is Created and Ownership Changes</t>
         </is>
       </c>
       <c r="D42" s="41" t="inlineStr">
         <is>
-          <t>Ability to display dynamically tailored knowledge articles based upon selection of the request category</t>
+          <t>Ability to send an email to a request owner (internal staff) when the request is created and on change of ownership</t>
         </is>
       </c>
       <c r="E42" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Create_Request_with_Accurate_Routing__rJ1x1Mx5TiyFBWwAWlrkIg</t>
+          <t>https://scribehow.com/shared/Send_automated_emails_on_Case_status_updates__V31q4CETSb-LcCWIlJhtbA</t>
         </is>
       </c>
       <c r="F42" s="41" t="n"/>
       <c r="G42" s="41" t="inlineStr">
         <is>
-          <t>Once a category is selected knowledge section will be visible; lists all the knowledge articles corresponding to selected category.</t>
+          <t>a. when case assigned to user, user is notified by email they are the new owner b. if owner is manually updated, then user if notified they are now the owner c. all members of queues need to be notified when a new wo is assigned to that queue</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-008</t>
+          <t>CFSUITE-SR-004</t>
         </is>
       </c>
     </row>
@@ -2675,33 +2672,33 @@
       </c>
       <c r="B43" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-023</t>
+          <t>CoM-Test-019</t>
         </is>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
-          <t>Correctly Auto assign Requests Based on business rules</t>
+          <t>Find Correct Request Categories</t>
         </is>
       </c>
       <c r="D43" s="40" t="inlineStr">
         <is>
-          <t>Ability to auto-assign requests at creation to an individual or team based upon a set of business rules or criteria such as request category, reason and sub-reason</t>
+          <t>Ability to easily find correct request categories by: . Allowing popular requests (Ignore) . Tool tips . SmartSearch tags</t>
         </is>
       </c>
       <c r="E43" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Correctly_Auto_assign_Requests_Based_on_business_rules__badm2voWSkWVZUiU0SpnrA</t>
+          <t>https://scribehow.com/shared/Find_Correct_Request_Categories__sx5OFbdqQcmacGmzZAkztQ</t>
         </is>
       </c>
       <c r="F43" s="40" t="n"/>
       <c r="G43" s="40" t="inlineStr">
         <is>
-          <t>Owner of the case automatically assigned a. spot check and verify against Master Request workbook (complete 4 spot checks)</t>
+          <t>a. popular categories config is working b. tool tips can be updated c. smart search tags can be updated</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-009</t>
+          <t>CFSUITE-SR-005</t>
         </is>
       </c>
     </row>
@@ -2713,38 +2710,34 @@
       </c>
       <c r="B44" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-024</t>
+          <t>CoM-Test-020</t>
         </is>
       </c>
       <c r="C44" s="41" t="inlineStr">
         <is>
-          <t>Correctly Calculate Request Due Date</t>
+          <t>Select Request Location</t>
         </is>
       </c>
       <c r="D44" s="41" t="inlineStr">
         <is>
-          <t>Ability to auto-calculate due date of a request based on Create Date + SLA Ability to update the due date by selecting an updated SLA to complete a given request.</t>
-        </is>
-      </c>
-      <c r="E44" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Correctly_Calculate_Request_Due_Date__s9i10LcVSzeK9oDKoSZ1NA</t>
-        </is>
-      </c>
+          <t>Ability to select a request location by: . Dropping a pin using GIS map . Searching for request location</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="n"/>
       <c r="F44" s="41" t="n"/>
       <c r="G44" s="41" t="inlineStr">
         <is>
-          <t>"Due Date" follows the formula that takes into account the number of days provided by the "SLA" field, and excludes weekends and public holidays. For example, if SLA = 5, and Creation Date is 29/11/2018 then the "Due Date" should show 6/12/2018</t>
+          <t>a. verify address comes up when moving pin b. verify address can be searched in the map</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-010</t>
-        </is>
-      </c>
-      <c r="AH44" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-010 (robot/tests/requests/CFSUITE-SR-010_calculate_request_due_date.robot)</t>
+          <t>CFSUITE-SR-006</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-010_calculate_request_due_date.robot</t>
         </is>
       </c>
     </row>
@@ -2756,38 +2749,38 @@
       </c>
       <c r="B45" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-025</t>
+          <t>CoM-Test-021</t>
         </is>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
-          <t>Create Child Request</t>
+          <t>Flag Requests Being Beyond Council Boundary</t>
         </is>
       </c>
       <c r="D45" s="40" t="inlineStr">
         <is>
-          <t>Ability to create a child request against a parent request record where: . Request info is auto populated in new request . Files are optionally linked to a new request</t>
+          <t>Ability to flag requests being created where location is not within Customer boundary</t>
         </is>
       </c>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Create_Child_Request__dBs8RGAcRN-9JZytcSuuRA</t>
+          <t>https://scribehow.com/shared/Flag_Requests_Being_Beyond_Council_Boundary__WtO2TTq2R6uuoAmIuRPJwQ</t>
         </is>
       </c>
       <c r="F45" s="40" t="n"/>
       <c r="G45" s="40" t="inlineStr">
         <is>
-          <t>All required fields populated; adhoc case created Following fields will be auto-populated: - Customer Name - Location - Notification method = no notification - Case Origin = - Category "Parent Case" field populated with the case number of the original case</t>
+          <t>Warning issued to the user that the chosen address is outside of Council</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-011</t>
-        </is>
-      </c>
-      <c r="AH45" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-011 (robot/tests/requests/CFSUITE-SR-011_create_child_case.robot)</t>
+          <t>CFSUITE-SR-007</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-011_create_child_case.robot</t>
         </is>
       </c>
     </row>
@@ -2799,34 +2792,38 @@
       </c>
       <c r="B46" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-026</t>
+          <t>CoM-Test-022</t>
         </is>
       </c>
       <c r="C46" s="41" t="inlineStr">
         <is>
-          <t>Correct Incorrect Request Category</t>
+          <t>Display Knowledge articles specific to Request Categories</t>
         </is>
       </c>
       <c r="D46" s="41" t="inlineStr">
         <is>
-          <t>Ability to correct the request category when an incorrect request category has been selected Check a CFSuite Misc Record is created to log the change</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="n"/>
+          <t>Ability to display dynamically tailored knowledge articles based upon selection of the request category</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Create_Request_with_Accurate_Routing__rJ1x1Mx5TiyFBWwAWlrkIg</t>
+        </is>
+      </c>
       <c r="F46" s="41" t="n"/>
       <c r="G46" s="41" t="inlineStr">
         <is>
-          <t>a. verify that parent case is closed with reason incorrect category b. verify correct emails are going out to customer Or if set up to correct the case Category rather than duplicate (Controlled by Custom Setting) a. Verify that the request category is changed b. Verify that emails are going to the customer</t>
+          <t>Once a category is selected knowledge section will be visible; lists all the knowledge articles corresponding to selected category.</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-012</t>
-        </is>
-      </c>
-      <c r="AH46" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-012 (robot/tests/requests/CFSUITE-SR-012_recategorise_case.robot)</t>
+          <t>CFSUITE-SR-008</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-012_recategorise_case.robot</t>
         </is>
       </c>
     </row>
@@ -2838,34 +2835,38 @@
       </c>
       <c r="B47" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-027</t>
+          <t>CoM-Test-023</t>
         </is>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>Flag Request as an Emergency</t>
+          <t>Correctly Auto assign Requests Based on business rules</t>
         </is>
       </c>
       <c r="D47" s="40" t="inlineStr">
         <is>
-          <t>Ability to dynamically flag a request as a hazard</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="n"/>
+          <t>Ability to auto-assign requests at creation to an individual or team based upon a set of business rules or criteria such as request category, reason and sub-reason</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Correctly_Auto_assign_Requests_Based_on_business_rules__badm2voWSkWVZUiU0SpnrA</t>
+        </is>
+      </c>
       <c r="F47" s="40" t="n"/>
       <c r="G47" s="40" t="inlineStr">
         <is>
-          <t>a. verify emergency status can be updated b. verify when updated on case</t>
+          <t>Owner of the case automatically assigned a. spot check and verify against Master Request workbook (complete 4 spot checks)</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-013</t>
-        </is>
-      </c>
-      <c r="AH47" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-013 (robot/tests/requests/CFSUITE-SR-013_flag_request_as_emergency.robot)</t>
+          <t>CFSUITE-SR-009</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-013_flag_request_as_emergency.robot</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2878,17 @@
       </c>
       <c r="B48" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-028</t>
+          <t>CoM-Test-024</t>
         </is>
       </c>
       <c r="C48" s="41" t="inlineStr">
         <is>
-          <t>Due Date is visible and calculated correctly</t>
+          <t>Correctly Calculate Request Due Date</t>
         </is>
       </c>
       <c r="D48" s="41" t="inlineStr">
         <is>
-          <t>Ability to view SLA and due date in the highlights panel Ability to correctly calculate due date using the formulae due date = created date + SLA</t>
+          <t>Ability to auto-calculate due date of a request based on Create Date + SLA Ability to update the due date by selecting an updated SLA to complete a given request.</t>
         </is>
       </c>
       <c r="E48" s="41" t="inlineStr">
@@ -2898,17 +2899,17 @@
       <c r="F48" s="41" t="n"/>
       <c r="G48" s="41" t="inlineStr">
         <is>
-          <t>Verify for all case categories.</t>
+          <t>"Due Date" follows the formula that takes into account the number of days provided by the "SLA" field, and excludes weekends and public holidays. For example, if SLA = 5, and Creation Date is 29/11/2018 then the "Due Date" should show 6/12/2018</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-014</t>
+          <t>CFSUITE-SR-010</t>
         </is>
       </c>
       <c r="AH48" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-014 (robot/tests/requests/CFSUITE-SR-014_due_date_visible_highlights.robot)</t>
+          <t>CFSUITE-SR-010 (robot/tests/requests/CFSUITE-SR-010_calculate_request_due_date.robot)</t>
         </is>
       </c>
     </row>
@@ -2920,38 +2921,38 @@
       </c>
       <c r="B49" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-029</t>
+          <t>CoM-Test-025</t>
         </is>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>Update SLA and Due Date when Assigned</t>
+          <t>Create Child Request</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
         <is>
-          <t>Ability for due date to be dynamically updated with the request is assigned.</t>
+          <t>Ability to create a child request against a parent request record where: . Request info is auto populated in new request . Files are optionally linked to a new request</t>
         </is>
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Correctly_Calculate_Request_Due_Date__s9i10LcVSzeK9oDKoSZ1NA</t>
+          <t>https://scribehow.com/shared/Create_Child_Request__dBs8RGAcRN-9JZytcSuuRA</t>
         </is>
       </c>
       <c r="F49" s="40" t="n"/>
       <c r="G49" s="40" t="inlineStr">
         <is>
-          <t>Verify for all case categories.</t>
+          <t>All required fields populated; adhoc case created Following fields will be auto-populated: - Customer Name - Location - Notification method = no notification - Case Origin = - Category "Parent Case" field populated with the case number of the original case</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-015</t>
+          <t>CFSUITE-SR-011</t>
         </is>
       </c>
       <c r="AH49" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-015 (robot/tests/requests/CFSUITE-SR-015_update_sla_and_due_date_when_assigned.robot)</t>
+          <t>CFSUITE-SR-011 (robot/tests/requests/CFSUITE-SR-011_create_child_case.robot)</t>
         </is>
       </c>
     </row>
@@ -2963,25 +2964,34 @@
       </c>
       <c r="B50" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-030</t>
+          <t>CoM-Test-026</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>Route requests to specific queues through work zones</t>
+          <t>Correct Incorrect Request Category</t>
         </is>
       </c>
       <c r="D50" s="41" t="inlineStr">
         <is>
-          <t>Ability to route requests to specific queues through work zones. Note: work zones provided by GIS layers</t>
+          <t>Ability to correct the request category when an incorrect request category has been selected Check a CFSuite Misc Record is created to log the change</t>
         </is>
       </c>
       <c r="E50" s="41" t="n"/>
       <c r="F50" s="41" t="n"/>
-      <c r="G50" s="41" t="n"/>
+      <c r="G50" s="41" t="inlineStr">
+        <is>
+          <t>a. verify that parent case is closed with reason incorrect category b. verify correct emails are going out to customer Or if set up to correct the case Category rather than duplicate (Controlled by Custom Setting) a. Verify that the request category is changed b. Verify that emails are going to the customer</t>
+        </is>
+      </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-016</t>
+          <t>CFSUITE-SR-012</t>
+        </is>
+      </c>
+      <c r="AH50" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-012 (robot/tests/requests/CFSUITE-SR-012_recategorise_case.robot)</t>
         </is>
       </c>
     </row>
@@ -2993,33 +3003,34 @@
       </c>
       <c r="B51" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-031</t>
+          <t>CoM-Test-027</t>
         </is>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
-          <t>Validation to ensure customer can received automated notifications</t>
+          <t>Flag Request as an Emergency</t>
         </is>
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>1. Ability to enforce that customer record has an email or mobile number if their pref comms is email or Mobile respectively 2. Ability for enfore that customer record has an email or mobile if the case they are creating has the notification selected as email or text and preferred notification method respectively</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Validation_to_ensure_customer_can_receive_automated_notification__xmxmOO8YTa2W8HoI7YvBow</t>
-        </is>
-      </c>
+          <t>Ability to dynamically flag a request as a hazard</t>
+        </is>
+      </c>
+      <c r="E51" s="40" t="n"/>
       <c r="F51" s="40" t="n"/>
       <c r="G51" s="40" t="inlineStr">
         <is>
-          <t>1. Warning message is displayed on customer when preferred notification method is email or mobile and they don’t have that information on customer record 1. Warning message is displayed on case when notification method is email or mobile and they don’t have that information on customer record</t>
+          <t>a. verify emergency status can be updated b. verify when updated on case</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-017</t>
+          <t>CFSUITE-SR-013</t>
+        </is>
+      </c>
+      <c r="AH51" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-013 (robot/tests/requests/CFSUITE-SR-013_flag_request_as_emergency.robot)</t>
         </is>
       </c>
     </row>
@@ -3031,25 +3042,38 @@
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-032</t>
+          <t>CoM-Test-028</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>Customer receives autoreply with Case Reference number</t>
+          <t>Due Date is visible and calculated correctly</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
         <is>
-          <t>Ability for a customer to receive an automatic notification which includes a reference number</t>
-        </is>
-      </c>
-      <c r="E52" s="41" t="n"/>
+          <t>Ability to view SLA and due date in the highlights panel Ability to correctly calculate due date using the formulae due date = created date + SLA</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Correctly_Calculate_Request_Due_Date__s9i10LcVSzeK9oDKoSZ1NA</t>
+        </is>
+      </c>
       <c r="F52" s="41" t="n"/>
-      <c r="G52" s="41" t="n"/>
+      <c r="G52" s="41" t="inlineStr">
+        <is>
+          <t>Verify for all case categories.</t>
+        </is>
+      </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-018</t>
+          <t>CFSUITE-SR-014</t>
+        </is>
+      </c>
+      <c r="AH52" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-014 (robot/tests/requests/CFSUITE-SR-014_due_date_visible_highlights.robot)</t>
         </is>
       </c>
     </row>
@@ -3061,29 +3085,38 @@
       </c>
       <c r="B53" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-033</t>
+          <t>CoM-Test-029</t>
         </is>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>Select Email / SMS as preferred Comms</t>
+          <t>Update SLA and Due Date when Assigned</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
         <is>
-          <t>Ability to select SMS &amp; Email as preferred comms</t>
+          <t>Ability for due date to be dynamically updated with the request is assigned.</t>
         </is>
       </c>
       <c r="E53" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Validation_to_ensure_customer_can_receive_automated_notification__xmxmOO8YTa2W8HoI7YvBow</t>
+          <t>https://scribehow.com/shared/Correctly_Calculate_Request_Due_Date__s9i10LcVSzeK9oDKoSZ1NA</t>
         </is>
       </c>
       <c r="F53" s="40" t="n"/>
-      <c r="G53" s="40" t="n"/>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>Verify for all case categories.</t>
+        </is>
+      </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-019</t>
+          <t>CFSUITE-SR-015</t>
+        </is>
+      </c>
+      <c r="AH53" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-015 (robot/tests/requests/CFSUITE-SR-015_update_sla_and_due_date_when_assigned.robot)</t>
         </is>
       </c>
     </row>
@@ -3095,17 +3128,17 @@
       </c>
       <c r="B54" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-034</t>
+          <t>CoM-Test-030</t>
         </is>
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Create Request with [Inspection Required] as initial status</t>
+          <t>Route requests to specific queues through work zones</t>
         </is>
       </c>
       <c r="D54" s="41" t="inlineStr">
         <is>
-          <t>Abilibity to set initial status for Fast Response request to be Inspection Required Ability to send customer notification when Fast Response request is created based on the selected preferred comms, either Email or SMS</t>
+          <t>Ability to route requests to specific queues through work zones. Note: work zones provided by GIS layers</t>
         </is>
       </c>
       <c r="E54" s="41" t="n"/>
@@ -3113,7 +3146,7 @@
       <c r="G54" s="41" t="n"/>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-020</t>
+          <t>CFSUITE-SR-016</t>
         </is>
       </c>
     </row>
@@ -3125,25 +3158,33 @@
       </c>
       <c r="B55" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-035</t>
+          <t>CoM-Test-031</t>
         </is>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Create Request with Accurate Routing</t>
+          <t>Validation to ensure customer can received automated notifications</t>
         </is>
       </c>
       <c r="D55" s="40" t="inlineStr">
         <is>
-          <t>Ability to create request type categories with reasons and subreason to support accurate routing Ability to add a file on first case creation page Ability to view the team and team members the request will be routed to Ability to add a Question to the request flow</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="n"/>
+          <t>1. Ability to enforce that customer record has an email or mobile number if their pref comms is email or Mobile respectively 2. Ability for enfore that customer record has an email or mobile if the case they are creating has the notification selected as email or text and preferred notification method respectively</t>
+        </is>
+      </c>
+      <c r="E55" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Validation_to_ensure_customer_can_receive_automated_notification__xmxmOO8YTa2W8HoI7YvBow</t>
+        </is>
+      </c>
       <c r="F55" s="40" t="n"/>
-      <c r="G55" s="40" t="n"/>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>1. Warning message is displayed on customer when preferred notification method is email or mobile and they don’t have that information on customer record 1. Warning message is displayed on case when notification method is email or mobile and they don’t have that information on customer record</t>
+        </is>
+      </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-021</t>
+          <t>CFSUITE-SR-017</t>
         </is>
       </c>
     </row>
@@ -3155,17 +3196,17 @@
       </c>
       <c r="B56" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-036</t>
+          <t>CoM-Test-032</t>
         </is>
       </c>
       <c r="C56" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Match Asset Rquest to Existing Customer or Create New one</t>
+          <t>Customer receives autoreply with Case Reference number</t>
         </is>
       </c>
       <c r="D56" s="41" t="inlineStr">
         <is>
-          <t>1. Ability to match requests to existing customers or create new ones 2. Ability to create request from the community member record which will auto link the community member to the request</t>
+          <t>Ability for a customer to receive an automatic notification which includes a reference number</t>
         </is>
       </c>
       <c r="E56" s="41" t="n"/>
@@ -3173,7 +3214,7 @@
       <c r="G56" s="41" t="n"/>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-022</t>
+          <t>CFSUITE-SR-018</t>
         </is>
       </c>
     </row>
@@ -3185,25 +3226,29 @@
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-037</t>
+          <t>CoM-Test-033</t>
         </is>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Do NOT Send E-mail to Request Owner when Case is Created and Ownership Changes</t>
+          <t>Select Email / SMS as preferred Comms</t>
         </is>
       </c>
       <c r="D57" s="40" t="inlineStr">
         <is>
-          <t>Ability to block the sending of email to a request owner (internal staff) when a confirm request is created and on change of ownership</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="n"/>
+          <t>Ability to select SMS &amp; Email as preferred comms</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Validation_to_ensure_customer_can_receive_automated_notification__xmxmOO8YTa2W8HoI7YvBow</t>
+        </is>
+      </c>
       <c r="F57" s="40" t="n"/>
       <c r="G57" s="40" t="n"/>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-023</t>
+          <t>CFSUITE-SR-019</t>
         </is>
       </c>
     </row>
@@ -3215,17 +3260,17 @@
       </c>
       <c r="B58" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-038</t>
+          <t>CoM-Test-034</t>
         </is>
       </c>
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Correctly Auto assign Requests Based on business rules</t>
+          <t>[Confirm] Create Request with [Inspection Required] as initial status</t>
         </is>
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>Ability to auto-assign requests at creation to an individual based upon a set of business rules or criteria such as request category, reason and sub-reason</t>
+          <t>Abilibity to set initial status for Fast Response request to be Inspection Required Ability to send customer notification when Fast Response request is created based on the selected preferred comms, either Email or SMS</t>
         </is>
       </c>
       <c r="E58" s="41" t="n"/>
@@ -3233,7 +3278,7 @@
       <c r="G58" s="41" t="n"/>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-024</t>
+          <t>CFSUITE-SR-020</t>
         </is>
       </c>
     </row>
@@ -3245,17 +3290,17 @@
       </c>
       <c r="B59" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-039</t>
+          <t>CoM-Test-035</t>
         </is>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Correctly Calculate Request Due Date</t>
+          <t>[Confirm] Create Request with Accurate Routing</t>
         </is>
       </c>
       <c r="D59" s="40" t="inlineStr">
         <is>
-          <t>Ability to auto-calculate due date of a request based on Create Date + SLA Ability to update the due date by selecting an updated SLA to complete a given request.</t>
+          <t>Ability to create request type categories with reasons and subreason to support accurate routing Ability to add a file on first case creation page Ability to view the team and team members the request will be routed to Ability to add a Question to the request flow</t>
         </is>
       </c>
       <c r="E59" s="40" t="n"/>
@@ -3263,7 +3308,7 @@
       <c r="G59" s="40" t="n"/>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-025</t>
+          <t>CFSUITE-SR-021</t>
         </is>
       </c>
     </row>
@@ -3275,17 +3320,17 @@
       </c>
       <c r="B60" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-040</t>
+          <t>CoM-Test-036</t>
         </is>
       </c>
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Create Child Request</t>
+          <t>[Confirm] Match Asset Rquest to Existing Customer or Create New one</t>
         </is>
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>Ability to create a child request against a parent request record where: . Request info is auto populated in new request . Files are optionally linked to a new request</t>
+          <t>1. Ability to match requests to existing customers or create new ones 2. Ability to create request from the community member record which will auto link the community member to the request</t>
         </is>
       </c>
       <c r="E60" s="41" t="n"/>
@@ -3293,7 +3338,7 @@
       <c r="G60" s="41" t="n"/>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-026</t>
+          <t>CFSUITE-SR-022</t>
         </is>
       </c>
     </row>
@@ -3305,17 +3350,17 @@
       </c>
       <c r="B61" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-041</t>
+          <t>CoM-Test-037</t>
         </is>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Can NOT Correct Incorrect Request Category</t>
+          <t>[Confirm] Do NOT Send E-mail to Request Owner when Case is Created and Ownership Changes</t>
         </is>
       </c>
       <c r="D61" s="40" t="inlineStr">
         <is>
-          <t>Ability to stop the correction of the request category within Salesforce.</t>
+          <t>Ability to block the sending of email to a request owner (internal staff) when a confirm request is created and on change of ownership</t>
         </is>
       </c>
       <c r="E61" s="40" t="n"/>
@@ -3323,7 +3368,7 @@
       <c r="G61" s="40" t="n"/>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-027</t>
+          <t>CFSUITE-SR-023</t>
         </is>
       </c>
     </row>
@@ -3335,17 +3380,17 @@
       </c>
       <c r="B62" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-042</t>
+          <t>CoM-Test-038</t>
         </is>
       </c>
       <c r="C62" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Print Case</t>
+          <t>[Confirm] Correctly Auto assign Requests Based on business rules</t>
         </is>
       </c>
       <c r="D62" s="41" t="inlineStr">
         <is>
-          <t>Ability to Print Case from Salesforce</t>
+          <t>Ability to auto-assign requests at creation to an individual based upon a set of business rules or criteria such as request category, reason and sub-reason</t>
         </is>
       </c>
       <c r="E62" s="41" t="n"/>
@@ -3353,7 +3398,7 @@
       <c r="G62" s="41" t="n"/>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-028</t>
+          <t>CFSUITE-SR-024</t>
         </is>
       </c>
     </row>
@@ -3365,17 +3410,17 @@
       </c>
       <c r="B63" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-043</t>
+          <t>CoM-Test-039</t>
         </is>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Due Date is showing and correct</t>
+          <t>[Confirm] Correctly Calculate Request Due Date</t>
         </is>
       </c>
       <c r="D63" s="40" t="inlineStr">
         <is>
-          <t>Ability to view SLA and due date in the highlights panel Ability to correctly calculate due date using the formulae due date = created date + SLA</t>
+          <t>Ability to auto-calculate due date of a request based on Create Date + SLA Ability to update the due date by selecting an updated SLA to complete a given request.</t>
         </is>
       </c>
       <c r="E63" s="40" t="n"/>
@@ -3383,7 +3428,7 @@
       <c r="G63" s="40" t="n"/>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-029</t>
+          <t>CFSUITE-SR-025</t>
         </is>
       </c>
     </row>
@@ -3395,17 +3440,17 @@
       </c>
       <c r="B64" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-044</t>
+          <t>CoM-Test-040</t>
         </is>
       </c>
       <c r="C64" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Assigned Due Date</t>
+          <t>[Confirm] Create Child Request</t>
         </is>
       </c>
       <c r="D64" s="41" t="inlineStr">
         <is>
-          <t>Ability for due date to be dynamically updated with the request is assigned.</t>
+          <t>Ability to create a child request against a parent request record where: . Request info is auto populated in new request . Files are optionally linked to a new request</t>
         </is>
       </c>
       <c r="E64" s="41" t="n"/>
@@ -3413,7 +3458,7 @@
       <c r="G64" s="41" t="n"/>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-030</t>
+          <t>CFSUITE-SR-026</t>
         </is>
       </c>
     </row>
@@ -3425,17 +3470,17 @@
       </c>
       <c r="B65" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-045</t>
+          <t>CoM-Test-041</t>
         </is>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Customer receives autoreply with Case Reference number</t>
+          <t>[Confirm] Can NOT Correct Incorrect Request Category</t>
         </is>
       </c>
       <c r="D65" s="40" t="inlineStr">
         <is>
-          <t>Ability for a customer to receive an automatic notification which includes a reference number</t>
+          <t>Ability to stop the correction of the request category within Salesforce.</t>
         </is>
       </c>
       <c r="E65" s="40" t="n"/>
@@ -3443,7 +3488,7 @@
       <c r="G65" s="40" t="n"/>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-031</t>
+          <t>CFSUITE-SR-027</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3500,17 @@
       </c>
       <c r="B66" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-046</t>
+          <t>CoM-Test-042</t>
         </is>
       </c>
       <c r="C66" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Select Email / SMS as preferred Comms</t>
+          <t>[Confirm] Print Case</t>
         </is>
       </c>
       <c r="D66" s="41" t="inlineStr">
         <is>
-          <t>Ability to select SMS &amp; Email as preferred comms</t>
+          <t>Ability to Print Case from Salesforce</t>
         </is>
       </c>
       <c r="E66" s="41" t="n"/>
@@ -3473,7 +3518,7 @@
       <c r="G66" s="41" t="n"/>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-032</t>
+          <t>CFSUITE-SR-028</t>
         </is>
       </c>
     </row>
@@ -3485,29 +3530,25 @@
       </c>
       <c r="B67" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-047</t>
+          <t>CoM-Test-043</t>
         </is>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
-          <t>View audit log of Restricted Pages</t>
+          <t>[Confirm] Due Date is showing and correct</t>
         </is>
       </c>
       <c r="D67" s="40" t="inlineStr">
         <is>
-          <t>Ability to view an audit log of pageviews of restricted requests</t>
-        </is>
-      </c>
-      <c r="E67" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/View_audit_logs_of_Restricted_Pages__jD8g0tf0RWqmaGT0-3GKow</t>
-        </is>
-      </c>
+          <t>Ability to view SLA and due date in the highlights panel Ability to correctly calculate due date using the formulae due date = created date + SLA</t>
+        </is>
+      </c>
+      <c r="E67" s="40" t="n"/>
       <c r="F67" s="40" t="n"/>
       <c r="G67" s="40" t="n"/>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-033</t>
+          <t>CFSUITE-SR-029</t>
         </is>
       </c>
     </row>
@@ -3519,34 +3560,30 @@
       </c>
       <c r="B68" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-048</t>
+          <t>CoM-Test-044</t>
         </is>
       </c>
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>Update Request Status to Assigned when case is assigned to User</t>
+          <t>[Confirm] Assigned Due Date</t>
         </is>
       </c>
       <c r="D68" s="41" t="inlineStr">
         <is>
-          <t>Ability to update request status to assigned when a case is assigned to a user</t>
-        </is>
-      </c>
-      <c r="E68" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Update_Request_Status_to_Assigened_when_Case_is_assigned_to_User__Gvh8p6oxQkWI1egOJg7sEg</t>
-        </is>
-      </c>
+          <t>Ability for due date to be dynamically updated with the request is assigned.</t>
+        </is>
+      </c>
+      <c r="E68" s="41" t="n"/>
       <c r="F68" s="41" t="n"/>
       <c r="G68" s="41" t="n"/>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-034</t>
-        </is>
-      </c>
-      <c r="AH68" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-034 (robot/tests/requests/CFSUITE-SR-034_assign_case.robot)</t>
+          <t>CFSUITE-SR-030</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-034_assign_case.robot</t>
         </is>
       </c>
     </row>
@@ -3558,34 +3595,30 @@
       </c>
       <c r="B69" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-049</t>
+          <t>CoM-Test-045</t>
         </is>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
-          <t>Link Customers to a Request as Interested Parties</t>
+          <t>[Confirm] Customer receives autoreply with Case Reference number</t>
         </is>
       </c>
       <c r="D69" s="40" t="inlineStr">
         <is>
-          <t>Ability to link multiple customers to an open request through interested parties</t>
-        </is>
-      </c>
-      <c r="E69" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Link_Customers_to_a_Request_as_Interested_Parties__MClfeKEjTnSvPz4hBkuUgA</t>
-        </is>
-      </c>
+          <t>Ability for a customer to receive an automatic notification which includes a reference number</t>
+        </is>
+      </c>
+      <c r="E69" s="40" t="n"/>
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="40" t="n"/>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-035</t>
-        </is>
-      </c>
-      <c r="AH69" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-035 (robot/tests/requests/CFSUITE-SR-035_link_interested_parties.robot)</t>
+          <t>CFSUITE-SR-031</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-035_link_interested_parties.robot</t>
         </is>
       </c>
     </row>
@@ -3597,34 +3630,30 @@
       </c>
       <c r="B70" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-050</t>
+          <t>CoM-Test-046</t>
         </is>
       </c>
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>Provide Reason for Changes on Due Date</t>
+          <t>[Confirm] Select Email / SMS as preferred Comms</t>
         </is>
       </c>
       <c r="D70" s="41" t="inlineStr">
         <is>
-          <t>Ability to enforce narrative or reason for changes to the due date field</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Provide_Reason_for_Changes_on_Due_Date__ZRr7zzROQ3ul8PhAD365cA</t>
-        </is>
-      </c>
+          <t>Ability to select SMS &amp; Email as preferred comms</t>
+        </is>
+      </c>
+      <c r="E70" s="41" t="n"/>
       <c r="F70" s="41" t="n"/>
       <c r="G70" s="41" t="n"/>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-036</t>
-        </is>
-      </c>
-      <c r="AH70" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-036 (robot/tests/requests/CFSUITE-SR-036_provide_reason_for_due_date_change.robot)</t>
+          <t>CFSUITE-SR-032</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-036_provide_reason_for_due_date_change.robot</t>
         </is>
       </c>
     </row>
@@ -3636,33 +3665,29 @@
       </c>
       <c r="B71" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-051</t>
+          <t>CoM-Test-047</t>
         </is>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
-          <t>Email Notification when Due Date is not met</t>
+          <t>View audit log of Restricted Pages</t>
         </is>
       </c>
       <c r="D71" s="40" t="inlineStr">
         <is>
-          <t>Ability to provide escalation emails when SLA (due date) is not met including: a. Notification to owner 1 day prior b. Notification to owner 1 minute after due date c. Notification to esculation group 1 day after d. Notification to esculation group 2 days after e. Notification to esculation group 3 days after + create a task and assign to contact center queue to follow up.</t>
+          <t>Ability to view an audit log of pageviews of restricted requests</t>
         </is>
       </c>
       <c r="E71" s="40" t="inlineStr">
         <is>
-          <t>1. Create a request 2 days AA SLA and signup to a Queue that the request is allocated 2. Wait over 7 working days to check all the correct SLA reminders are received. 3. Create and Assign to the testers AO user that is linked to testers email. (use category with a Low Perform Works SLA to ensure it moves to perform works. (say 5 days) 4. Wait 10 days to ensure all the SLA reminders are received and eventually a task is created on the Contact Center Task Queue.</t>
+          <t>https://scribehow.com/shared/View_audit_logs_of_Restricted_Pages__jD8g0tf0RWqmaGT0-3GKow</t>
         </is>
       </c>
       <c r="F71" s="40" t="n"/>
-      <c r="G71" s="40" t="inlineStr">
-        <is>
-          <t>Check that email are generated as per business requirements Check that task is created on the Contact Center Agent Task Queue</t>
-        </is>
-      </c>
+      <c r="G71" s="40" t="n"/>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-037</t>
+          <t>CFSUITE-SR-033</t>
         </is>
       </c>
     </row>
@@ -3674,38 +3699,34 @@
       </c>
       <c r="B72" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-052</t>
+          <t>CoM-Test-048</t>
         </is>
       </c>
       <c r="C72" s="41" t="inlineStr">
         <is>
-          <t>Track Request History</t>
+          <t>Update Request Status to Assigned when case is assigned to User</t>
         </is>
       </c>
       <c r="D72" s="41" t="inlineStr">
         <is>
-          <t>Ability to track history on specific request fields (Salesforce has a limit of max 20 fields) for: a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request</t>
+          <t>Ability to update request status to assigned when a case is assigned to a user</t>
         </is>
       </c>
       <c r="E72" s="41" t="inlineStr">
         <is>
-          <t>1. Update fields on each of the following records, then check the field history related list to ensure that the updates have been recorded. a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request [Video: https://drive.google.com/file/d/1uGOR_UMUkMuue8JNC8p5mn746Cg8fnj3/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/Update_Request_Status_to_Assigened_when_Case_is_assigned_to_User__Gvh8p6oxQkWI1egOJg7sEg</t>
         </is>
       </c>
       <c r="F72" s="41" t="n"/>
-      <c r="G72" s="41" t="inlineStr">
-        <is>
-          <t>Key fields (up to 20) are tracked on listed records</t>
-        </is>
-      </c>
+      <c r="G72" s="41" t="n"/>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-038</t>
+          <t>CFSUITE-SR-034</t>
         </is>
       </c>
       <c r="AH72" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-038 (robot/tests/requests/CFSUITE-SR-038_track_request_history.robot)</t>
+          <t>CFSUITE-SR-034 (robot/tests/requests/CFSUITE-SR-034_assign_case.robot)</t>
         </is>
       </c>
     </row>
@@ -3717,34 +3738,34 @@
       </c>
       <c r="B73" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-053</t>
+          <t>CoM-Test-049</t>
         </is>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
-          <t>Provide Reason for Closing Requests</t>
+          <t>Link Customers to a Request as Interested Parties</t>
         </is>
       </c>
       <c r="D73" s="40" t="inlineStr">
         <is>
-          <t>Ability to add and enforce a reason code when a request is closed</t>
+          <t>Ability to link multiple customers to an open request through interested parties</t>
         </is>
       </c>
       <c r="E73" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Provide_Reason_for_Closing_Requests__VuPiIqmkSoqfWUf2Y4vYJw</t>
+          <t>https://scribehow.com/shared/Link_Customers_to_a_Request_as_Interested_Parties__MClfeKEjTnSvPz4hBkuUgA</t>
         </is>
       </c>
       <c r="F73" s="40" t="n"/>
       <c r="G73" s="40" t="n"/>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-039</t>
+          <t>CFSUITE-SR-035</t>
         </is>
       </c>
       <c r="AH73" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-039 (robot/tests/requests/CFSUITE-SR-039_provide_reason_for_closing.robot)</t>
+          <t>CFSUITE-SR-035 (robot/tests/requests/CFSUITE-SR-035_link_interested_parties.robot)</t>
         </is>
       </c>
     </row>
@@ -3756,34 +3777,34 @@
       </c>
       <c r="B74" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-054</t>
+          <t>CoM-Test-050</t>
         </is>
       </c>
       <c r="C74" s="41" t="inlineStr">
         <is>
-          <t>Provide comment ,when reason code is "Other"</t>
+          <t>Provide Reason for Changes on Due Date</t>
         </is>
       </c>
       <c r="D74" s="41" t="inlineStr">
         <is>
-          <t>Ability to add ‘Other’ reason code which enforces input of free text comment field</t>
+          <t>Ability to enforce narrative or reason for changes to the due date field</t>
         </is>
       </c>
       <c r="E74" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Provide_Reason_for_Closing_Requests__VuPiIqmkSoqfWUf2Y4vYJw</t>
+          <t>https://scribehow.com/shared/Provide_Reason_for_Changes_on_Due_Date__ZRr7zzROQ3ul8PhAD365cA</t>
         </is>
       </c>
       <c r="F74" s="41" t="n"/>
       <c r="G74" s="41" t="n"/>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-040</t>
+          <t>CFSUITE-SR-036</t>
         </is>
       </c>
       <c r="AH74" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-040 (robot/tests/requests/CFSUITE-SR-040_other_close_reason_requires_comment.robot)</t>
+          <t>CFSUITE-SR-036 (robot/tests/requests/CFSUITE-SR-036_provide_reason_for_due_date_change.robot)</t>
         </is>
       </c>
     </row>
@@ -3795,29 +3816,33 @@
       </c>
       <c r="B75" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-055</t>
+          <t>CoM-Test-051</t>
         </is>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
-          <t>Update Case via webrowser backend workbench</t>
+          <t>Email Notification when Due Date is not met</t>
         </is>
       </c>
       <c r="D75" s="40" t="inlineStr">
         <is>
-          <t>Ability to update and close Cases in the field via mobile app or web app</t>
+          <t>Ability to provide escalation emails when SLA (due date) is not met including: a. Notification to owner 1 day prior b. Notification to owner 1 minute after due date c. Notification to esculation group 1 day after d. Notification to esculation group 2 days after e. Notification to esculation group 3 days after + create a task and assign to contact center queue to follow up.</t>
         </is>
       </c>
       <c r="E75" s="40" t="inlineStr">
         <is>
-          <t>1. Login to Salesforce as an AO or CCA 2. Navigate to case record and update the status 3. Login to Salesforce mobile app 4. Navigate to case record and update the status</t>
+          <t>1. Create a request 2 days AA SLA and signup to a Queue that the request is allocated 2. Wait over 7 working days to check all the correct SLA reminders are received. 3. Create and Assign to the testers AO user that is linked to testers email. (use category with a Low Perform Works SLA to ensure it moves to perform works. (say 5 days) 4. Wait 10 days to ensure all the SLA reminders are received and eventually a task is created on the Contact Center Task Queue.</t>
         </is>
       </c>
       <c r="F75" s="40" t="n"/>
-      <c r="G75" s="40" t="n"/>
+      <c r="G75" s="40" t="inlineStr">
+        <is>
+          <t>Check that email are generated as per business requirements Check that task is created on the Contact Center Agent Task Queue</t>
+        </is>
+      </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-041</t>
+          <t>CFSUITE-SR-037</t>
         </is>
       </c>
     </row>
@@ -3829,29 +3854,38 @@
       </c>
       <c r="B76" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-056</t>
+          <t>CoM-Test-052</t>
         </is>
       </c>
       <c r="C76" s="41" t="inlineStr">
         <is>
-          <t>Duplicate requests within close proximity</t>
+          <t>Track Request History</t>
         </is>
       </c>
       <c r="D76" s="41" t="inlineStr">
         <is>
-          <t>Ability to identify a duplicate request if submitted within close proximity with the same request category</t>
+          <t>Ability to track history on specific request fields (Salesforce has a limit of max 20 fields) for: a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request</t>
         </is>
       </c>
       <c r="E76" s="41" t="inlineStr">
         <is>
-          <t>1. login to Salesforce 2. Select create new request 3. Select a category and move pin to a location near another request. 4. Keep moving pin until its close enough to other pins that they turn orange. 5 Create the request at the point near duplicates.</t>
+          <t>1. Update fields on each of the following records, then check the field history related list to ensure that the updates have been recorded. a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request [Video: https://drive.google.com/file/d/1uGOR_UMUkMuue8JNC8p5mn746Cg8fnj3/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F76" s="41" t="n"/>
-      <c r="G76" s="41" t="n"/>
+      <c r="G76" s="41" t="inlineStr">
+        <is>
+          <t>Key fields (up to 20) are tracked on listed records</t>
+        </is>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-042</t>
+          <t>CFSUITE-SR-038</t>
+        </is>
+      </c>
+      <c r="AH76" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-038 (robot/tests/requests/CFSUITE-SR-038_track_request_history.robot)</t>
         </is>
       </c>
     </row>
@@ -3863,34 +3897,34 @@
       </c>
       <c r="B77" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-057</t>
+          <t>CoM-Test-053</t>
         </is>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
-          <t>Flag request record with an alert warning</t>
+          <t>Provide Reason for Closing Requests</t>
         </is>
       </c>
       <c r="D77" s="40" t="inlineStr">
         <is>
-          <t>Ability to flag a request as containing an alert if there is an alert on the linked record including: Customer Property Asset (Nice to have)</t>
+          <t>Ability to add and enforce a reason code when a request is closed</t>
         </is>
       </c>
       <c r="E77" s="40" t="inlineStr">
         <is>
-          <t>follow through these steps from step 7</t>
+          <t>https://scribehow.com/shared/Provide_Reason_for_Closing_Requests__VuPiIqmkSoqfWUf2Y4vYJw</t>
         </is>
       </c>
       <c r="F77" s="40" t="n"/>
       <c r="G77" s="40" t="n"/>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-043</t>
+          <t>CFSUITE-SR-039</t>
         </is>
       </c>
       <c r="AH77" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-043 (robot/tests/requests/CFSUITE-SR-043_flag_request_with_alert_warning.robot)</t>
+          <t>CFSUITE-SR-039 (robot/tests/requests/CFSUITE-SR-039_provide_reason_for_closing.robot)</t>
         </is>
       </c>
     </row>
@@ -3902,29 +3936,34 @@
       </c>
       <c r="B78" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-058</t>
+          <t>CoM-Test-054</t>
         </is>
       </c>
       <c r="C78" s="41" t="inlineStr">
         <is>
-          <t>Action Officer Map to manage requests</t>
+          <t>Provide comment ,when reason code is "Other"</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>Ability to view a set of requests on a map, filterable by: Category (multi-select) Status Create date Due date</t>
+          <t>Ability to add ‘Other’ reason code which enforces input of free text comment field</t>
         </is>
       </c>
       <c r="E78" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/How_to_Create_AO_Map_Filter__lXKlnoIWQm66FUeTnFWbmw</t>
+          <t>https://scribehow.com/shared/Provide_Reason_for_Closing_Requests__VuPiIqmkSoqfWUf2Y4vYJw</t>
         </is>
       </c>
       <c r="F78" s="41" t="n"/>
       <c r="G78" s="41" t="n"/>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-044</t>
+          <t>CFSUITE-SR-040</t>
+        </is>
+      </c>
+      <c r="AH78" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-040 (robot/tests/requests/CFSUITE-SR-040_other_close_reason_requires_comment.robot)</t>
         </is>
       </c>
     </row>
@@ -3936,34 +3975,34 @@
       </c>
       <c r="B79" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-059</t>
+          <t>CoM-Test-055</t>
         </is>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
-          <t>Provide Comment ,when Closing Requests</t>
+          <t>Update Case via webrowser backend workbench</t>
         </is>
       </c>
       <c r="D79" s="40" t="inlineStr">
         <is>
-          <t>Ability to enforce a comment when closing a request</t>
+          <t>Ability to update and close Cases in the field via mobile app or web app</t>
         </is>
       </c>
       <c r="E79" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Ability_to_enforce_a_comment_when_closing_a_request__AEJ8K0vCQem0soCCwY-e2A</t>
+          <t>1. Login to Salesforce as an AO or CCA 2. Navigate to case record and update the status 3. Login to Salesforce mobile app 4. Navigate to case record and update the status</t>
         </is>
       </c>
       <c r="F79" s="40" t="n"/>
       <c r="G79" s="40" t="n"/>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-045</t>
-        </is>
-      </c>
-      <c r="AH79" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-045 (robot/tests/requests/CFSUITE-SR-045_provide_comment_when_closing.robot)</t>
+          <t>CFSUITE-SR-041</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-045_provide_comment_when_closing.robot</t>
         </is>
       </c>
     </row>
@@ -3975,30 +4014,34 @@
       </c>
       <c r="B80" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-060</t>
+          <t>CoM-Test-056</t>
         </is>
       </c>
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>Create Tasks on Case</t>
+          <t>Duplicate requests within close proximity</t>
         </is>
       </c>
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>Ability to include a Action / task for a given request Ability to view task in activity list</t>
-        </is>
-      </c>
-      <c r="E80" s="41" t="n"/>
+          <t>Ability to identify a duplicate request if submitted within close proximity with the same request category</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>1. login to Salesforce 2. Select create new request 3. Select a category and move pin to a location near another request. 4. Keep moving pin until its close enough to other pins that they turn orange. 5 Create the request at the point near duplicates.</t>
+        </is>
+      </c>
       <c r="F80" s="41" t="n"/>
       <c r="G80" s="41" t="n"/>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-046</t>
-        </is>
-      </c>
-      <c r="AH80" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-046 (robot/tests/requests/CFSUITE-SR-046_create_tasks_on_case.robot)</t>
+          <t>CFSUITE-SR-042</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-046_create_tasks_on_case.robot</t>
         </is>
       </c>
     </row>
@@ -4010,38 +4053,34 @@
       </c>
       <c r="B81" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-061</t>
+          <t>CoM-Test-057</t>
         </is>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
-          <t>Custom on hold and close reasons when selecting other</t>
+          <t>Flag request record with an alert warning</t>
         </is>
       </c>
       <c r="D81" s="40" t="inlineStr">
         <is>
-          <t>Ability for council staff to enter additional close &amp;/OR additional on hold reasons which are viewable to the customer</t>
+          <t>Ability to flag a request as containing an alert if there is an alert on the linked record including: Customer Property Asset (Nice to have)</t>
         </is>
       </c>
       <c r="E81" s="40" t="inlineStr">
         <is>
-          <t>1. navigate to an open request case 2. select on hold, with reason = other 3. enter some custom text in the other on hold reason field. 4 repeate above process for closing a case.</t>
+          <t>follow through these steps from step 7</t>
         </is>
       </c>
       <c r="F81" s="40" t="n"/>
-      <c r="G81" s="40" t="inlineStr">
-        <is>
-          <t>1. Ability to include a custom on hold reason and custom close reason. 2. Ability to view this custom text in the on hold and close email or sms</t>
-        </is>
-      </c>
+      <c r="G81" s="40" t="n"/>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-047</t>
+          <t>CFSUITE-SR-043</t>
         </is>
       </c>
       <c r="AH81" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-047 (robot/tests/requests/CFSUITE-SR-047_custom_on_hold_and_close_reasons.robot)</t>
+          <t>CFSUITE-SR-043 (robot/tests/requests/CFSUITE-SR-043_flag_request_with_alert_warning.robot)</t>
         </is>
       </c>
     </row>
@@ -4053,25 +4092,29 @@
       </c>
       <c r="B82" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-062</t>
+          <t>CoM-Test-058</t>
         </is>
       </c>
       <c r="C82" s="41" t="inlineStr">
         <is>
-          <t>Preferred comms updates on Assigned, on hold and closed</t>
+          <t>Action Officer Map to manage requests</t>
         </is>
       </c>
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>Ability to send a notification via SMS or email when a. Request Assigned b. Request put On Hold c. Request is Closed</t>
-        </is>
-      </c>
-      <c r="E82" s="41" t="n"/>
+          <t>Ability to view a set of requests on a map, filterable by: Category (multi-select) Status Create date Due date</t>
+        </is>
+      </c>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/How_to_Create_AO_Map_Filter__lXKlnoIWQm66FUeTnFWbmw</t>
+        </is>
+      </c>
       <c r="F82" s="41" t="n"/>
       <c r="G82" s="41" t="n"/>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-048</t>
+          <t>CFSUITE-SR-044</t>
         </is>
       </c>
     </row>
@@ -4083,25 +4126,34 @@
       </c>
       <c r="B83" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-063</t>
+          <t>CoM-Test-059</t>
         </is>
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
-          <t>Post Request Surveys</t>
+          <t>Provide Comment ,when Closing Requests</t>
         </is>
       </c>
       <c r="D83" s="40" t="inlineStr">
         <is>
-          <t>Ability to send a survey request by email if pref comms is email Ability to send a survey request by mobile (requires URL shortner) if pref comms is SMS Ability to track survey responses against request categories and community member records</t>
-        </is>
-      </c>
-      <c r="E83" s="40" t="n"/>
+          <t>Ability to enforce a comment when closing a request</t>
+        </is>
+      </c>
+      <c r="E83" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Ability_to_enforce_a_comment_when_closing_a_request__AEJ8K0vCQem0soCCwY-e2A</t>
+        </is>
+      </c>
       <c r="F83" s="40" t="n"/>
       <c r="G83" s="40" t="n"/>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-049</t>
+          <t>CFSUITE-SR-045</t>
+        </is>
+      </c>
+      <c r="AH83" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-045 (robot/tests/requests/CFSUITE-SR-045_provide_comment_when_closing.robot)</t>
         </is>
       </c>
     </row>
@@ -4113,30 +4165,30 @@
       </c>
       <c r="B84" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-064</t>
+          <t>CoM-Test-060</t>
         </is>
       </c>
       <c r="C84" s="41" t="inlineStr">
         <is>
-          <t>PATH / Guidenace for Success</t>
-        </is>
-      </c>
-      <c r="D84" s="41" t="n"/>
-      <c r="E84" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Path_and_Guidance_For_Success__pOZii7DmSG6RS9J2uIpNyA</t>
-        </is>
-      </c>
+          <t>Create Tasks on Case</t>
+        </is>
+      </c>
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>Ability to include a Action / task for a given request Ability to view task in activity list</t>
+        </is>
+      </c>
+      <c r="E84" s="41" t="n"/>
       <c r="F84" s="41" t="n"/>
       <c r="G84" s="41" t="n"/>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-050</t>
+          <t>CFSUITE-SR-046</t>
         </is>
       </c>
       <c r="AH84" s="47" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-050 (robot/tests/requests/CFSUITE-SR-050_path_and_guidance_for_success.robot)</t>
+          <t>CFSUITE-SR-046 (robot/tests/requests/CFSUITE-SR-046_create_tasks_on_case.robot)</t>
         </is>
       </c>
     </row>
@@ -4148,25 +4200,38 @@
       </c>
       <c r="B85" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-065</t>
+          <t>CoM-Test-061</t>
         </is>
       </c>
       <c r="C85" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] View audit log of Restricted Pages</t>
+          <t>Custom on hold and close reasons when selecting other</t>
         </is>
       </c>
       <c r="D85" s="40" t="inlineStr">
         <is>
-          <t>Ability to view an audit log of pageviews of restricted requests</t>
-        </is>
-      </c>
-      <c r="E85" s="40" t="n"/>
+          <t>Ability for council staff to enter additional close &amp;/OR additional on hold reasons which are viewable to the customer</t>
+        </is>
+      </c>
+      <c r="E85" s="40" t="inlineStr">
+        <is>
+          <t>1. navigate to an open request case 2. select on hold, with reason = other 3. enter some custom text in the other on hold reason field. 4 repeate above process for closing a case.</t>
+        </is>
+      </c>
       <c r="F85" s="40" t="n"/>
-      <c r="G85" s="40" t="n"/>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>1. Ability to include a custom on hold reason and custom close reason. 2. Ability to view this custom text in the on hold and close email or sms</t>
+        </is>
+      </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-051</t>
+          <t>CFSUITE-SR-047</t>
+        </is>
+      </c>
+      <c r="AH85" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-047 (robot/tests/requests/CFSUITE-SR-047_custom_on_hold_and_close_reasons.robot)</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4243,17 @@
       </c>
       <c r="B86" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-067</t>
+          <t>CoM-Test-062</t>
         </is>
       </c>
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Validation rule to block AO's and CCAs from updating the status of a confirm case in Salesforce</t>
+          <t>Preferred comms updates on Assigned, on hold and closed</t>
         </is>
       </c>
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>Ability to stop AO's and CCAs from updating status of confirm synced requests in Salesforce</t>
+          <t>Ability to send a notification via SMS or email when a. Request Assigned b. Request put On Hold c. Request is Closed</t>
         </is>
       </c>
       <c r="E86" s="41" t="n"/>
@@ -4196,7 +4261,7 @@
       <c r="G86" s="41" t="n"/>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-052</t>
+          <t>CFSUITE-SR-048</t>
         </is>
       </c>
     </row>
@@ -4208,17 +4273,17 @@
       </c>
       <c r="B87" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-068</t>
+          <t>CoM-Test-063</t>
         </is>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Track Request History</t>
+          <t>Post Request Surveys</t>
         </is>
       </c>
       <c r="D87" s="40" t="inlineStr">
         <is>
-          <t>Ability to track history on specific request fields (Salesforce has a limit of max 20 fields) for: a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request</t>
+          <t>Ability to send a survey request by email if pref comms is email Ability to send a survey request by mobile (requires URL shortner) if pref comms is SMS Ability to track survey responses against request categories and community member records</t>
         </is>
       </c>
       <c r="E87" s="40" t="n"/>
@@ -4226,7 +4291,7 @@
       <c r="G87" s="40" t="n"/>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-053</t>
+          <t>CFSUITE-SR-049</t>
         </is>
       </c>
     </row>
@@ -4238,25 +4303,30 @@
       </c>
       <c r="B88" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-069</t>
+          <t>CoM-Test-064</t>
         </is>
       </c>
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Duplicate requests within close proximity</t>
-        </is>
-      </c>
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>Ability to identify a duplicate request if submitted within close proximity with the same request category</t>
-        </is>
-      </c>
-      <c r="E88" s="41" t="n"/>
+          <t>PATH / Guidenace for Success</t>
+        </is>
+      </c>
+      <c r="D88" s="41" t="n"/>
+      <c r="E88" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Path_and_Guidance_For_Success__pOZii7DmSG6RS9J2uIpNyA</t>
+        </is>
+      </c>
       <c r="F88" s="41" t="n"/>
       <c r="G88" s="41" t="n"/>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-054</t>
+          <t>CFSUITE-SR-050</t>
+        </is>
+      </c>
+      <c r="AH88" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-050 (robot/tests/requests/CFSUITE-SR-050_path_and_guidance_for_success.robot)</t>
         </is>
       </c>
     </row>
@@ -4268,17 +4338,17 @@
       </c>
       <c r="B89" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-070</t>
+          <t>CoM-Test-065</t>
         </is>
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Flag request it is linked to a record with an alert</t>
+          <t>[Confirm] View audit log of Restricted Pages</t>
         </is>
       </c>
       <c r="D89" s="40" t="inlineStr">
         <is>
-          <t>Ability to flag a request as containing an alert if there is an alert on the linked record including: Customer Property Asset (Nice to have)</t>
+          <t>Ability to view an audit log of pageviews of restricted requests</t>
         </is>
       </c>
       <c r="E89" s="40" t="n"/>
@@ -4286,7 +4356,7 @@
       <c r="G89" s="40" t="n"/>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-055</t>
+          <t>CFSUITE-SR-051</t>
         </is>
       </c>
     </row>
@@ -4298,17 +4368,17 @@
       </c>
       <c r="B90" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-071</t>
+          <t>CoM-Test-067</t>
         </is>
       </c>
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Action Officer Map to manage requests</t>
+          <t>[Confirm] Validation rule to block AO's and CCAs from updating the status of a confirm case in Salesforce</t>
         </is>
       </c>
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>Ability to view a set of requests on a map, filterable by: Category (multi-select) Status Create date Due date</t>
+          <t>Ability to stop AO's and CCAs from updating status of confirm synced requests in Salesforce</t>
         </is>
       </c>
       <c r="E90" s="41" t="n"/>
@@ -4316,7 +4386,7 @@
       <c r="G90" s="41" t="n"/>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-056</t>
+          <t>CFSUITE-SR-052</t>
         </is>
       </c>
     </row>
@@ -4328,17 +4398,17 @@
       </c>
       <c r="B91" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-072</t>
+          <t>CoM-Test-068</t>
         </is>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Preferred comms updates on Assigned, and closed</t>
+          <t>[Confirm] Track Request History</t>
         </is>
       </c>
       <c r="D91" s="40" t="inlineStr">
         <is>
-          <t>Ability to send a notification via SMS or email when a. Request Assigned b. Request is Closed</t>
+          <t>Ability to track history on specific request fields (Salesforce has a limit of max 20 fields) for: a. Case, b. Community Member, c. Business Account, d. Busiesss Contact, e. CFSuite Flow e. CFSuite Community Request</t>
         </is>
       </c>
       <c r="E91" s="40" t="n"/>
@@ -4346,7 +4416,7 @@
       <c r="G91" s="40" t="n"/>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-057</t>
+          <t>CFSUITE-SR-053</t>
         </is>
       </c>
     </row>
@@ -4358,17 +4428,17 @@
       </c>
       <c r="B92" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-073</t>
+          <t>CoM-Test-069</t>
         </is>
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>[Confirm] Post Request Surveys</t>
+          <t>[Confirm] Duplicate requests within close proximity</t>
         </is>
       </c>
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>Ability to send a survey request by email if pref comms is email Ability to send a survey request by mobile (requires URL shortner) if pref comms is SMS Ability to track survey responses against request categories and community member records</t>
+          <t>Ability to identify a duplicate request if submitted within close proximity with the same request category</t>
         </is>
       </c>
       <c r="E92" s="41" t="n"/>
@@ -4376,7 +4446,7 @@
       <c r="G92" s="41" t="n"/>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-058</t>
+          <t>CFSUITE-SR-054</t>
         </is>
       </c>
     </row>
@@ -4388,21 +4458,25 @@
       </c>
       <c r="B93" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-074</t>
+          <t>CoM-Test-070</t>
         </is>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] PATH / Guidenace for Success</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="n"/>
+          <t>[Confirm] Flag request it is linked to a record with an alert</t>
+        </is>
+      </c>
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>Ability to flag a request as containing an alert if there is an alert on the linked record including: Customer Property Asset (Nice to have)</t>
+        </is>
+      </c>
       <c r="E93" s="40" t="n"/>
       <c r="F93" s="40" t="n"/>
       <c r="G93" s="40" t="n"/>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-059</t>
+          <t>CFSUITE-SR-055</t>
         </is>
       </c>
     </row>
@@ -4414,17 +4488,17 @@
       </c>
       <c r="B94" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-075</t>
+          <t>CoM-Test-071</t>
         </is>
       </c>
       <c r="C94" s="41" t="inlineStr">
         <is>
-          <t>[Confirm Fast Response] Preferred comms updates on Closed</t>
+          <t>[Confirm] Action Officer Map to manage requests</t>
         </is>
       </c>
       <c r="D94" s="41" t="inlineStr">
         <is>
-          <t>Ability to send a notification via SMS or email when a. Fast Response Request is Closed</t>
+          <t>Ability to view a set of requests on a map, filterable by: Category (multi-select) Status Create date Due date</t>
         </is>
       </c>
       <c r="E94" s="41" t="n"/>
@@ -4432,7 +4506,7 @@
       <c r="G94" s="41" t="n"/>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-060</t>
+          <t>CFSUITE-SR-056</t>
         </is>
       </c>
     </row>
@@ -4444,17 +4518,17 @@
       </c>
       <c r="B95" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-076</t>
+          <t>CoM-Test-072</t>
         </is>
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
-          <t>[Confirm] Integration with Confirm</t>
+          <t>[Confirm] Preferred comms updates on Assigned, and closed</t>
         </is>
       </c>
       <c r="D95" s="40" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Ability to send a notification via SMS or email when a. Request Assigned b. Request is Closed</t>
         </is>
       </c>
       <c r="E95" s="40" t="n"/>
@@ -4462,7 +4536,7 @@
       <c r="G95" s="40" t="n"/>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-061</t>
+          <t>CFSUITE-SR-057</t>
         </is>
       </c>
     </row>
@@ -4474,33 +4548,25 @@
       </c>
       <c r="B96" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-080</t>
+          <t>CoM-Test-073</t>
         </is>
       </c>
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>Configure identified requests categories to be restricted</t>
+          <t>[Confirm] Post Request Surveys</t>
         </is>
       </c>
       <c r="D96" s="41" t="inlineStr">
         <is>
-          <t>Ability to make selected request types confidential automatically</t>
-        </is>
-      </c>
-      <c r="E96" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Ability_to_make_selected_request_types_confidential_automatically__zvWZ4uPNSteDBWZ-b-ftKA</t>
-        </is>
-      </c>
+          <t>Ability to send a survey request by email if pref comms is email Ability to send a survey request by mobile (requires URL shortner) if pref comms is SMS Ability to track survey responses against request categories and community member records</t>
+        </is>
+      </c>
+      <c r="E96" s="41" t="n"/>
       <c r="F96" s="41" t="n"/>
-      <c r="G96" s="41" t="inlineStr">
-        <is>
-          <t>1. Cases configured to be restricted (e.g. public health requests) are visiblity only to selected groups provided access to these records.</t>
-        </is>
-      </c>
+      <c r="G96" s="41" t="n"/>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-062</t>
+          <t>CFSUITE-SR-058</t>
         </is>
       </c>
     </row>
@@ -4512,33 +4578,21 @@
       </c>
       <c r="B97" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-081</t>
+          <t>CoM-Test-074</t>
         </is>
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
-          <t>Log views of restricted request categories</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="inlineStr">
-        <is>
-          <t>Ability to view a log of all users who have viewed a restricted request</t>
-        </is>
-      </c>
-      <c r="E97" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Ability_to_view_log_of_restricted_categories___V9cK4W9SsWL3PG1_HGnIg</t>
-        </is>
-      </c>
+          <t>[Confirm] PATH / Guidenace for Success</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="n"/>
+      <c r="E97" s="40" t="n"/>
       <c r="F97" s="40" t="n"/>
-      <c r="G97" s="40" t="inlineStr">
-        <is>
-          <t>1. Log available to view users who have viewed restricted category records</t>
-        </is>
-      </c>
+      <c r="G97" s="40" t="n"/>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-063</t>
+          <t>CFSUITE-SR-059</t>
         </is>
       </c>
     </row>
@@ -4550,17 +4604,17 @@
       </c>
       <c r="B98" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-084</t>
+          <t>CoM-Test-075</t>
         </is>
       </c>
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>Create feedback and complaint requests</t>
+          <t>[Confirm Fast Response] Preferred comms updates on Closed</t>
         </is>
       </c>
       <c r="D98" s="41" t="inlineStr">
         <is>
-          <t>Ability to create a complaint request with sub type options including: a. Comment b. Complaint c. Compliment</t>
+          <t>Ability to send a notification via SMS or email when a. Fast Response Request is Closed</t>
         </is>
       </c>
       <c r="E98" s="41" t="n"/>
@@ -4568,7 +4622,7 @@
       <c r="G98" s="41" t="n"/>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-064</t>
+          <t>CFSUITE-SR-060</t>
         </is>
       </c>
     </row>
@@ -4580,29 +4634,25 @@
       </c>
       <c r="B99" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-085</t>
+          <t>CoM-Test-076</t>
         </is>
       </c>
       <c r="C99" s="40" t="inlineStr">
         <is>
-          <t>Create complaint as child against a request</t>
+          <t>[Confirm] Integration with Confirm</t>
         </is>
       </c>
       <c r="D99" s="40" t="inlineStr">
         <is>
-          <t>Ability to link the complaint against an existing request</t>
-        </is>
-      </c>
-      <c r="E99" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Create_complaint_as_child_against_a_request__iiVVhGe8ReubUOHzh2VNuA</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="n"/>
       <c r="F99" s="40" t="n"/>
       <c r="G99" s="40" t="n"/>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-065</t>
+          <t>CFSUITE-SR-061</t>
         </is>
       </c>
     </row>
@@ -4614,25 +4664,33 @@
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-086</t>
+          <t>CoM-Test-080</t>
         </is>
       </c>
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>Complaint SLA and esculation</t>
+          <t>Configure identified requests categories to be restricted</t>
         </is>
       </c>
       <c r="D100" s="41" t="inlineStr">
         <is>
-          <t>Ability to define and trigger escalation rules when SLA (due date) is not met for a complaint</t>
-        </is>
-      </c>
-      <c r="E100" s="41" t="n"/>
+          <t>Ability to make selected request types confidential automatically</t>
+        </is>
+      </c>
+      <c r="E100" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Ability_to_make_selected_request_types_confidential_automatically__zvWZ4uPNSteDBWZ-b-ftKA</t>
+        </is>
+      </c>
       <c r="F100" s="41" t="n"/>
-      <c r="G100" s="41" t="n"/>
+      <c r="G100" s="41" t="inlineStr">
+        <is>
+          <t>1. Cases configured to be restricted (e.g. public health requests) are visiblity only to selected groups provided access to these records.</t>
+        </is>
+      </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-066</t>
+          <t>CFSUITE-SR-062</t>
         </is>
       </c>
     </row>
@@ -4644,30 +4702,38 @@
       </c>
       <c r="B101" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-087</t>
+          <t>CoM-Test-081</t>
         </is>
       </c>
       <c r="C101" s="40" t="inlineStr">
         <is>
-          <t>Enforce a comment when closing a complaint</t>
+          <t>Log views of restricted request categories</t>
         </is>
       </c>
       <c r="D101" s="40" t="inlineStr">
         <is>
-          <t>Ability to add and enforce reason codes when the request is closed</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="n"/>
+          <t>Ability to view a log of all users who have viewed a restricted request</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Ability_to_view_log_of_restricted_categories___V9cK4W9SsWL3PG1_HGnIg</t>
+        </is>
+      </c>
       <c r="F101" s="40" t="n"/>
-      <c r="G101" s="40" t="n"/>
+      <c r="G101" s="40" t="inlineStr">
+        <is>
+          <t>1. Log available to view users who have viewed restricted category records</t>
+        </is>
+      </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-067</t>
-        </is>
-      </c>
-      <c r="AH101" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-067 (robot/tests/requests/CFSUITE-SR-067_enforce_comment_closing_complaint.robot)</t>
+          <t>CFSUITE-SR-063</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-067_enforce_comment_closing_complaint.robot</t>
         </is>
       </c>
     </row>
@@ -4679,17 +4745,17 @@
       </c>
       <c r="B102" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-088</t>
+          <t>CoM-Test-084</t>
         </is>
       </c>
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>Restricted Access to complaints</t>
+          <t>Create feedback and complaint requests</t>
         </is>
       </c>
       <c r="D102" s="41" t="inlineStr">
         <is>
-          <t>Ability to restict visibility of complaint case to a complaint group</t>
+          <t>Ability to create a complaint request with sub type options including: a. Comment b. Complaint c. Compliment</t>
         </is>
       </c>
       <c r="E102" s="41" t="n"/>
@@ -4697,7 +4763,7 @@
       <c r="G102" s="41" t="n"/>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-068</t>
+          <t>CFSUITE-SR-064</t>
         </is>
       </c>
     </row>
@@ -4709,25 +4775,29 @@
       </c>
       <c r="B103" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-089</t>
+          <t>CoM-Test-085</t>
         </is>
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
-          <t>Create a PDF of Request when case is closed</t>
+          <t>Create complaint as child against a request</t>
         </is>
       </c>
       <c r="D103" s="40" t="inlineStr">
         <is>
-          <t>Ability to PDF Case meta data of request</t>
-        </is>
-      </c>
-      <c r="E103" s="40" t="n"/>
+          <t>Ability to link the complaint against an existing request</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Create_complaint_as_child_against_a_request__iiVVhGe8ReubUOHzh2VNuA</t>
+        </is>
+      </c>
       <c r="F103" s="40" t="n"/>
       <c r="G103" s="40" t="n"/>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-069</t>
+          <t>CFSUITE-SR-065</t>
         </is>
       </c>
     </row>
@@ -4739,17 +4809,17 @@
       </c>
       <c r="B104" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-090</t>
+          <t>CoM-Test-086</t>
         </is>
       </c>
       <c r="C104" s="41" t="inlineStr">
         <is>
-          <t>Copy attached files to EDMRS (SharePoint) when case is closed</t>
+          <t>Complaint SLA and esculation</t>
         </is>
       </c>
       <c r="D104" s="41" t="inlineStr">
         <is>
-          <t>Ability to copy files attached to a request to EDRMS</t>
+          <t>Ability to define and trigger escalation rules when SLA (due date) is not met for a complaint</t>
         </is>
       </c>
       <c r="E104" s="41" t="n"/>
@@ -4757,7 +4827,7 @@
       <c r="G104" s="41" t="n"/>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-070</t>
+          <t>CFSUITE-SR-066</t>
         </is>
       </c>
     </row>
@@ -4769,17 +4839,17 @@
       </c>
       <c r="B105" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-091</t>
+          <t>CoM-Test-087</t>
         </is>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
-          <t>Create a CFSuite Archive-related list record within Salesforce when case is closed</t>
+          <t>Enforce a comment when closing a complaint</t>
         </is>
       </c>
       <c r="D105" s="40" t="inlineStr">
         <is>
-          <t>Ability to locate where files attached to a request are located within the EDRMS</t>
+          <t>Ability to add and enforce reason codes when the request is closed</t>
         </is>
       </c>
       <c r="E105" s="40" t="n"/>
@@ -4787,7 +4857,12 @@
       <c r="G105" s="40" t="n"/>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-071</t>
+          <t>CFSUITE-SR-067</t>
+        </is>
+      </c>
+      <c r="AH105" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-067 (robot/tests/requests/CFSUITE-SR-067_enforce_comment_closing_complaint.robot)</t>
         </is>
       </c>
     </row>
@@ -4799,17 +4874,17 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-092</t>
+          <t>CoM-Test-088</t>
         </is>
       </c>
       <c r="C106" s="41" t="inlineStr">
         <is>
-          <t>Create a PDF of Request when Manual Archive Button within a case is selected</t>
+          <t>Restricted Access to complaints</t>
         </is>
       </c>
       <c r="D106" s="41" t="inlineStr">
         <is>
-          <t>Ability to PDF Case meta data of request</t>
+          <t>Ability to restict visibility of complaint case to a complaint group</t>
         </is>
       </c>
       <c r="E106" s="41" t="n"/>
@@ -4817,7 +4892,7 @@
       <c r="G106" s="41" t="n"/>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-072</t>
+          <t>CFSUITE-SR-068</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4904,17 @@
       </c>
       <c r="B107" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-093</t>
+          <t>CoM-Test-089</t>
         </is>
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
-          <t>Copy attached files to EDMRS (SharePoint) when Manual Archive Button within a case is selected</t>
+          <t>Create a PDF of Request when case is closed</t>
         </is>
       </c>
       <c r="D107" s="40" t="inlineStr">
         <is>
-          <t>Ability to copy files attached to a request to EDRMS</t>
+          <t>Ability to PDF Case meta data of request</t>
         </is>
       </c>
       <c r="E107" s="40" t="n"/>
@@ -4847,7 +4922,7 @@
       <c r="G107" s="40" t="n"/>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-073</t>
+          <t>CFSUITE-SR-069</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4934,17 @@
       </c>
       <c r="B108" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-094</t>
+          <t>CoM-Test-090</t>
         </is>
       </c>
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>Create a CFSuite Archive-related list record within Salesforce when Manual Archive Button within a case is selected</t>
+          <t>Copy attached files to EDMRS (SharePoint) when case is closed</t>
         </is>
       </c>
       <c r="D108" s="41" t="inlineStr">
         <is>
-          <t>Ability to locate where files attached to a request are located within the EDRMS</t>
+          <t>Ability to copy files attached to a request to EDRMS</t>
         </is>
       </c>
       <c r="E108" s="41" t="n"/>
@@ -4877,7 +4952,7 @@
       <c r="G108" s="41" t="n"/>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-074</t>
+          <t>CFSUITE-SR-070</t>
         </is>
       </c>
     </row>
@@ -4889,29 +4964,25 @@
       </c>
       <c r="B109" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-095</t>
+          <t>CoM-Test-091</t>
         </is>
       </c>
       <c r="C109" s="40" t="inlineStr">
         <is>
-          <t>Register a user as deifferent customer</t>
+          <t>Create a CFSuite Archive-related list record within Salesforce when case is closed</t>
         </is>
       </c>
       <c r="D109" s="40" t="inlineStr">
         <is>
-          <t>Ability to register a user account as: a. Resident customer b. Business customer</t>
-        </is>
-      </c>
-      <c r="E109" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Ability_to_register_a_user_account_as-a_Resident_customer-b_Business_customer__A6FkzPmDRGCXuNT8VRMcIA [Video: https://drive.google.com/file/d/10u8FVViq33IlkJB4RQAzR4_WTqj8zXfF/view?usp=sharing]</t>
-        </is>
-      </c>
+          <t>Ability to locate where files attached to a request are located within the EDRMS</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="n"/>
       <c r="F109" s="40" t="n"/>
       <c r="G109" s="40" t="n"/>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-075</t>
+          <t>CFSUITE-SR-071</t>
         </is>
       </c>
     </row>
@@ -4923,29 +4994,25 @@
       </c>
       <c r="B110" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-096</t>
+          <t>CoM-Test-092</t>
         </is>
       </c>
       <c r="C110" s="41" t="inlineStr">
         <is>
-          <t>Link an Existing Account</t>
+          <t>Create a PDF of Request when Manual Archive Button within a case is selected</t>
         </is>
       </c>
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>Ability to link to an existing account if there is the following matching rules: “Firstname” + “Lastname” + “verified email” exact match</t>
-        </is>
-      </c>
-      <c r="E110" s="41" t="inlineStr">
-        <is>
-          <t>Covered in R.002 Scrib Doc to test 002 and 003 in one test</t>
-        </is>
-      </c>
+          <t>Ability to PDF Case meta data of request</t>
+        </is>
+      </c>
+      <c r="E110" s="41" t="n"/>
       <c r="F110" s="41" t="n"/>
       <c r="G110" s="41" t="n"/>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-076</t>
+          <t>CFSUITE-SR-072</t>
         </is>
       </c>
     </row>
@@ -4957,29 +5024,25 @@
       </c>
       <c r="B111" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-097</t>
+          <t>CoM-Test-093</t>
         </is>
       </c>
       <c r="C111" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Ability_to_log_a_request_through_a_QandA_SMARTForm_workflow_as_a__6hGhCwV4TZiaetcvu7QSJg</t>
+          <t>Copy attached files to EDMRS (SharePoint) when Manual Archive Button within a case is selected</t>
         </is>
       </c>
       <c r="D111" s="40" t="inlineStr">
         <is>
-          <t>Ability to search for a request by: a. SmartSearch tags b. Tiles with drill down</t>
-        </is>
-      </c>
-      <c r="E111" s="40" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Ability_to_search_for_a_request_by-a_SmartSearch_tags-b_Tiles_with_drill_down__tsI3z9J9Q5-z_6G_pxoCSQ</t>
-        </is>
-      </c>
+          <t>Ability to copy files attached to a request to EDRMS</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="n"/>
       <c r="F111" s="40" t="n"/>
       <c r="G111" s="40" t="n"/>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-077</t>
+          <t>CFSUITE-SR-073</t>
         </is>
       </c>
     </row>
@@ -4991,29 +5054,25 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-098</t>
+          <t>CoM-Test-094</t>
         </is>
       </c>
       <c r="C112" s="41" t="inlineStr">
         <is>
-          <t>Log a Request through Q&amp;A Workflow</t>
+          <t>Create a CFSuite Archive-related list record within Salesforce when Manual Archive Button within a case is selected</t>
         </is>
       </c>
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>Ability to log a request through a Q&amp;A SMARTForm workflow as a: a. Guest User (not logged in) b. Authenticated User (logged in)</t>
-        </is>
-      </c>
-      <c r="E112" s="41" t="inlineStr">
-        <is>
-          <t>https://scribehow.com/shared/Log_a_Request_through_QandA_Workflow_as_portal_user__rDeICb-TQbi3cFdyWhhHug [Video: https://drive.google.com/file/d/10UUDGjtEA8GhN8LPUdmXuj4oYYRJFtib/view?usp=sharing]</t>
-        </is>
-      </c>
+          <t>Ability to locate where files attached to a request are located within the EDRMS</t>
+        </is>
+      </c>
+      <c r="E112" s="41" t="n"/>
       <c r="F112" s="41" t="n"/>
       <c r="G112" s="41" t="n"/>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-078</t>
+          <t>CFSUITE-SR-074</t>
         </is>
       </c>
     </row>
@@ -5025,29 +5084,29 @@
       </c>
       <c r="B113" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-099</t>
+          <t>CoM-Test-095</t>
         </is>
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
-          <t>Restrict user to submit a request</t>
+          <t>Register a user as deifferent customer</t>
         </is>
       </c>
       <c r="D113" s="40" t="inlineStr">
         <is>
-          <t>Ability to restrict some categories to require the user to login in order to submit a request</t>
+          <t>Ability to register a user account as: a. Resident customer b. Business customer</t>
         </is>
       </c>
       <c r="E113" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Ability_to_restrict_some_categories_to_require_the_user_to_login_in_order_to_submit_a_request__y2j9wmiBROuv5iGwwi3VXQ [Video: https://drive.google.com/file/d/1aHVZPNBvHePWarDRnSj1DZkdiHNVgXFV/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/Ability_to_register_a_user_account_as-a_Resident_customer-b_Business_customer__A6FkzPmDRGCXuNT8VRMcIA [Video: https://drive.google.com/file/d/10u8FVViq33IlkJB4RQAzR4_WTqj8zXfF/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F113" s="40" t="n"/>
       <c r="G113" s="40" t="n"/>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-079</t>
+          <t>CFSUITE-SR-075</t>
         </is>
       </c>
     </row>
@@ -5059,33 +5118,29 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-100</t>
+          <t>CoM-Test-096</t>
         </is>
       </c>
       <c r="C114" s="41" t="inlineStr">
         <is>
-          <t>Select a location on a map on community request form</t>
+          <t>Link an Existing Account</t>
         </is>
       </c>
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>Ability to select a location via: a. Selecting with a pin on the map b. Searching the location address</t>
+          <t>Ability to link to an existing account if there is the following matching rules: “Firstname” + “Lastname” + “verified email” exact match</t>
         </is>
       </c>
       <c r="E114" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Ability_to_select_a_location_via-a_Selecting_with_a_pin_on_the_map-b_Searching_the_location_address__4U0cX6BXRbqbZ95zvgoCgw [Video: https://drive.google.com/file/d/1lZMxgEpyDG0bGf_20eLjPLmGAW6igz6s/view?usp=sharing]</t>
+          <t>Covered in R.002 Scrib Doc to test 002 and 003 in one test</t>
         </is>
       </c>
       <c r="F114" s="41" t="n"/>
-      <c r="G114" s="41" t="inlineStr">
-        <is>
-          <t>a. Address displayed in the search bar that is located above the map; displayed info includes street number, street name, suburb, state and postcode</t>
-        </is>
-      </c>
+      <c r="G114" s="41" t="n"/>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-080</t>
+          <t>CFSUITE-SR-076</t>
         </is>
       </c>
     </row>
@@ -5097,38 +5152,34 @@
       </c>
       <c r="B115" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-101</t>
+          <t>CoM-Test-097</t>
         </is>
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
-          <t>Follow Request as Intrested party</t>
+          <t>https://scribehow.com/shared/Ability_to_log_a_request_through_a_QandA_SMARTForm_workflow_as_a__6hGhCwV4TZiaetcvu7QSJg</t>
         </is>
       </c>
       <c r="D115" s="40" t="inlineStr">
         <is>
-          <t>Ability to follow a request as an interested party</t>
+          <t>Ability to search for a request by: a. SmartSearch tags b. Tiles with drill down</t>
         </is>
       </c>
       <c r="E115" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Follow_Request_as_interested_Party__usdPT19eS-6vDgaibEvzVg [Video: https://drive.google.com/file/d/1e7q9ZGLIDYBG7uunzZEUMvOmIvf8TN2i/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/Ability_to_search_for_a_request_by-a_SmartSearch_tags-b_Tiles_with_drill_down__tsI3z9J9Q5-z_6G_pxoCSQ</t>
         </is>
       </c>
       <c r="F115" s="40" t="n"/>
-      <c r="G115" s="40" t="inlineStr">
-        <is>
-          <t>Green "Follow" button vanished and replaced with the following text: "You are now following: [case number]"</t>
-        </is>
-      </c>
+      <c r="G115" s="40" t="n"/>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-081</t>
-        </is>
-      </c>
-      <c r="AH115" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-081 (robot/tests/requests/CFSUITE-SR-081_community_follow_case.robot)</t>
+          <t>CFSUITE-SR-077</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-081_community_follow_case.robot</t>
         </is>
       </c>
     </row>
@@ -5140,29 +5191,29 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-102</t>
+          <t>CoM-Test-098</t>
         </is>
       </c>
       <c r="C116" s="41" t="inlineStr">
         <is>
-          <t>Flag a duplicate request on community request form</t>
+          <t>Log a Request through Q&amp;A Workflow</t>
         </is>
       </c>
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>Ability to flag a request as a duplicate</t>
-        </is>
-      </c>
-      <c r="E116" s="41" t="n"/>
+          <t>Ability to log a request through a Q&amp;A SMARTForm workflow as a: a. Guest User (not logged in) b. Authenticated User (logged in)</t>
+        </is>
+      </c>
+      <c r="E116" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Log_a_Request_through_QandA_Workflow_as_portal_user__rDeICb-TQbi3cFdyWhhHug [Video: https://drive.google.com/file/d/10UUDGjtEA8GhN8LPUdmXuj4oYYRJFtib/view?usp=sharing]</t>
+        </is>
+      </c>
       <c r="F116" s="41" t="n"/>
-      <c r="G116" s="41" t="inlineStr">
-        <is>
-          <t>Warning message provided along with the number of potential duplicated</t>
-        </is>
-      </c>
+      <c r="G116" s="41" t="n"/>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-082</t>
+          <t>CFSUITE-SR-078</t>
         </is>
       </c>
     </row>
@@ -5174,29 +5225,29 @@
       </c>
       <c r="B117" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-103</t>
+          <t>CoM-Test-099</t>
         </is>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
-          <t>view and edit personal detail as residential customer</t>
+          <t>Restrict user to submit a request</t>
         </is>
       </c>
       <c r="D117" s="40" t="inlineStr">
         <is>
-          <t>Ability for a residential customer to view and edit personal details such as: a. Name b. Email c. Phone number d. Notification settings e. Addresses</t>
+          <t>Ability to restrict some categories to require the user to login in order to submit a request</t>
         </is>
       </c>
       <c r="E117" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/View_and_Edit_Personal_detail_as_residential_customer__iwnehHTTSAOvs4GxuYtsoQ [Video: https://drive.google.com/file/d/1Gv-NxP7zs3Xd9_urBRWcSfPfSfTHfP-y/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/Ability_to_restrict_some_categories_to_require_the_user_to_login_in_order_to_submit_a_request__y2j9wmiBROuv5iGwwi3VXQ [Video: https://drive.google.com/file/d/1aHVZPNBvHePWarDRnSj1DZkdiHNVgXFV/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F117" s="40" t="n"/>
       <c r="G117" s="40" t="n"/>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-083</t>
+          <t>CFSUITE-SR-079</t>
         </is>
       </c>
     </row>
@@ -5208,29 +5259,33 @@
       </c>
       <c r="B118" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-104</t>
+          <t>CoM-Test-100</t>
         </is>
       </c>
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>view and edit personal detail as bsuiness customer</t>
+          <t>Select a location on a map on community request form</t>
         </is>
       </c>
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>Ability for a business customer to view and edit personal details such as: a. Business Name b. Email c. Phone number d. Notification settings e. Addresses</t>
+          <t>Ability to select a location via: a. Selecting with a pin on the map b. Searching the location address</t>
         </is>
       </c>
       <c r="E118" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/View_and_Edit_Personal_Details_as_Business_Customer__ZD6yV1e7SaWiuyqffTIYmQ [Video: https://drive.google.com/file/d/15z6_rQZFOVPxNreKIuGJ22olcj1Lj97y/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/Ability_to_select_a_location_via-a_Selecting_with_a_pin_on_the_map-b_Searching_the_location_address__4U0cX6BXRbqbZ95zvgoCgw [Video: https://drive.google.com/file/d/1lZMxgEpyDG0bGf_20eLjPLmGAW6igz6s/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F118" s="41" t="n"/>
-      <c r="G118" s="41" t="n"/>
+      <c r="G118" s="41" t="inlineStr">
+        <is>
+          <t>a. Address displayed in the search bar that is located above the map; displayed info includes street number, street name, suburb, state and postcode</t>
+        </is>
+      </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-084</t>
+          <t>CFSUITE-SR-080</t>
         </is>
       </c>
     </row>
@@ -5242,29 +5297,38 @@
       </c>
       <c r="B119" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-105</t>
+          <t>CoM-Test-101</t>
         </is>
       </c>
       <c r="C119" s="40" t="inlineStr">
         <is>
-          <t>Stop customer of updating address if record is NAR synced</t>
+          <t>Follow Request as Intrested party</t>
         </is>
       </c>
       <c r="D119" s="40" t="inlineStr">
         <is>
-          <t>Ability to stop NAR synced customers from updating their NAR records</t>
-        </is>
-      </c>
-      <c r="E119" s="40" t="n"/>
+          <t>Ability to follow a request as an interested party</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Follow_Request_as_interested_Party__usdPT19eS-6vDgaibEvzVg [Video: https://drive.google.com/file/d/1e7q9ZGLIDYBG7uunzZEUMvOmIvf8TN2i/view?usp=sharing]</t>
+        </is>
+      </c>
       <c r="F119" s="40" t="n"/>
       <c r="G119" s="40" t="inlineStr">
         <is>
-          <t>When Sync with NAR is "yes " you can't Edit name and Address</t>
+          <t>Green "Follow" button vanished and replaced with the following text: "You are now following: [case number]"</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-085</t>
+          <t>CFSUITE-SR-081</t>
+        </is>
+      </c>
+      <c r="AH119" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-081 (robot/tests/requests/CFSUITE-SR-081_community_follow_case.robot)</t>
         </is>
       </c>
     </row>
@@ -5276,38 +5340,34 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-106</t>
+          <t>CoM-Test-102</t>
         </is>
       </c>
       <c r="C120" s="41" t="inlineStr">
         <is>
-          <t>login to community portal</t>
+          <t>Flag a duplicate request on community request form</t>
         </is>
       </c>
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>Ability to have login features including: a. Login with user/password b. Reset password</t>
-        </is>
-      </c>
-      <c r="E120" s="41" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1wVPHtp4rRzpnJZ6A6bXVLrwJGp4410Q3/view?usp=sharing</t>
-        </is>
-      </c>
+          <t>Ability to flag a request as a duplicate</t>
+        </is>
+      </c>
+      <c r="E120" s="41" t="n"/>
       <c r="F120" s="41" t="n"/>
       <c r="G120" s="41" t="inlineStr">
         <is>
-          <t>See acceptance criteria in source EPT</t>
+          <t>Warning message provided along with the number of potential duplicated</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-086</t>
-        </is>
-      </c>
-      <c r="AH120" s="47" t="inlineStr">
-        <is>
-          <t>CFSUITE-SR-086 (robot/tests/requests/CFSUITE-SR-086_customer_portal_login.robot)</t>
+          <t>CFSUITE-SR-082</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-086_customer_portal_login.robot</t>
         </is>
       </c>
     </row>
@@ -5319,25 +5379,29 @@
       </c>
       <c r="B121" s="40" t="inlineStr">
         <is>
-          <t>CoM-Test-107</t>
+          <t>CoM-Test-103</t>
         </is>
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
-          <t>Raise request anonomously via the Request Portal</t>
-        </is>
-      </c>
-      <c r="D121" s="40" t="n"/>
+          <t>view and edit personal detail as residential customer</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="inlineStr">
+        <is>
+          <t>Ability for a residential customer to view and edit personal details such as: a. Name b. Email c. Phone number d. Notification settings e. Addresses</t>
+        </is>
+      </c>
       <c r="E121" s="40" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/Raise_Request_As_Guest_User__C1wAQZynTiOkS9xGEmJ-VQ</t>
+          <t>https://scribehow.com/shared/View_and_Edit_Personal_detail_as_residential_customer__iwnehHTTSAOvs4GxuYtsoQ [Video: https://drive.google.com/file/d/1Gv-NxP7zs3Xd9_urBRWcSfPfSfTHfP-y/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F121" s="40" t="n"/>
       <c r="G121" s="40" t="n"/>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>CFSUITE-SR-087</t>
+          <t>CFSUITE-SR-083</t>
         </is>
       </c>
     </row>
@@ -5349,104 +5413,250 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>CoM-Test-108</t>
+          <t>CoM-Test-104</t>
         </is>
       </c>
       <c r="C122" s="41" t="inlineStr">
         <is>
-          <t>community member tracking a request</t>
+          <t>view and edit personal detail as bsuiness customer</t>
         </is>
       </c>
       <c r="D122" s="41" t="inlineStr">
         <is>
-          <t>Ability to track a request by: a. Request ID as a public user b. Request list/followed request list as a logged in user</t>
+          <t>Ability for a business customer to view and edit personal details such as: a. Business Name b. Email c. Phone number d. Notification settings e. Addresses</t>
         </is>
       </c>
       <c r="E122" s="41" t="inlineStr">
         <is>
-          <t>https://scribehow.com/shared/1Ability_to_track_a_request_by_a_Request_ID_as_a_public_user_b_Request_listfollowed_request_list_as_a_logged_in_user__vq9AbtRbT2K5MCWHcEWFKA [Video: https://drive.google.com/file/d/1lZWCRLMl7RC27R2qh0EzySkCswDhT3EZ/view?usp=sharing]</t>
+          <t>https://scribehow.com/shared/View_and_Edit_Personal_Details_as_Business_Customer__ZD6yV1e7SaWiuyqffTIYmQ [Video: https://drive.google.com/file/d/15z6_rQZFOVPxNreKIuGJ22olcj1Lj97y/view?usp=sharing]</t>
         </is>
       </c>
       <c r="F122" s="41" t="n"/>
       <c r="G122" s="41" t="n"/>
       <c r="AG122" t="inlineStr">
         <is>
+          <t>CFSUITE-SR-084</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="40" t="inlineStr">
+        <is>
+          <t>Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B123" s="40" t="inlineStr">
+        <is>
+          <t>CoM-Test-105</t>
+        </is>
+      </c>
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>Stop customer of updating address if record is NAR synced</t>
+        </is>
+      </c>
+      <c r="D123" s="40" t="inlineStr">
+        <is>
+          <t>Ability to stop NAR synced customers from updating their NAR records</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="n"/>
+      <c r="F123" s="40" t="n"/>
+      <c r="G123" s="40" t="inlineStr">
+        <is>
+          <t>When Sync with NAR is "yes " you can't Edit name and Address</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-085</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>robot/tests/requests/CFSUITE-SR-089_clone_case.robot</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="84" customHeight="1">
+      <c r="A124" s="41" t="inlineStr">
+        <is>
+          <t>Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B124" s="41" t="inlineStr">
+        <is>
+          <t>CoM-Test-106</t>
+        </is>
+      </c>
+      <c r="C124" s="41" t="inlineStr">
+        <is>
+          <t>login to community portal</t>
+        </is>
+      </c>
+      <c r="D124" s="41" t="inlineStr">
+        <is>
+          <t>Ability to have login features including: a. Login with user/password b. Reset password</t>
+        </is>
+      </c>
+      <c r="E124" s="41" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1wVPHtp4rRzpnJZ6A6bXVLrwJGp4410Q3/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="F124" s="41" t="n"/>
+      <c r="G124" s="41" t="inlineStr">
+        <is>
+          <t>See acceptance criteria in source EPT</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-086</t>
+        </is>
+      </c>
+      <c r="AH124" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-086 (robot/tests/requests/CFSUITE-SR-086_customer_portal_login.robot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="72" customHeight="1">
+      <c r="A125" s="40" t="inlineStr">
+        <is>
+          <t>Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B125" s="40" t="inlineStr">
+        <is>
+          <t>CoM-Test-107</t>
+        </is>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>Raise request anonomously via the Request Portal</t>
+        </is>
+      </c>
+      <c r="D125" s="40" t="n"/>
+      <c r="E125" s="40" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/Raise_Request_As_Guest_User__C1wAQZynTiOkS9xGEmJ-VQ</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="n"/>
+      <c r="G125" s="40" t="n"/>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-087</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="84" customHeight="1">
+      <c r="A126" s="41" t="inlineStr">
+        <is>
+          <t>Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B126" s="41" t="inlineStr">
+        <is>
+          <t>CoM-Test-108</t>
+        </is>
+      </c>
+      <c r="C126" s="41" t="inlineStr">
+        <is>
+          <t>community member tracking a request</t>
+        </is>
+      </c>
+      <c r="D126" s="41" t="inlineStr">
+        <is>
+          <t>Ability to track a request by: a. Request ID as a public user b. Request list/followed request list as a logged in user</t>
+        </is>
+      </c>
+      <c r="E126" s="41" t="inlineStr">
+        <is>
+          <t>https://scribehow.com/shared/1Ability_to_track_a_request_by_a_Request_ID_as_a_public_user_b_Request_listfollowed_request_list_as_a_logged_in_user__vq9AbtRbT2K5MCWHcEWFKA [Video: https://drive.google.com/file/d/1lZWCRLMl7RC27R2qh0EzySkCswDhT3EZ/view?usp=sharing]</t>
+        </is>
+      </c>
+      <c r="F126" s="41" t="n"/>
+      <c r="G126" s="41" t="n"/>
+      <c r="AG126" t="inlineStr">
+        <is>
           <t>CFSUITE-SR-088</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Additional - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>REQ-006</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Clone Case</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>Ability to clone an existing case as a starting point for a new one. Cloned case carries category and reason fields.</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Cloned case opens with the parent's fields pre-filled and can be saved as a new case.</t>
         </is>
       </c>
-      <c r="AG123" t="inlineStr">
+      <c r="AG127" t="inlineStr">
         <is>
           <t>CFSUITE-SR-089</t>
         </is>
       </c>
-      <c r="AH123" s="47" t="inlineStr">
+      <c r="AH127" s="47" t="inlineStr">
         <is>
           <t>CFSUITE-SR-089 (robot/tests/requests/CFSUITE-SR-089_clone_case.robot)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="84" customHeight="1">
-      <c r="A124" s="42" t="inlineStr">
+    <row r="128" ht="72" customHeight="1">
+      <c r="A128" s="42" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B124" s="42" t="n"/>
-      <c r="C124" s="42" t="n"/>
-      <c r="D124" s="42" t="n"/>
-      <c r="E124" s="42" t="n"/>
-      <c r="F124" s="42" t="n"/>
-      <c r="G124" s="42" t="n"/>
-    </row>
-    <row r="125" ht="72" customHeight="1">
-      <c r="A125" s="43" t="inlineStr">
+      <c r="B128" s="42" t="n"/>
+      <c r="C128" s="42" t="n"/>
+      <c r="D128" s="42" t="n"/>
+      <c r="E128" s="42" t="n"/>
+      <c r="F128" s="42" t="n"/>
+      <c r="G128" s="42" t="n"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B125" s="43" t="inlineStr">
+      <c r="B129" s="43" t="inlineStr">
         <is>
           <t>PROP-006</t>
         </is>
       </c>
-      <c r="C125" s="43" t="inlineStr">
+      <c r="C129" s="43" t="inlineStr">
         <is>
           <t>Submit New Service Request - Map Form Type</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D129" s="43" t="inlineStr">
         <is>
           <t>Case is created with correct category, location pin, and linked to the logged-in contact</t>
         </is>
       </c>
-      <c r="E125" s="43" t="inlineStr">
+      <c r="E129" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request' or equivalent
@@ -5457,44 +5667,44 @@
 7. Verify confirmation/receipt page shown with case number</t>
         </is>
       </c>
-      <c r="F125" s="43" t="inlineStr">
+      <c r="F129" s="43" t="inlineStr">
         <is>
           <t>Category: Road Repairs and Maintenance - Pothole, Location: pin on valid street</t>
         </is>
       </c>
-      <c r="G125" s="43" t="inlineStr">
+      <c r="G129" s="43" t="inlineStr">
         <is>
           <t>Case record created with correct RecordType, cfsuite1__CFSuite_Request_Flow__c lookup populated, geolocation captured; CommunityUserInsertCaseHelperClass executes without error; case number displayed to user</t>
         </is>
       </c>
-      <c r="AG125" t="inlineStr">
+      <c r="AG129" t="inlineStr">
         <is>
           <t>CFSUITE-SR-090</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="84" customHeight="1">
-      <c r="A126" s="43" t="inlineStr">
+    <row r="130" ht="72" customHeight="1">
+      <c r="A130" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B126" s="43" t="inlineStr">
+      <c r="B130" s="43" t="inlineStr">
         <is>
           <t>PROP-007</t>
         </is>
       </c>
-      <c r="C126" s="43" t="inlineStr">
+      <c r="C130" s="43" t="inlineStr">
         <is>
           <t>Submit New Service Request - Salesforce Flow Form Type</t>
         </is>
       </c>
-      <c r="D126" s="43" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>Case is created via the configured Salesforce Flow, all flow-collected fields mapped to Case</t>
         </is>
       </c>
-      <c r="E126" s="43" t="inlineStr">
+      <c r="E130" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category with Form Type = Flow
@@ -5503,44 +5713,44 @@
 5. Verify case created with correct category and flow-mapped field values</t>
         </is>
       </c>
-      <c r="F126" s="43" t="inlineStr">
+      <c r="F130" s="43" t="inlineStr">
         <is>
           <t>Category: Animals - Dog - Barking (or any Flow-type category), flow fields as required</t>
         </is>
       </c>
-      <c r="G126" s="43" t="inlineStr">
+      <c r="G130" s="43" t="inlineStr">
         <is>
           <t>RequestSubmissionFlow Apex class executes; Case record created; cfsuite1__Animal_Description__c or appropriate description field populated; confirmation number shown</t>
         </is>
       </c>
-      <c r="AG126" t="inlineStr">
+      <c r="AG130" t="inlineStr">
         <is>
           <t>CFSUITE-SR-091</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="43" t="inlineStr">
+    <row r="131" ht="84" customHeight="1">
+      <c r="A131" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B127" s="43" t="inlineStr">
+      <c r="B131" s="43" t="inlineStr">
         <is>
           <t>PROP-008</t>
         </is>
       </c>
-      <c r="C127" s="43" t="inlineStr">
+      <c r="C131" s="43" t="inlineStr">
         <is>
           <t>Submit Service Request - Duplicate Detection</t>
         </is>
       </c>
-      <c r="D127" s="43" t="inlineStr">
+      <c r="D131" s="43" t="inlineStr">
         <is>
           <t>When a duplicate open request exists for the same location and category, a warning or duplicate flag is set</t>
         </is>
       </c>
-      <c r="E127" s="43" t="inlineStr">
+      <c r="E131" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Submit a request for 'Road Repairs - Pothole' at a specific address
@@ -5549,44 +5759,44 @@
 5. Verify the second case is flagged as a duplicate or a warning presented</t>
         </is>
       </c>
-      <c r="F127" s="43" t="inlineStr">
+      <c r="F131" s="43" t="inlineStr">
         <is>
           <t>Same category and map pin location as an existing open case</t>
         </is>
       </c>
-      <c r="G127" s="43" t="inlineStr">
+      <c r="G131" s="43" t="inlineStr">
         <is>
           <t>cfsuite1__Duplicate__c picklist on Case set to 'Yes' or 'Potential'; GuestUserRetrieveDupCaseHelperClass fires; user sees duplicate warning in UI</t>
         </is>
       </c>
-      <c r="AG127" t="inlineStr">
+      <c r="AG131" t="inlineStr">
         <is>
           <t>CFSUITE-SR-092</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="72" customHeight="1">
-      <c r="A128" s="43" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B128" s="43" t="inlineStr">
+      <c r="B132" s="43" t="inlineStr">
         <is>
           <t>PROP-009</t>
         </is>
       </c>
-      <c r="C128" s="43" t="inlineStr">
+      <c r="C132" s="43" t="inlineStr">
         <is>
           <t>Guest User Service Request Submission</t>
         </is>
       </c>
-      <c r="D128" s="43" t="inlineStr">
+      <c r="D132" s="43" t="inlineStr">
         <is>
           <t>Unauthenticated (guest) user can submit a service request; contact created or matched</t>
         </is>
       </c>
-      <c r="E128" s="43" t="inlineStr">
+      <c r="E132" s="43" t="inlineStr">
         <is>
           <t>1. Browse to community portal without logging in
 2. Select a category that allows guest submission
@@ -5595,44 +5805,44 @@
 5. Verify case is created and confirmation shown</t>
         </is>
       </c>
-      <c r="F128" s="43" t="inlineStr">
+      <c r="F132" s="43" t="inlineStr">
         <is>
           <t>guestFirstName=Guest, guestLastName=User, email=guesttest+001@test.com, address=123 Main St</t>
         </is>
       </c>
-      <c r="G128" s="43" t="inlineStr">
+      <c r="G132" s="43" t="inlineStr">
         <is>
           <t>GuestUserHelperClass and GuestUserInsertContactHelperClass execute; Case created without a linked community User; ContactId populated from matched or new Contact</t>
         </is>
       </c>
-      <c r="AG128" t="inlineStr">
+      <c r="AG132" t="inlineStr">
         <is>
           <t>CFSUITE-SR-093</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="43" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B129" s="43" t="inlineStr">
+      <c r="B133" s="43" t="inlineStr">
         <is>
           <t>PROP-010</t>
         </is>
       </c>
-      <c r="C129" s="43" t="inlineStr">
+      <c r="C133" s="43" t="inlineStr">
         <is>
           <t>File Attachment Upload on Request Submission</t>
         </is>
       </c>
-      <c r="D129" s="43" t="inlineStr">
+      <c r="D133" s="43" t="inlineStr">
         <is>
           <t>Photo/document attached to submitted case is stored and visible on case detail</t>
         </is>
       </c>
-      <c r="E129" s="43" t="inlineStr">
+      <c r="E133" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Start a new service request
@@ -5642,44 +5852,44 @@
 6. Verify the attachment is listed</t>
         </is>
       </c>
-      <c r="F129" s="43" t="inlineStr">
+      <c r="F133" s="43" t="inlineStr">
         <is>
           <t>File: test-photo.jpg (under 5MB), Category: Parks and Reserves - Vandalism</t>
         </is>
       </c>
-      <c r="G129" s="43" t="inlineStr">
+      <c r="G133" s="43" t="inlineStr">
         <is>
           <t>ContentVersion record created and linked to Case via ContentDocumentLink; CommunityUserCaseAttachmentsHelperClass executes without error; file visible in community case detail</t>
         </is>
       </c>
-      <c r="AG129" t="inlineStr">
+      <c r="AG133" t="inlineStr">
         <is>
           <t>CFSUITE-SR-094</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="72" customHeight="1">
-      <c r="A130" s="43" t="inlineStr">
+    <row r="134" ht="48" customHeight="1">
+      <c r="A134" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B130" s="43" t="inlineStr">
+      <c r="B134" s="43" t="inlineStr">
         <is>
           <t>PROP-011</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>View My Submitted Requests List</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D134" s="43" t="inlineStr">
         <is>
           <t>Logged-in user sees a list of all their previously submitted requests with status and date</t>
         </is>
       </c>
-      <c r="E130" s="43" t="inlineStr">
+      <c r="E134" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Requests' section
@@ -5687,44 +5897,44 @@
 4. Verify each row shows case number, subject, status, and creation date</t>
         </is>
       </c>
-      <c r="F130" s="43" t="inlineStr">
+      <c r="F134" s="43" t="inlineStr">
         <is>
           <t>User must have at least 2 existing case submissions</t>
         </is>
       </c>
-      <c r="G130" s="43" t="inlineStr">
+      <c r="G134" s="43" t="inlineStr">
         <is>
           <t>MyRequestRecordListPageController returns cases for the contact; list renders with case number, subject, status columns; pagination present if more than 10 records</t>
         </is>
       </c>
-      <c r="AG130" t="inlineStr">
+      <c r="AG134" t="inlineStr">
         <is>
           <t>CFSUITE-SR-095</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="84" customHeight="1">
-      <c r="A131" s="43" t="inlineStr">
+    <row r="135" ht="96" customHeight="1">
+      <c r="A135" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B131" s="43" t="inlineStr">
+      <c r="B135" s="43" t="inlineStr">
         <is>
           <t>PROP-012</t>
         </is>
       </c>
-      <c r="C131" s="43" t="inlineStr">
+      <c r="C135" s="43" t="inlineStr">
         <is>
           <t>View Case Detail from My Requests</t>
         </is>
       </c>
-      <c r="D131" s="43" t="inlineStr">
+      <c r="D135" s="43" t="inlineStr">
         <is>
           <t>User can click a case and see full detail including description, location, status, and any updates</t>
         </is>
       </c>
-      <c r="E131" s="43" t="inlineStr">
+      <c r="E135" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Requests'
@@ -5733,44 +5943,44 @@
 5. Verify any case notes/comments visible to community are shown</t>
         </is>
       </c>
-      <c r="F131" s="43" t="inlineStr">
+      <c r="F135" s="43" t="inlineStr">
         <is>
           <t>Existing case with at least one community-visible note</t>
         </is>
       </c>
-      <c r="G131" s="43" t="inlineStr">
+      <c r="G135" s="43" t="inlineStr">
         <is>
           <t>CommunityUserCaseDetailHelperClass returns full case data; ProgressIndicatorController shows current case status stage; attachments section present</t>
         </is>
       </c>
-      <c r="AG131" t="inlineStr">
+      <c r="AG135" t="inlineStr">
         <is>
           <t>CFSUITE-SR-096</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="43" t="inlineStr">
+    <row r="136" ht="72" customHeight="1">
+      <c r="A136" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B132" s="43" t="inlineStr">
+      <c r="B136" s="43" t="inlineStr">
         <is>
           <t>PROP-013</t>
         </is>
       </c>
-      <c r="C132" s="43" t="inlineStr">
+      <c r="C136" s="43" t="inlineStr">
         <is>
           <t>Follow / Unfollow a Public Request on Map</t>
         </is>
       </c>
-      <c r="D132" s="43" t="inlineStr">
+      <c r="D136" s="43" t="inlineStr">
         <is>
           <t>User can follow another user's public request and have it appear in their followed requests list</t>
         </is>
       </c>
-      <c r="E132" s="43" t="inlineStr">
+      <c r="E136" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to the community map
@@ -5781,44 +5991,44 @@
 7. Click 'Unfollow' and verify it is removed</t>
         </is>
       </c>
-      <c r="F132" s="43" t="inlineStr">
+      <c r="F136" s="43" t="inlineStr">
         <is>
           <t>Existing public case created by a different contact</t>
         </is>
       </c>
-      <c r="G132" s="43" t="inlineStr">
+      <c r="G136" s="43" t="inlineStr">
         <is>
           <t>CommunityUserFollowedCaseHelperClass creates/deletes EntitySubscription or Interested_Parties record; case appears/disappears from followed list; MyFollowedRequestController returns correct list</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr">
+      <c r="AG136" t="inlineStr">
         <is>
           <t>CFSUITE-SR-097</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="43" t="inlineStr">
+    <row r="137" ht="96" customHeight="1">
+      <c r="A137" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B133" s="43" t="inlineStr">
+      <c r="B137" s="43" t="inlineStr">
         <is>
           <t>PROP-014</t>
         </is>
       </c>
-      <c r="C133" s="43" t="inlineStr">
+      <c r="C137" s="43" t="inlineStr">
         <is>
           <t>Community Map Loads with Active Request Pins</t>
         </is>
       </c>
-      <c r="D133" s="43" t="inlineStr">
+      <c r="D137" s="43" t="inlineStr">
         <is>
           <t>Map component renders with pins for all public open cases; pins show correct category icon</t>
         </is>
       </c>
-      <c r="E133" s="43" t="inlineStr">
+      <c r="E137" s="43" t="inlineStr">
         <is>
           <t>1. Log in (or browse as guest) to community portal
 2. Navigate to the community map page
@@ -5827,44 +6037,44 @@
 5. Click a pin and verify popup shows case summary</t>
         </is>
       </c>
-      <c r="F133" s="43" t="inlineStr">
+      <c r="F137" s="43" t="inlineStr">
         <is>
           <t>Org must have at least 5 public open cases with geolocation</t>
         </is>
       </c>
-      <c r="G133" s="43" t="inlineStr">
+      <c r="G137" s="43" t="inlineStr">
         <is>
           <t>AOMapCaseQueryHelperClass returns cases with coordinates; cf_MapContentController serves map data; pins rendered with cfsuite1__Pin_Image__c icon; no JS console errors</t>
         </is>
       </c>
-      <c r="AG133" t="inlineStr">
+      <c r="AG137" t="inlineStr">
         <is>
           <t>CFSUITE-SR-098</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="43" t="inlineStr">
+    <row r="138" ht="84" customHeight="1">
+      <c r="A138" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B134" s="43" t="inlineStr">
+      <c r="B138" s="43" t="inlineStr">
         <is>
           <t>PROP-015</t>
         </is>
       </c>
-      <c r="C134" s="43" t="inlineStr">
+      <c r="C138" s="43" t="inlineStr">
         <is>
           <t>Category Filter on Community Map</t>
         </is>
       </c>
-      <c r="D134" s="43" t="inlineStr">
+      <c r="D138" s="43" t="inlineStr">
         <is>
           <t>Selecting a category filter updates the map to show only pins matching that category</t>
         </is>
       </c>
-      <c r="E134" s="43" t="inlineStr">
+      <c r="E138" s="43" t="inlineStr">
         <is>
           <t>1. Navigate to community map
 2. Note total number of pins displayed
@@ -5873,44 +6083,44 @@
 5. Clear the filter and verify all pins return</t>
         </is>
       </c>
-      <c r="F134" s="43" t="inlineStr">
+      <c r="F138" s="43" t="inlineStr">
         <is>
           <t>Org has cases in multiple categories with geolocation set</t>
         </is>
       </c>
-      <c r="G134" s="43" t="inlineStr">
+      <c r="G138" s="43" t="inlineStr">
         <is>
           <t>Map re-queries with category filter; pin count changes to match filtered set; clearing filter restores full pin set</t>
         </is>
       </c>
-      <c r="AG134" t="inlineStr">
+      <c r="AG138" t="inlineStr">
         <is>
           <t>CFSUITE-SR-099</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="96" customHeight="1">
-      <c r="A135" s="43" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B135" s="43" t="inlineStr">
+      <c r="B139" s="43" t="inlineStr">
         <is>
           <t>PROP-016</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
+      <c r="C139" s="43" t="inlineStr">
         <is>
           <t>Address Search on Community Map</t>
         </is>
       </c>
-      <c r="D135" s="43" t="inlineStr">
+      <c r="D139" s="43" t="inlineStr">
         <is>
           <t>Searching for an address pans the map to that location</t>
         </is>
       </c>
-      <c r="E135" s="43" t="inlineStr">
+      <c r="E139" s="43" t="inlineStr">
         <is>
           <t>1. Navigate to community map
 2. Enter a valid suburb or street address in the search bar
@@ -5918,44 +6128,44 @@
 4. Verify map centres on the searched address</t>
         </is>
       </c>
-      <c r="F135" s="43" t="inlineStr">
+      <c r="F139" s="43" t="inlineStr">
         <is>
           <t>searchAddress=1 Main Street [configured council suburb]</t>
         </is>
       </c>
-      <c r="G135" s="43" t="inlineStr">
+      <c r="G139" s="43" t="inlineStr">
         <is>
           <t>Address search component calls geocoding (ArcGIS or Google Maps API); map viewport pans and zooms to matched location; nearby pins visible</t>
         </is>
       </c>
-      <c r="AG135" t="inlineStr">
+      <c r="AG139" t="inlineStr">
         <is>
           <t>CFSUITE-SR-100</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="72" customHeight="1">
-      <c r="A136" s="43" t="inlineStr">
+    <row r="140" ht="72" customHeight="1">
+      <c r="A140" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B136" s="43" t="inlineStr">
+      <c r="B140" s="43" t="inlineStr">
         <is>
           <t>PROP-027</t>
         </is>
       </c>
-      <c r="C136" s="43" t="inlineStr">
+      <c r="C140" s="43" t="inlineStr">
         <is>
           <t>Create New Case (Internal Staff)</t>
         </is>
       </c>
-      <c r="D136" s="43" t="inlineStr">
+      <c r="D140" s="43" t="inlineStr">
         <is>
           <t>Internal staff user creates a new case record with all required fields; case number auto-generated</t>
         </is>
       </c>
-      <c r="E136" s="43" t="inlineStr">
+      <c r="E140" s="43" t="inlineStr">
         <is>
           <t>1. Log in as internal staff user
 2. Navigate to Cases and click 'New'
@@ -5966,44 +6176,44 @@
 7. Verify case is created with auto-generated case number</t>
         </is>
       </c>
-      <c r="F136" s="43" t="inlineStr">
+      <c r="F140" s="43" t="inlineStr">
         <is>
           <t>Subject=Test pothole report, Category=Road Repairs and Maintenance - Pothole, Contact=existing test contact</t>
         </is>
       </c>
-      <c r="G136" s="43" t="inlineStr">
+      <c r="G140" s="43" t="inlineStr">
         <is>
           <t>Case record created; CaseTriggerHandler fires; Work Order creation triggered if Request Flow mapping exists; case number formatted correctly (e.g. 00001234)</t>
         </is>
       </c>
-      <c r="AG136" t="inlineStr">
+      <c r="AG140" t="inlineStr">
         <is>
           <t>CFSUITE-SR-101</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="96" customHeight="1">
-      <c r="A137" s="43" t="inlineStr">
+    <row r="141" ht="84" customHeight="1">
+      <c r="A141" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B137" s="43" t="inlineStr">
+      <c r="B141" s="43" t="inlineStr">
         <is>
           <t>PROP-028</t>
         </is>
       </c>
-      <c r="C137" s="43" t="inlineStr">
+      <c r="C141" s="43" t="inlineStr">
         <is>
           <t>Case Auto-Assignment via Request Flow</t>
         </is>
       </c>
-      <c r="D137" s="43" t="inlineStr">
+      <c r="D141" s="43" t="inlineStr">
         <is>
           <t>On case save, the case is automatically assigned to the correct queue/user based on the Request Flow Case Assignment configuration</t>
         </is>
       </c>
-      <c r="E137" s="43" t="inlineStr">
+      <c r="E141" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a category that has a Case Assignment Request Flow record
 2. Save the case
@@ -6011,44 +6221,44 @@
 4. Verify Department and Team fields are populated per the Work Order Mapping</t>
         </is>
       </c>
-      <c r="F137" s="43" t="inlineStr">
+      <c r="F141" s="43" t="inlineStr">
         <is>
           <t>Category with active Case Assignment Request Flow record configured</t>
         </is>
       </c>
-      <c r="G137" s="43" t="inlineStr">
+      <c r="G141" s="43" t="inlineStr">
         <is>
           <t>CaseTriggerOperation fires assignment logic; Case OwnerId matches configured queue/user; cfsuite1__Department__c and cfsuite1__Team__c set per mapping</t>
         </is>
       </c>
-      <c r="AG137" t="inlineStr">
+      <c r="AG141" t="inlineStr">
         <is>
           <t>CFSUITE-SR-102</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="84" customHeight="1">
-      <c r="A138" s="43" t="inlineStr">
+    <row r="142" ht="72" customHeight="1">
+      <c r="A142" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B138" s="43" t="inlineStr">
+      <c r="B142" s="43" t="inlineStr">
         <is>
           <t>PROP-029</t>
         </is>
       </c>
-      <c r="C138" s="43" t="inlineStr">
+      <c r="C142" s="43" t="inlineStr">
         <is>
           <t>Case Status Transition - Close Case</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
+      <c r="D142" s="43" t="inlineStr">
         <is>
           <t>Staff closes a case with a close reason; case status updates and closure notification sent</t>
         </is>
       </c>
-      <c r="E138" s="43" t="inlineStr">
+      <c r="E142" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing open case
 2. Change Status to 'Closed'
@@ -6059,44 +6269,44 @@
 7. Verify closure email notification dispatched (check Message Queue)</t>
         </is>
       </c>
-      <c r="F138" s="43" t="inlineStr">
+      <c r="F142" s="43" t="inlineStr">
         <is>
           <t>closeReason=Work Complete, completionComment=Works carried out on 01/05/2026</t>
         </is>
       </c>
-      <c r="G138" s="43" t="inlineStr">
+      <c r="G142" s="43" t="inlineStr">
         <is>
           <t>Case Status=Closed; CaseTriggerOperation fires close logic; CommsEventHandler queues notification; Message_Queue__c record created for customer notification</t>
         </is>
       </c>
-      <c r="AG138" t="inlineStr">
+      <c r="AG142" t="inlineStr">
         <is>
           <t>CFSUITE-SR-103</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="43" t="inlineStr">
+    <row r="143" ht="84" customHeight="1">
+      <c r="A143" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B139" s="43" t="inlineStr">
+      <c r="B143" s="43" t="inlineStr">
         <is>
           <t>PROP-030</t>
         </is>
       </c>
-      <c r="C139" s="43" t="inlineStr">
+      <c r="C143" s="43" t="inlineStr">
         <is>
           <t>Add Case Note Visible to Community</t>
         </is>
       </c>
-      <c r="D139" s="43" t="inlineStr">
+      <c r="D143" s="43" t="inlineStr">
         <is>
           <t>Staff adds a case note; note is visible in the community portal case detail</t>
         </is>
       </c>
-      <c r="E139" s="43" t="inlineStr">
+      <c r="E143" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing case
 2. Add a new Case Note / Chatter post with visibility set to community
@@ -6106,44 +6316,44 @@
 6. Verify the note is visible</t>
         </is>
       </c>
-      <c r="F139" s="43" t="inlineStr">
+      <c r="F143" s="43" t="inlineStr">
         <is>
           <t>noteText=Your request is currently being assessed by our roads team.</t>
         </is>
       </c>
-      <c r="G139" s="43" t="inlineStr">
+      <c r="G143" s="43" t="inlineStr">
         <is>
           <t>FeedItem created with appropriate visibility; FeedItemTriggerHandler executes; community user sees note in case detail; no error in FeedItemInsertHelperClass</t>
         </is>
       </c>
-      <c r="AG139" t="inlineStr">
+      <c r="AG143" t="inlineStr">
         <is>
           <t>CFSUITE-SR-104</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="72" customHeight="1">
-      <c r="A140" s="43" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B140" s="43" t="inlineStr">
+      <c r="B144" s="43" t="inlineStr">
         <is>
           <t>PROP-031</t>
         </is>
       </c>
-      <c r="C140" s="43" t="inlineStr">
+      <c r="C144" s="43" t="inlineStr">
         <is>
           <t>Duplicate Case Detection and Linking</t>
         </is>
       </c>
-      <c r="D140" s="43" t="inlineStr">
+      <c r="D144" s="43" t="inlineStr">
         <is>
           <t>When staff creates a case matching an existing open case by category and location, duplicate flag is set and linked</t>
         </is>
       </c>
-      <c r="E140" s="43" t="inlineStr">
+      <c r="E144" s="43" t="inlineStr">
         <is>
           <t>1. Create a case for 'Illegal Dumping' at a specific address
 2. Create a second case with same category and nearby address
@@ -6151,44 +6361,44 @@
 4. Verify the two cases are linked</t>
         </is>
       </c>
-      <c r="F140" s="43" t="inlineStr">
+      <c r="F144" s="43" t="inlineStr">
         <is>
           <t>Two cases with same category and address within duplicate-detection threshold</t>
         </is>
       </c>
-      <c r="G140" s="43" t="inlineStr">
+      <c r="G144" s="43" t="inlineStr">
         <is>
           <t>CaseTriggerOperation duplicate detection fires; cfsuite1__Duplicate__c field populated; parent/child case relationship established</t>
         </is>
       </c>
-      <c r="AG140" t="inlineStr">
+      <c r="AG144" t="inlineStr">
         <is>
           <t>CFSUITE-SR-105</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="84" customHeight="1">
-      <c r="A141" s="43" t="inlineStr">
+    <row r="145" ht="48" customHeight="1">
+      <c r="A145" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B141" s="43" t="inlineStr">
+      <c r="B145" s="43" t="inlineStr">
         <is>
           <t>PROP-032</t>
         </is>
       </c>
-      <c r="C141" s="43" t="inlineStr">
+      <c r="C145" s="43" t="inlineStr">
         <is>
           <t>Work Order Auto-Creation from Case</t>
         </is>
       </c>
-      <c r="D141" s="43" t="inlineStr">
+      <c r="D145" s="43" t="inlineStr">
         <is>
           <t>When a case with a category that has Create_Work_Order=true is saved, a Work Order is automatically created</t>
         </is>
       </c>
-      <c r="E141" s="43" t="inlineStr">
+      <c r="E145" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a category mapped to a Work Order Mapping Request Flow record with Create_Work_Order=true
 2. Save the case
@@ -6196,44 +6406,44 @@
 4. Verify a Work Order record has been created with the correct category, queue, and record type</t>
         </is>
       </c>
-      <c r="F141" s="43" t="inlineStr">
+      <c r="F145" s="43" t="inlineStr">
         <is>
           <t>Category with Work Order Mapping record: Create_Work_Order=true, WO_Record_Type_Developer_Name populated</t>
         </is>
       </c>
-      <c r="G141" s="43" t="inlineStr">
+      <c r="G145" s="43" t="inlineStr">
         <is>
           <t>WorkOrderHandler creates WorkOrder record; WO linked to Case; cfsuite1__Work_Order_Category__c, cfsuite1__Work_Order_Queue__c populated; WorkOrderMilestoneHelperClass assigns entitlement process if configured</t>
         </is>
       </c>
-      <c r="AG141" t="inlineStr">
+      <c r="AG145" t="inlineStr">
         <is>
           <t>CFSUITE-SR-106</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="72" customHeight="1">
-      <c r="A142" s="43" t="inlineStr">
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B142" s="43" t="inlineStr">
+      <c r="B146" s="43" t="inlineStr">
         <is>
           <t>PROP-033</t>
         </is>
       </c>
-      <c r="C142" s="43" t="inlineStr">
+      <c r="C146" s="43" t="inlineStr">
         <is>
           <t>Work Order Status Update Triggers Case Update</t>
         </is>
       </c>
-      <c r="D142" s="43" t="inlineStr">
+      <c r="D146" s="43" t="inlineStr">
         <is>
           <t>When a Work Order is set to 'Completed', the parent Case status is updated per the Request Flow mapping</t>
         </is>
       </c>
-      <c r="E142" s="43" t="inlineStr">
+      <c r="E146" s="43" t="inlineStr">
         <is>
           <t>1. Open a Work Order linked to a Case via a Work Order Mapping record
 2. Change Work Order Status to 'Completed'
@@ -6242,44 +6452,44 @@
 5. Verify Case Status has updated per the New_Status on the Request Flow mapping</t>
         </is>
       </c>
-      <c r="F142" s="43" t="inlineStr">
+      <c r="F146" s="43" t="inlineStr">
         <is>
           <t>Work Order with parent Case and active Work Order Mapping with New_Status and Update_Case=true</t>
         </is>
       </c>
-      <c r="G142" s="43" t="inlineStr">
+      <c r="G146" s="43" t="inlineStr">
         <is>
           <t>WorkOrderTriggerHandler fires; CaseTriggerOperation updates parent case status; Case status matches cfsuite1__New_Status__c from Work Order Mapping record</t>
         </is>
       </c>
-      <c r="AG142" t="inlineStr">
+      <c r="AG146" t="inlineStr">
         <is>
           <t>CFSUITE-SR-107</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="84" customHeight="1">
-      <c r="A143" s="43" t="inlineStr">
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B143" s="43" t="inlineStr">
+      <c r="B147" s="43" t="inlineStr">
         <is>
           <t>PROP-034</t>
         </is>
       </c>
-      <c r="C143" s="43" t="inlineStr">
+      <c r="C147" s="43" t="inlineStr">
         <is>
           <t>Work Order Hazard Flag - Emergency SLA Assignment</t>
         </is>
       </c>
-      <c r="D143" s="43" t="inlineStr">
+      <c r="D147" s="43" t="inlineStr">
         <is>
           <t>Marking a work order as a hazard applies the Hazard SLA defined in the Request Flow mapping</t>
         </is>
       </c>
-      <c r="E143" s="43" t="inlineStr">
+      <c r="E147" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing Work Order linked to a category with a Hazard_SLA configured
 2. Set the Hazard flag to true
@@ -6287,44 +6497,44 @@
 4. Verify the SLA on the Work Order has been updated to the Hazard SLA value</t>
         </is>
       </c>
-      <c r="F143" s="43" t="inlineStr">
+      <c r="F147" s="43" t="inlineStr">
         <is>
           <t>Work Order category with Hazard_SLA field populated in Request Flow</t>
         </is>
       </c>
-      <c r="G143" s="43" t="inlineStr">
+      <c r="G147" s="43" t="inlineStr">
         <is>
           <t>WorkOrderUpdateHelperClass applies hazard SLA; EntitlementId updated on Work Order; milestone timestamps recalculated by WorkOrderMilestoneHelperClass</t>
         </is>
       </c>
-      <c r="AG143" t="inlineStr">
+      <c r="AG147" t="inlineStr">
         <is>
           <t>CFSUITE-SR-108</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="43" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="43" t="inlineStr">
         <is>
           <t>Proposed - Service Requests &amp; Case Management</t>
         </is>
       </c>
-      <c r="B144" s="43" t="inlineStr">
+      <c r="B148" s="43" t="inlineStr">
         <is>
           <t>PROP-038</t>
         </is>
       </c>
-      <c r="C144" s="43" t="inlineStr">
+      <c r="C148" s="43" t="inlineStr">
         <is>
           <t>Add Interested Party to a Case</t>
         </is>
       </c>
-      <c r="D144" s="43" t="inlineStr">
+      <c r="D148" s="43" t="inlineStr">
         <is>
           <t>An interested party contact can be added to a case and receives notifications about that case</t>
         </is>
       </c>
-      <c r="E144" s="43" t="inlineStr">
+      <c r="E148" s="43" t="inlineStr">
         <is>
           <t>1. Open an existing Case (internal view)
 2. Navigate to the Interested Parties related list
@@ -6335,172 +6545,1616 @@
 7. Verify an email notification is sent to the interested party</t>
         </is>
       </c>
-      <c r="F144" s="43" t="inlineStr">
+      <c r="F148" s="43" t="inlineStr">
         <is>
           <t>Contact: existing test contact not the case requester</t>
         </is>
       </c>
-      <c r="G144" s="43" t="inlineStr">
+      <c r="G148" s="43" t="inlineStr">
         <is>
           <t>cfsuite1__Interested_Parties__c record created linked to Case and Contact; CommsEventHandler dispatches notification to interested party on case update; Message_Queue__c record created</t>
         </is>
       </c>
-      <c r="AG144" t="inlineStr">
+      <c r="AG148" t="inlineStr">
         <is>
           <t>CFSUITE-SR-109</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="48" customHeight="1">
-      <c r="A145" s="42" t="inlineStr">
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PROP-059</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Guest - Submit case via Request/Location/Details/Complete with map next step</t>
+        </is>
+      </c>
+      <c r="D149" s="48" t="inlineStr">
+        <is>
+          <t>An unauthenticated (guest) user can submit a service request through the four-step Request -&gt; Location -&gt; Details -&gt; Complete wizard for a category whose final response Request Flow has Next Step = Map. The resulting Case carries the location pin selected on the map.</t>
+        </is>
+      </c>
+      <c r="G149" s="48" t="inlineStr">
+        <is>
+          <t>Case record created with cfsuite1__Request_location__c populated; cfsuite1__Location__Latitude__s and cfsuite1__Location__Longitude__s set from the map pin; no community User linked to the case; ContactId resolved from the matched/new Contact via GuestUserInsertContactHelperClass.</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-110</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="72" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PROP-060</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Guest - Submit case via Request/Details/Complete with flow next step</t>
+        </is>
+      </c>
+      <c r="D150" s="48" t="inlineStr">
+        <is>
+          <t>An unauthenticated (guest) user can submit a service request through the three-step Request -&gt; Details -&gt; Complete wizard for a category whose final response Request Flow has Next Step = Flow. The wizard does NOT show the Location step; the embedded Salesforce Flow captures the request details.</t>
+        </is>
+      </c>
+      <c r="G150" s="48" t="inlineStr">
+        <is>
+          <t>Case record created via the configured Salesforce Flow; flow-collected fields are mapped onto the Case; no cfsuite1__Request_location__c is populated; no community User linked; ContactId resolved via guest helpers.</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-111</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="72" customHeight="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PROP-061</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Guest - Submit case with asset layer; verify AssetId captured</t>
+        </is>
+      </c>
+      <c r="D151" s="48" t="inlineStr">
+        <is>
+          <t>Guest submits via Request -&gt; Location -&gt; Details -&gt; Complete for a category whose final response Request Flow has Next Step = Map AND an asset layer configured. Selecting an asset on the map associates the asset with the case.</t>
+        </is>
+      </c>
+      <c r="G151" s="48" t="inlineStr">
+        <is>
+          <t>Case.cfsuite1__AssetId__c is populated with the Id of the asset chosen on the map layer; map pin location is also captured in cfsuite1__Request_location__c.</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-112</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PROP-062</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Guest - Submit case with zone layer; verify Zone captured</t>
+        </is>
+      </c>
+      <c r="D152" s="48" t="inlineStr">
+        <is>
+          <t>Guest submits via Request -&gt; Location -&gt; Details -&gt; Complete for a category whose final response Request Flow has Next Step = Map AND a zone layer configured. Selecting a location within a zone associates the zone with the case.</t>
+        </is>
+      </c>
+      <c r="G152" s="48" t="inlineStr">
+        <is>
+          <t>Case.cfsuite1__Zone_GIS__c (and/or cfsuite1__Zones__c) is populated with the zone name resolved from the map pin position; map pin location also captured in cfsuite1__Request_location__c.</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-113</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="72" customHeight="1">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PROP-063</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Logged-in - Submit case via Request/Location/Details/Complete with map next step</t>
+        </is>
+      </c>
+      <c r="D153" s="48" t="inlineStr">
+        <is>
+          <t>Authenticated community user submits the four-step wizard as in PROP-059. Case is linked to the user's Account and Contact.</t>
+        </is>
+      </c>
+      <c r="G153" s="48" t="inlineStr">
+        <is>
+          <t>Same outputs as PROP-059, plus: Case.AccountId and Case.ContactId match the logged-in community user's PersonAccount; CommunityUserInsertCaseHelperClass executes without error.</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-114</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PROP-064</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Logged-in - Submit case via Request/Details/Complete with flow next step</t>
+        </is>
+      </c>
+      <c r="D154" s="48" t="inlineStr">
+        <is>
+          <t>Authenticated community user submits the three-step wizard as in PROP-060. Case is linked to the user's Account and Contact.</t>
+        </is>
+      </c>
+      <c r="G154" s="48" t="inlineStr">
+        <is>
+          <t>Same outputs as PROP-060, plus: Case.AccountId and Case.ContactId match the logged-in user; cfsuite1__Request_location__c remains empty (no Location step).</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-115</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PROP-065</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Logged-in - Submit case with asset layer; verify AssetId captured</t>
+        </is>
+      </c>
+      <c r="D155" s="48" t="inlineStr">
+        <is>
+          <t>Authenticated community user submits as in PROP-061.</t>
+        </is>
+      </c>
+      <c r="G155" s="48" t="inlineStr">
+        <is>
+          <t>Same outputs as PROP-061, plus the Case is linked to the logged-in user's AccountId / ContactId.</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-116</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PROP-066</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Logged-in - Submit case with zone layer; verify Zone captured</t>
+        </is>
+      </c>
+      <c r="D156" s="48" t="inlineStr">
+        <is>
+          <t>Authenticated community user submits as in PROP-062.</t>
+        </is>
+      </c>
+      <c r="G156" s="48" t="inlineStr">
+        <is>
+          <t>Same outputs as PROP-062, plus the Case is linked to the logged-in user's AccountId / ContactId.</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-117</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PROP-067</t>
+        </is>
+      </c>
+      <c r="C157" s="48" t="inlineStr">
+        <is>
+          <t>Map layer result limits configurable</t>
+        </is>
+      </c>
+      <c r="D157" s="48" t="inlineStr">
+        <is>
+          <t>Custom settings BusLayerMaxResults/Suggestions, BuildingLayerMaxResults/Suggestions, ReserveLayerMaxResults/Suggestions, AddressLayerMaxResults/Suggestions control the max rows returned by the corresponding map layer in the Internal Case Creation view.
+Source: Release 3.156 (47118, 31415)</t>
+        </is>
+      </c>
+      <c r="G157" s="48" t="inlineStr">
+        <is>
+          <t>Setting each *MaxResults__c to 20 (or 100 for Address) caps the search results at that count. Search suggestions appear after 2 chars for Bus Stops and 3 chars for other layers.</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-118</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PROP-068</t>
+        </is>
+      </c>
+      <c r="C158" s="48" t="inlineStr">
+        <is>
+          <t>My Requests table shows Request Reason column in portal</t>
+        </is>
+      </c>
+      <c r="D158" s="48" t="inlineStr">
+        <is>
+          <t>Logged-in community user viewing the My Requests tile sees a Request Reason column on each row.
+Source: Release 3.156 (34327)</t>
+        </is>
+      </c>
+      <c r="G158" s="48" t="inlineStr">
+        <is>
+          <t>Request Reason column is present and shows the case's cfReq_Request_Reason value for each row.</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-119</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PROP-069</t>
+        </is>
+      </c>
+      <c r="C159" s="48" t="inlineStr">
+        <is>
+          <t>Asset layer opacity configurable on Map Layers</t>
+        </is>
+      </c>
+      <c r="D159" s="48" t="inlineStr">
+        <is>
+          <t>Opacity setting on a CFSuite Map Layers asset record controls the transparency of the rendered asset overlay on the map.
+Source: Release 3.156 (39932, 41244)</t>
+        </is>
+      </c>
+      <c r="G159" s="48" t="inlineStr">
+        <is>
+          <t>Setting a lower opacity makes the asset layer more transparent so the underlying base map is visible through it.</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PROP-070</t>
+        </is>
+      </c>
+      <c r="C160" s="48" t="inlineStr">
+        <is>
+          <t>Create Case button disabled until asset selected - category first</t>
+        </is>
+      </c>
+      <c r="D160" s="48" t="inlineStr">
+        <is>
+          <t>When an asset-layer category is chosen first (then a location), the Create Case button remains disabled until an asset is selected on the map.
+Source: Release 3.156 (46375)</t>
+        </is>
+      </c>
+      <c r="G160" s="48" t="inlineStr">
+        <is>
+          <t>Button stays disabled after category/reason/sub-reason selection; enables once an asset is clicked; created case has cfsuite1__AssetId__c populated.</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-121</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="84" customHeight="1">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PROP-071</t>
+        </is>
+      </c>
+      <c r="C161" s="48" t="inlineStr">
+        <is>
+          <t>Create Case button disabled until asset selected - location first</t>
+        </is>
+      </c>
+      <c r="D161" s="48" t="inlineStr">
+        <is>
+          <t>When a location is chosen first (then an asset-layer category), the Create Case button stays disabled until an asset is selected on the map layer.
+Source: Release 3.156 (46375)</t>
+        </is>
+      </c>
+      <c r="G161" s="48" t="inlineStr">
+        <is>
+          <t>Reverse order from PROP-070: location selected, then category/reason/sub-reason that displays asset layer; button stays disabled until asset chosen; case carries cfsuite1__AssetId__c.</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-122</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PROP-072</t>
+        </is>
+      </c>
+      <c r="C162" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - 'Optional contact details' + SMS entered</t>
+        </is>
+      </c>
+      <c r="D162" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured as 'Allow anonymous with optional contact details'. Guest user submits with Notification Method = SMS and a mobile number.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G162" s="48" t="inlineStr">
+        <is>
+          <t>Case is created; Web_Name/Web_Email/Web_Phone fields populated; SMS_Message__c record with Status='Pending' created; warning text from Guest Comms Warning setting visible during the wizard.</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-123</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="24" customHeight="1">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PROP-073</t>
+        </is>
+      </c>
+      <c r="C163" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - 'Optional contact details' + Email entered</t>
+        </is>
+      </c>
+      <c r="D163" s="48" t="inlineStr">
+        <is>
+          <t>Same Community Request configuration as PROP-072 but guest provides Email + Notification Method = Email.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G163" s="48" t="inlineStr">
+        <is>
+          <t>Case is created; Web_* fields populated; email dispatched to the guest's address; warning visible on contact-details page.</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-124</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PROP-074</t>
+        </is>
+      </c>
+      <c r="C164" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - 'Optional contact details' + No details + No updates</t>
+        </is>
+      </c>
+      <c r="D164" s="48" t="inlineStr">
+        <is>
+          <t>Same configuration as PROP-072 but guest provides no contact details and ticks 'No updates required'.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G164" s="48" t="inlineStr">
+        <is>
+          <t>Submit succeeds; Case is created with Notification Method blank; Description has no guest-user info appended; no notifications sent.</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="24" customHeight="1">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PROP-075</t>
+        </is>
+      </c>
+      <c r="C165" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - validation rule SMS-channel mismatch</t>
+        </is>
+      </c>
+      <c r="D165" s="48" t="inlineStr">
+        <is>
+          <t>Same configuration as PROP-072 but guest enters a mobile number while selecting Email as the Notification Method.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G165" s="48" t="inlineStr">
+        <is>
+          <t>No_Phone_And_Notification_Method_Is_SMS / No_Email_And_Notification_Method_Is_Email validation rule fires; Case cannot be saved.</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-126</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PROP-076</t>
+        </is>
+      </c>
+      <c r="C166" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - validation rule Email-channel mismatch</t>
+        </is>
+      </c>
+      <c r="D166" s="48" t="inlineStr">
+        <is>
+          <t>Same configuration as PROP-075 but reverse: guest enters Email while selecting SMS as Notification Method.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G166" s="48" t="inlineStr">
+        <is>
+          <t>Validation rule fires; Case cannot be saved.</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-127</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PROP-077</t>
+        </is>
+      </c>
+      <c r="C167" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - 'Allow anonymous with contact details' mandatory</t>
+        </is>
+      </c>
+      <c r="D167" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured as 'Allow anonymous with contact details' (NOT optional). Guest submits.
+Source: Release 3.156 (47242)</t>
+        </is>
+      </c>
+      <c r="G167" s="48" t="inlineStr">
+        <is>
+          <t>Contact details section is shown with mandatory fields; submitting empty fields shows validation errors; valid submit creates case with Web_* fields populated and Notification Method set; email is received.</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-128</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="72" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PROP-078</t>
+        </is>
+      </c>
+      <c r="C168" s="48" t="inlineStr">
+        <is>
+          <t>Guest routing - 'Do not allow anonymous'</t>
+        </is>
+      </c>
+      <c r="D168" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured to disallow anonymous submission.
+Source: Release 3.156 (47242) / 3.152 (23704, 26146, 27230)</t>
+        </is>
+      </c>
+      <c r="G168" s="48" t="inlineStr">
+        <is>
+          <t>Guest viewing the category does NOT see a 'Continue as Guest User' button; only the login flow is available.</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-129</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="72" customHeight="1">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PROP-079</t>
+        </is>
+      </c>
+      <c r="C169" s="48" t="inlineStr">
+        <is>
+          <t>Recategorisation due date rebaseline toggle</t>
+        </is>
+      </c>
+      <c r="D169" s="48" t="inlineStr">
+        <is>
+          <t>When 'Enable Recat Due Date Rebaseline' is OFF, recategorising a case to a request flow with a different SLA leaves Milestone_Start_Date unchanged but updates Original_Due_Date based on new SLA from the original start. When ON, both dates rebaseline from the recategorisation time.
+Source: Release 3.156 (43127)</t>
+        </is>
+      </c>
+      <c r="G169" s="48" t="inlineStr">
+        <is>
+          <t>Toggle OFF: Milestone_Start_Date unchanged after recat; Original_Due_Date reflects new SLA from original start. Toggle ON: Milestone_Start_Date = recategorisation time; Original_Due_Date = recat time + new SLA.</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-130</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PROP-080</t>
+        </is>
+      </c>
+      <c r="C170" s="48" t="inlineStr">
+        <is>
+          <t>AO Map Select All / Clear All filter behaviour</t>
+        </is>
+      </c>
+      <c r="D170" s="48" t="inlineStr">
+        <is>
+          <t>On the AO Map &gt; More Filters &gt; Team and Work Category, the 'All' toggle and 'Clear All' link work consistently with individual flags.
+Source: Release 3.156 (51034)</t>
+        </is>
+      </c>
+      <c r="G170" s="48" t="inlineStr">
+        <is>
+          <t>Click 'All': all child flags checked; click 'All' again: all unchecked. Click 'Clear All' link: all individual flags clear.</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-131</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PROP-081</t>
+        </is>
+      </c>
+      <c r="C171" s="48" t="inlineStr">
+        <is>
+          <t>Description preserved through case recategorisation</t>
+        </is>
+      </c>
+      <c r="D171" s="48" t="inlineStr">
+        <is>
+          <t>Description entered on a case is retained when the case is recategorised via 'Correct Case Category'.
+Source: Release 3.156 (51132)</t>
+        </is>
+      </c>
+      <c r="G171" s="48" t="inlineStr">
+        <is>
+          <t>After recategorisation, Description field on the case still contains the original text.</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-132</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="48" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PROP-082</t>
+        </is>
+      </c>
+      <c r="C172" s="48" t="inlineStr">
+        <is>
+          <t>Create case via bus-stop layer captures bus-stop address</t>
+        </is>
+      </c>
+      <c r="D172" s="48" t="inlineStr">
+        <is>
+          <t>Internal case create: choose a category/reason that uses the bus-stop layer; select a bus stop on the map; create case.
+Source: Release 3.154 (21079, 33892, 37490)</t>
+        </is>
+      </c>
+      <c r="G172" s="48" t="inlineStr">
+        <is>
+          <t>Case Request_location is populated with the bus stop's address attribute.</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="84" customHeight="1">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PROP-083</t>
+        </is>
+      </c>
+      <c r="C173" s="48" t="inlineStr">
+        <is>
+          <t>Create case via building layer captures building address</t>
+        </is>
+      </c>
+      <c r="D173" s="48" t="inlineStr">
+        <is>
+          <t>Same as PROP-082 but with the building layer.
+Source: Release 3.154 (21079, 33892, 37490) / 3.152 (21079, 23530, 23732, 25327)</t>
+        </is>
+      </c>
+      <c r="G173" s="48" t="inlineStr">
+        <is>
+          <t>Case Request_location is populated with the building's address attribute.</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-134</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="84" customHeight="1">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PROP-084</t>
+        </is>
+      </c>
+      <c r="C174" s="48" t="inlineStr">
+        <is>
+          <t>Create case via reserve layer captures reserve address</t>
+        </is>
+      </c>
+      <c r="D174" s="48" t="inlineStr">
+        <is>
+          <t>Same as PROP-082 but with the reserve layer.
+Source: Release 3.154 (21079, 33892, 37490)</t>
+        </is>
+      </c>
+      <c r="G174" s="48" t="inlineStr">
+        <is>
+          <t>Case Request_location is populated with the reserve's address attribute.</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="72" customHeight="1">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PROP-085</t>
+        </is>
+      </c>
+      <c r="C175" s="48" t="inlineStr">
+        <is>
+          <t>Show All Cases Default setting on internal case view</t>
+        </is>
+      </c>
+      <c r="D175" s="48" t="inlineStr">
+        <is>
+          <t>Custom setting 'Show All Cases Default' controls the default state of the Show All Cases toggle in the internal Case Creation view.
+Source: Release 3.154 (24016)</t>
+        </is>
+      </c>
+      <c r="G175" s="48" t="inlineStr">
+        <is>
+          <t>Setting = Yes: toggle defaults ON. Setting = No: toggle defaults OFF. Reflects current setting on next page load.</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PROP-086</t>
+        </is>
+      </c>
+      <c r="C176" s="48" t="inlineStr">
+        <is>
+          <t>Description retained through category change on internal case create</t>
+        </is>
+      </c>
+      <c r="D176" s="48" t="inlineStr">
+        <is>
+          <t>On the internal case creation view, entering a Description and then changing the category does not clear the Description.
+Source: Release 3.154 (34323)</t>
+        </is>
+      </c>
+      <c r="G176" s="48" t="inlineStr">
+        <is>
+          <t>Description text persists across category/reason/sub-reason changes; persists on the final saved Case.</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-137</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PROP-087</t>
+        </is>
+      </c>
+      <c r="C177" s="48" t="inlineStr">
+        <is>
+          <t>Portal case with flow accepts multi-file attachments</t>
+        </is>
+      </c>
+      <c r="D177" s="48" t="inlineStr">
+        <is>
+          <t>On the community portal, creating a case that uses a Flow form supports the configured number of file attachments (per CFSuite Settings).
+Source: Release 3.154 (29954, 22612)</t>
+        </is>
+      </c>
+      <c r="G177" s="48" t="inlineStr">
+        <is>
+          <t>Attachments setting = 5: portal accepts up to 5 files; each uploaded file is listed; submitted case has all files attached as ContentVersion + ContentDocumentLink.</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-138</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PROP-088</t>
+        </is>
+      </c>
+      <c r="C178" s="48" t="inlineStr">
+        <is>
+          <t>AO Map pin popup, saved filters, manual assignment</t>
+        </is>
+      </c>
+      <c r="D178" s="48" t="inlineStr">
+        <is>
+          <t>Action Officer Map: clicking a pin shows the popup; saved filter loads records; new filter can be created and saved; assign-to flow assigns ownership; list view reflects the active filter.
+Source: Release 3.154 (36041)</t>
+        </is>
+      </c>
+      <c r="G178" s="48" t="inlineStr">
+        <is>
+          <t>Pin popup displays; saved filter returns matching cases; new filter persists; case OwnerId updates after assign-to; list view filtered consistently.</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-139</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PROP-089</t>
+        </is>
+      </c>
+      <c r="C179" s="48" t="inlineStr">
+        <is>
+          <t>Portal category search suggested list clears when input empty</t>
+        </is>
+      </c>
+      <c r="D179" s="48" t="inlineStr">
+        <is>
+          <t>Customer portal category search bar shows suggested categories as the user types; clearing the input removes the suggestions.
+Source: Release 3.154 (32651)</t>
+        </is>
+      </c>
+      <c r="G179" s="48" t="inlineStr">
+        <is>
+          <t>Typing returns suggestions; deleting all characters hides the suggestions list.</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-140</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PROP-090</t>
+        </is>
+      </c>
+      <c r="C180" s="48" t="inlineStr">
+        <is>
+          <t>AO Map list view shows Due Date column and sorts by it</t>
+        </is>
+      </c>
+      <c r="D180" s="48" t="inlineStr">
+        <is>
+          <t>AO Map list tab displays a Due Date column; clicking the header sorts by due date asc/desc.
+Source: Release 3.152 (17300, 24341, 23471)</t>
+        </is>
+      </c>
+      <c r="G180" s="48" t="inlineStr">
+        <is>
+          <t>Due Date column visible; sort order changes on header click; rows ordered correctly.</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-141</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PROP-091</t>
+        </is>
+      </c>
+      <c r="C181" s="48" t="inlineStr">
+        <is>
+          <t>AO Map default view (List/Map) controlled by setting</t>
+        </is>
+      </c>
+      <c r="D181" s="48" t="inlineStr">
+        <is>
+          <t>CFSuite Settings 'AO Map Default view' setting controls whether the AO Map opens in List or Map view on the Home page.
+Source: Release 3.152 (19846)</t>
+        </is>
+      </c>
+      <c r="G181" s="48" t="inlineStr">
+        <is>
+          <t>Setting = List: AO Map opens to list view. Setting = Map: AO Map opens to map view.</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-142</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PROP-092</t>
+        </is>
+      </c>
+      <c r="C182" s="48" t="inlineStr">
+        <is>
+          <t>Console - clicking case number opens case in new console tab</t>
+        </is>
+      </c>
+      <c r="D182" s="48" t="inlineStr">
+        <is>
+          <t>From a console view such as CFSuite Console, clicking a case number from the home page opens the case in a new console tab (not navigates away).
+Source: Release 3.152 (19112)</t>
+        </is>
+      </c>
+      <c r="G182" s="48" t="inlineStr">
+        <is>
+          <t>New console tab opens with the case detail loaded; original tab stays intact.</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-143</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PROP-093</t>
+        </is>
+      </c>
+      <c r="C183" s="48" t="inlineStr">
+        <is>
+          <t>Updating Customer Name auto-updates Contact Name on case</t>
+        </is>
+      </c>
+      <c r="D183" s="48" t="inlineStr">
+        <is>
+          <t>On a Case owned by a Person Account: updating the Customer Name (Account lookup) to a Business Account auto-updates the Contact Name field to the related contact.
+Source: Release 3.152 (30313)</t>
+        </is>
+      </c>
+      <c r="G183" s="48" t="inlineStr">
+        <is>
+          <t>Contact Name field reflects the new account's primary contact after Customer Name change.</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-144</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PROP-094</t>
+        </is>
+      </c>
+      <c r="C184" s="48" t="inlineStr">
+        <is>
+          <t>Edit Location preserves asset Id when pin not moved</t>
+        </is>
+      </c>
+      <c r="D184" s="48" t="inlineStr">
+        <is>
+          <t>On a case created via an asset layer, clicking Edit Location and then Update Location without moving the pin leaves the asset Id intact.
+Source: Release 3.152 (23472)</t>
+        </is>
+      </c>
+      <c r="G184" s="48" t="inlineStr">
+        <is>
+          <t>After Edit Location + Update Location with unchanged pin, Case.cfsuite1__AssetId__c is unchanged.</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-145</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PROP-095</t>
+        </is>
+      </c>
+      <c r="C185" s="48" t="inlineStr">
+        <is>
+          <t>Additional Details Mandatory portal setting enforces field</t>
+        </is>
+      </c>
+      <c r="D185" s="48" t="inlineStr">
+        <is>
+          <t>CFSuite Settings 'Additional Details Mandatory' set to Yes makes the additional information field required at the end of the request wizard.
+Source: Release 3.152 (26144)</t>
+        </is>
+      </c>
+      <c r="G185" s="48" t="inlineStr">
+        <is>
+          <t>Submitting an empty additional-info field shows the validation error; filling and submitting allows the request to proceed to the thank-you page.</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-146</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PROP-096</t>
+        </is>
+      </c>
+      <c r="C186" s="48" t="inlineStr">
+        <is>
+          <t>Guest user 'Allow anonymous with no contact details' - no contact form</t>
+        </is>
+      </c>
+      <c r="D186" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured with 'Allow anonymous with no contact details': guest user submission skips the contact details step entirely.
+Source: Release 3.156 (47242) - Test 6</t>
+        </is>
+      </c>
+      <c r="G186" s="48" t="inlineStr">
+        <is>
+          <t>After location selection, no contact-details section displayed; submit goes directly to thank-you; no notifications dispatched.</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-147</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PROP-097</t>
+        </is>
+      </c>
+      <c r="C187" s="48" t="inlineStr">
+        <is>
+          <t>Per-flow Cancel button on My Requests opens configured flow in modal</t>
+        </is>
+      </c>
+      <c r="D187" s="48" t="inlineStr">
+        <is>
+          <t>On a Request Flow record, enabling the cancel button and setting My Request Button Flow + My Request Button Name surfaces a button on the My Requests screen for matching cases. Clicking presents the configured flow in a modal.
+Source: Release 3.152 (23707)</t>
+        </is>
+      </c>
+      <c r="G187" s="48" t="inlineStr">
+        <is>
+          <t>Button visible only on cases that match the configured request flow; click opens flow in modal; flow runs to completion and reflects on case.</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-148</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PROP-098</t>
+        </is>
+      </c>
+      <c r="C188" s="48" t="inlineStr">
+        <is>
+          <t>Deflection to custom community page with embedded flow</t>
+        </is>
+      </c>
+      <c r="D188" s="48" t="inlineStr">
+        <is>
+          <t>A Community Request record configured to deflect to a URL pointing at a custom community page that hosts a Flow component. Guest user choosing that category is shown the guest-user login first, then the deflection page with the flow.
+Source: Release 3.152 (27879)</t>
+        </is>
+      </c>
+      <c r="G188" s="48" t="inlineStr">
+        <is>
+          <t>Guest user login presented before deflection; community page renders the configured Flow component; flow runs as expected.</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-149</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PROP-099</t>
+        </is>
+      </c>
+      <c r="C189" s="48" t="inlineStr">
+        <is>
+          <t>Mass change owner from case list view</t>
+        </is>
+      </c>
+      <c r="D189" s="48" t="inlineStr">
+        <is>
+          <t>On a Case list view, multi-select cases and use the Change Owner action to update all selected cases at once.
+Source: Release 3.157 (00030439)</t>
+        </is>
+      </c>
+      <c r="G189" s="48" t="inlineStr">
+        <is>
+          <t>All selected cases get OwnerId updated to the chosen user/queue; success toast displayed; list view refreshes to show the new owner on each row.</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PROP-100</t>
+        </is>
+      </c>
+      <c r="C190" s="48" t="inlineStr">
+        <is>
+          <t>Raise a case as a logged-in business contact</t>
+        </is>
+      </c>
+      <c r="D190" s="48" t="inlineStr">
+        <is>
+          <t>Logged-in community user whose Contact belongs to a Business Account submits a case via the standard wizard. After submission, the case Contact is the logged-in user's contact and the case Account is the business account.
+Source: Release 3.157 (00032450)</t>
+        </is>
+      </c>
+      <c r="G190" s="48" t="inlineStr">
+        <is>
+          <t>Case.ContactId matches the logged-in business contact; Case.AccountId matches the business account; submission completes through the location -&gt; submit flow.</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-151</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PROP-101</t>
+        </is>
+      </c>
+      <c r="C191" s="48" t="inlineStr">
+        <is>
+          <t>Anonymous-with-optional in-form validation feedback</t>
+        </is>
+      </c>
+      <c r="D191" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured with 'Anonymous with optional contact details'. Guest user wizard contact-details page shows the 'No Updates' panel when nothing is selected; the word 'Optional' is NOT shown next to field labels; clicking SMS triggers field-level validation on the SMS Mobile field; clicking Email triggers field-level validation on the Email field; valid submit reaches the thank-you page.
+Source: Release 3.157 (no ticket recorded)</t>
+        </is>
+      </c>
+      <c r="G191" s="48" t="inlineStr">
+        <is>
+          <t>'No Updates' panel renders when no method selected; 'Optional' label absent next to fields; selecting SMS validates SMS Mobile; selecting Email validates Email; valid + complete details reach thank-you page.</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-152</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Proposed - Service Requests &amp; Case Management</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PROP-102</t>
+        </is>
+      </c>
+      <c r="C192" s="48" t="inlineStr">
+        <is>
+          <t>Anonymous-with-contact-details (mandatory) in-form validation feedback</t>
+        </is>
+      </c>
+      <c r="D192" s="48" t="inlineStr">
+        <is>
+          <t>Community Request configured with 'Anonymous with contact details' (mandatory). Guest user contact-details page validates all fields when SMS is selected and all fields when Email is selected; user cannot proceed without completing all required fields per channel choice.
+Source: Release 3.157 (no ticket recorded)</t>
+        </is>
+      </c>
+      <c r="G192" s="48" t="inlineStr">
+        <is>
+          <t>Selecting SMS shows validation across the SMS-channel fields; selecting Email shows validation across the Email-channel fields; submission blocked until all required fields per channel are filled.</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-153</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="42" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B145" s="42" t="n"/>
-      <c r="C145" s="42" t="n"/>
-      <c r="D145" s="42" t="n"/>
-      <c r="E145" s="42" t="n"/>
-      <c r="F145" s="42" t="n"/>
-      <c r="G145" s="42" t="n"/>
-    </row>
-    <row r="146" ht="36" customHeight="1">
-      <c r="A146" s="40" t="inlineStr">
+      <c r="B193" s="42" t="n"/>
+      <c r="C193" s="42" t="n"/>
+      <c r="D193" s="42" t="n"/>
+      <c r="E193" s="42" t="n"/>
+      <c r="F193" s="42" t="n"/>
+      <c r="G193" s="42" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="40" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B146" s="40" t="inlineStr">
+      <c r="B194" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-077</t>
         </is>
       </c>
-      <c r="C146" s="40" t="inlineStr">
+      <c r="C194" s="40" t="inlineStr">
         <is>
           <t>Automated email notifications</t>
         </is>
       </c>
-      <c r="D146" s="40" t="inlineStr">
+      <c r="D194" s="40" t="inlineStr">
         <is>
           <t>Ability to send automated emails on Case status updates to: . Customer submitting a request . An interested party Both receiving their own unique email template</t>
         </is>
       </c>
-      <c r="E146" s="40" t="n"/>
-      <c r="F146" s="40" t="n"/>
-      <c r="G146" s="40" t="inlineStr">
+      <c r="E194" s="40" t="n"/>
+      <c r="F194" s="40" t="n"/>
+      <c r="G194" s="40" t="inlineStr">
         <is>
           <t>Customer and Interested party receive the correct email templates</t>
         </is>
       </c>
-      <c r="AG146" t="inlineStr">
+      <c r="AG194" t="inlineStr">
         <is>
           <t>CFSUITE-CN-001</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="41" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="41" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B147" s="41" t="inlineStr">
+      <c r="B195" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-078</t>
         </is>
       </c>
-      <c r="C147" s="41" t="inlineStr">
+      <c r="C195" s="41" t="inlineStr">
         <is>
           <t>Automated SMS notification</t>
         </is>
       </c>
-      <c r="D147" s="41" t="inlineStr">
+      <c r="D195" s="41" t="inlineStr">
         <is>
           <t>Ability to send automated SMS on Case status updates to: . Customer submitting a request . An interested party Both receiving their own unique SMS template</t>
         </is>
       </c>
-      <c r="E147" s="41" t="n"/>
-      <c r="F147" s="41" t="n"/>
-      <c r="G147" s="41" t="inlineStr">
+      <c r="E195" s="41" t="n"/>
+      <c r="F195" s="41" t="n"/>
+      <c r="G195" s="41" t="inlineStr">
         <is>
           <t>Customer and Interested party receive the correct sms templates</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AG195" t="inlineStr">
         <is>
           <t>CFSUITE-CN-002</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="40" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="40" t="inlineStr">
         <is>
           <t>Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B148" s="40" t="inlineStr">
+      <c r="B196" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-079</t>
         </is>
       </c>
-      <c r="C148" s="40" t="inlineStr">
+      <c r="C196" s="40" t="inlineStr">
         <is>
           <t>Ad hoc email and SMS notifications</t>
         </is>
       </c>
-      <c r="D148" s="40" t="n"/>
-      <c r="E148" s="40" t="inlineStr">
+      <c r="D196" s="40" t="n"/>
+      <c r="E196" s="40" t="inlineStr">
         <is>
           <t>Create a case with your own customer record. Add a interested party. Move the case through the statuses.</t>
         </is>
       </c>
-      <c r="F148" s="40" t="n"/>
-      <c r="G148" s="40" t="inlineStr">
+      <c r="F196" s="40" t="n"/>
+      <c r="G196" s="40" t="inlineStr">
         <is>
           <t>Email is received SMS is received Intereaction for both are recorded in the activity timeline</t>
         </is>
       </c>
-      <c r="AG148" t="inlineStr">
+      <c r="AG196" t="inlineStr">
         <is>
           <t>CFSUITE-CN-003</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="42" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="42" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B149" s="42" t="n"/>
-      <c r="C149" s="42" t="n"/>
-      <c r="D149" s="42" t="n"/>
-      <c r="E149" s="42" t="n"/>
-      <c r="F149" s="42" t="n"/>
-      <c r="G149" s="42" t="n"/>
-    </row>
-    <row r="150" ht="72" customHeight="1">
-      <c r="A150" s="43" t="inlineStr">
+      <c r="B197" s="42" t="n"/>
+      <c r="C197" s="42" t="n"/>
+      <c r="D197" s="42" t="n"/>
+      <c r="E197" s="42" t="n"/>
+      <c r="F197" s="42" t="n"/>
+      <c r="G197" s="42" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B150" s="43" t="inlineStr">
+      <c r="B198" s="43" t="inlineStr">
         <is>
           <t>PROP-020</t>
         </is>
       </c>
-      <c r="C150" s="43" t="inlineStr">
+      <c r="C198" s="43" t="inlineStr">
         <is>
           <t>View Inbox Messages</t>
         </is>
       </c>
-      <c r="D150" s="43" t="inlineStr">
+      <c r="D198" s="43" t="inlineStr">
         <is>
           <t>User sees a list of incoming messages/notifications in their community inbox</t>
         </is>
       </c>
-      <c r="E150" s="43" t="inlineStr">
+      <c r="E198" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Inbox'
@@ -6509,44 +8163,44 @@
 5. Verify message content renders correctly</t>
         </is>
       </c>
-      <c r="F150" s="43" t="inlineStr">
+      <c r="F198" s="43" t="inlineStr">
         <is>
           <t>User must have at least one cfsuite1__CFSuite_Inbox_Message__c record</t>
         </is>
       </c>
-      <c r="G150" s="43" t="inlineStr">
+      <c r="G198" s="43" t="inlineStr">
         <is>
           <t>cfsuite_MyInboxController / MyInboxControllerQueryHelperClass returns messages for logged-in user; unread count badge displays correctly; message body renders HTML content</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
+      <c r="AG198" t="inlineStr">
         <is>
           <t>CFSUITE-CN-004</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="72" customHeight="1">
-      <c r="A151" s="43" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B151" s="43" t="inlineStr">
+      <c r="B199" s="43" t="inlineStr">
         <is>
           <t>PROP-021</t>
         </is>
       </c>
-      <c r="C151" s="43" t="inlineStr">
+      <c r="C199" s="43" t="inlineStr">
         <is>
           <t>Message Folder Organisation</t>
         </is>
       </c>
-      <c r="D151" s="43" t="inlineStr">
+      <c r="D199" s="43" t="inlineStr">
         <is>
           <t>Messages can be moved between folders and folder counts update accordingly</t>
         </is>
       </c>
-      <c r="E151" s="43" t="inlineStr">
+      <c r="E199" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'My Inbox'
@@ -6555,44 +8209,44 @@
 5. Verify message appears in target folder and is removed from Inbox</t>
         </is>
       </c>
-      <c r="F151" s="43" t="inlineStr">
+      <c r="F199" s="43" t="inlineStr">
         <is>
           <t>At least one existing inbox message; at least two folders available</t>
         </is>
       </c>
-      <c r="G151" s="43" t="inlineStr">
+      <c r="G199" s="43" t="inlineStr">
         <is>
           <t>CFSuiteMessageFolderController updates cfsuite1__CFSuite_Message_Folder__c lookup on message; folder message counts reflect change</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr">
+      <c r="AG199" t="inlineStr">
         <is>
           <t>CFSUITE-CN-005</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" s="43" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B152" s="43" t="inlineStr">
+      <c r="B200" s="43" t="inlineStr">
         <is>
           <t>PROP-039</t>
         </is>
       </c>
-      <c r="C152" s="43" t="inlineStr">
+      <c r="C200" s="43" t="inlineStr">
         <is>
           <t>Customer Email Notification on Case Creation</t>
         </is>
       </c>
-      <c r="D152" s="43" t="inlineStr">
+      <c r="D200" s="43" t="inlineStr">
         <is>
           <t>When a case is created with a contact email, an acknowledgement email is sent to the customer</t>
         </is>
       </c>
-      <c r="E152" s="43" t="inlineStr">
+      <c r="E200" s="43" t="inlineStr">
         <is>
           <t>1. Create a new case with a Contact that has a valid email address
 2. Save the case
@@ -6601,44 +8255,44 @@
 5. Verify recipient email matches contact email</t>
         </is>
       </c>
-      <c r="F152" s="43" t="inlineStr">
+      <c r="F200" s="43" t="inlineStr">
         <is>
           <t>Case with Contact email=test@testcouncil.gov.au, Enable_Staff_Notifications_Create=true on Request Flow</t>
         </is>
       </c>
-      <c r="G152" s="43" t="inlineStr">
+      <c r="G200" s="43" t="inlineStr">
         <is>
           <t>CommsEventHandler fires on case create; Message_Queue__c record created with correct recipient; ScheduleMessageProcessing dispatches email; no error in CommsSettingsEvaluator</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
+      <c r="AG200" t="inlineStr">
         <is>
           <t>CFSUITE-CN-006</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="72" customHeight="1">
-      <c r="A153" s="43" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B153" s="43" t="inlineStr">
+      <c r="B201" s="43" t="inlineStr">
         <is>
           <t>PROP-040</t>
         </is>
       </c>
-      <c r="C153" s="43" t="inlineStr">
+      <c r="C201" s="43" t="inlineStr">
         <is>
           <t>SMS Notification Sent on Case Status Change</t>
         </is>
       </c>
-      <c r="D153" s="43" t="inlineStr">
+      <c r="D201" s="43" t="inlineStr">
         <is>
           <t>When a case is updated and the customer has SMS notification preference, an SMS is queued</t>
         </is>
       </c>
-      <c r="E153" s="43" t="inlineStr">
+      <c r="E201" s="43" t="inlineStr">
         <is>
           <t>1. Create/find a case where the contact has a mobile number and notification preference = Phone
 2. Update the case status
@@ -6646,44 +8300,44 @@
 4. Verify SMS content includes case number and new status</t>
         </is>
       </c>
-      <c r="F153" s="43" t="inlineStr">
+      <c r="F201" s="43" t="inlineStr">
         <is>
           <t>Contact with MobilePhone populated, case cfsuite1__Advise_Your_Preferred_Contact__c=Phone</t>
         </is>
       </c>
-      <c r="G153" s="43" t="inlineStr">
+      <c r="G201" s="43" t="inlineStr">
         <is>
           <t>SMSMessageUtility creates SMS message in Message_Queue__c; SMSMessageTriggerHandler executes; SmsInfo object populated with correct mobile number and case reference</t>
         </is>
       </c>
-      <c r="AG153" t="inlineStr">
+      <c r="AG201" t="inlineStr">
         <is>
           <t>CFSUITE-CN-007</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="43" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="43" t="inlineStr">
         <is>
           <t>Proposed - Communications &amp; Notifications</t>
         </is>
       </c>
-      <c r="B154" s="43" t="inlineStr">
+      <c r="B202" s="43" t="inlineStr">
         <is>
           <t>PROP-041</t>
         </is>
       </c>
-      <c r="C154" s="43" t="inlineStr">
+      <c r="C202" s="43" t="inlineStr">
         <is>
           <t>Emergency Notification - After Hours</t>
         </is>
       </c>
-      <c r="D154" s="43" t="inlineStr">
+      <c r="D202" s="43" t="inlineStr">
         <is>
           <t>A case flagged as Emergency triggers an after-hours notification to the configured recipient</t>
         </is>
       </c>
-      <c r="E154" s="43" t="inlineStr">
+      <c r="E202" s="43" t="inlineStr">
         <is>
           <t>1. Create a case with category where Emergency_Notification=Yes on Request Flow
 2. Save the case
@@ -6691,240 +8345,306 @@
 4. Check Message Queue for after-hours alert record</t>
         </is>
       </c>
-      <c r="F154" s="43" t="inlineStr">
+      <c r="F202" s="43" t="inlineStr">
         <is>
           <t>Category with Emergency_Notification=Yes and Notify_After_Hours email configured</t>
         </is>
       </c>
-      <c r="G154" s="43" t="inlineStr">
+      <c r="G202" s="43" t="inlineStr">
         <is>
           <t>EmergencyCommsSettingEvaluator fires; after-hours email queued in Message_Queue__c; notification clearly identified as emergency; contact details included in message</t>
         </is>
       </c>
-      <c r="AG154" t="inlineStr">
+      <c r="AG202" t="inlineStr">
         <is>
           <t>CFSUITE-CN-008</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="42" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Proposed - Communications &amp; Notifications</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PROP-067-CN</t>
+        </is>
+      </c>
+      <c r="C203" s="48" t="inlineStr">
+        <is>
+          <t>My Local Gov inbox returns and marks messages read</t>
+        </is>
+      </c>
+      <c r="D203" s="48" t="inlineStr">
+        <is>
+          <t>On the My Local Gov portal, navigating to the Inbox shows existing messages with correct unread state; clicking a message marks it read both in the portal and the internal view.
+Source: Release 3.154 (36042)</t>
+        </is>
+      </c>
+      <c r="G203" s="48" t="inlineStr">
+        <is>
+          <t>Messages returned in Inbox; unread indicator matches IsRead on the backing record; click toggles to read state.</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Proposed - Communications &amp; Notifications</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PROP-068-CN</t>
+        </is>
+      </c>
+      <c r="C204" s="48" t="inlineStr">
+        <is>
+          <t>My Local Gov create folder and move messages between folders</t>
+        </is>
+      </c>
+      <c r="D204" s="48" t="inlineStr">
+        <is>
+          <t>User creates a new folder under Inbox; drags a message from Inbox to the new folder; the message moves between folders correctly.
+Source: Release 3.154 (36042)</t>
+        </is>
+      </c>
+      <c r="G204" s="48" t="inlineStr">
+        <is>
+          <t>New folder is created and visible; message moves out of Inbox into the new folder; both views reflect the move.</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>CFSUITE-CN-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="42" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B155" s="42" t="n"/>
-      <c r="C155" s="42" t="n"/>
-      <c r="D155" s="42" t="n"/>
-      <c r="E155" s="42" t="n"/>
-      <c r="F155" s="42" t="n"/>
-      <c r="G155" s="42" t="n"/>
-    </row>
-    <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="40" t="inlineStr">
+      <c r="B205" s="42" t="n"/>
+      <c r="C205" s="42" t="n"/>
+      <c r="D205" s="42" t="n"/>
+      <c r="E205" s="42" t="n"/>
+      <c r="F205" s="42" t="n"/>
+      <c r="G205" s="42" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B156" s="40" t="inlineStr">
+      <c r="B206" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-109</t>
         </is>
       </c>
-      <c r="C156" s="40" t="inlineStr">
+      <c r="C206" s="40" t="inlineStr">
         <is>
           <t>Personalised Councillor Interface</t>
         </is>
       </c>
-      <c r="D156" s="40" t="inlineStr">
+      <c r="D206" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to have a personalised councillor interface when logging into the portal</t>
         </is>
       </c>
-      <c r="E156" s="40" t="n"/>
-      <c r="F156" s="40" t="n"/>
-      <c r="G156" s="40" t="inlineStr">
+      <c r="E206" s="40" t="n"/>
+      <c r="F206" s="40" t="n"/>
+      <c r="G206" s="40" t="inlineStr">
         <is>
           <t>1. Councillor sees additional functionality such as All Questions and My questions</t>
         </is>
       </c>
-      <c r="AG156" t="inlineStr">
+      <c r="AG206" t="inlineStr">
         <is>
           <t>CFSUITE-CP-001</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="24" customHeight="1">
-      <c r="A157" s="41" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="41" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B157" s="41" t="inlineStr">
+      <c r="B207" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-110</t>
         </is>
       </c>
-      <c r="C157" s="41" t="inlineStr">
+      <c r="C207" s="41" t="inlineStr">
         <is>
           <t>Standard Request Portal Features for councillor</t>
         </is>
       </c>
-      <c r="D157" s="41" t="inlineStr">
+      <c r="D207" s="41" t="inlineStr">
         <is>
           <t>The Councillor portal shall include all the standard features available in the CFSuite Request portal</t>
         </is>
       </c>
-      <c r="E157" s="41" t="n"/>
-      <c r="F157" s="41" t="n"/>
-      <c r="G157" s="41" t="inlineStr">
+      <c r="E207" s="41" t="n"/>
+      <c r="F207" s="41" t="n"/>
+      <c r="G207" s="41" t="inlineStr">
         <is>
           <t>1. Councillor sees Standard portal functionality</t>
         </is>
       </c>
-      <c r="AG157" t="inlineStr">
+      <c r="AG207" t="inlineStr">
         <is>
           <t>CFSUITE-CP-002</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="36" customHeight="1">
-      <c r="A158" s="40" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B158" s="40" t="inlineStr">
+      <c r="B208" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-111</t>
         </is>
       </c>
-      <c r="C158" s="40" t="inlineStr">
+      <c r="C208" s="40" t="inlineStr">
         <is>
           <t>Submit Councillor Questions</t>
         </is>
       </c>
-      <c r="D158" s="40" t="inlineStr">
+      <c r="D208" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to submit councillor questions through the portal</t>
         </is>
       </c>
-      <c r="E158" s="40" t="n"/>
-      <c r="F158" s="40" t="n"/>
-      <c r="G158" s="40" t="inlineStr">
+      <c r="E208" s="40" t="n"/>
+      <c r="F208" s="40" t="n"/>
+      <c r="G208" s="40" t="inlineStr">
         <is>
           <t>1. Check the Councillor Question is created correctly</t>
         </is>
       </c>
-      <c r="AG158" t="inlineStr">
+      <c r="AG208" t="inlineStr">
         <is>
           <t>CFSUITE-CP-003</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="41" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="41" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B159" s="41" t="inlineStr">
+      <c r="B209" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-112</t>
         </is>
       </c>
-      <c r="C159" s="41" t="inlineStr">
+      <c r="C209" s="41" t="inlineStr">
         <is>
           <t>View and Filter All Councillor Questions</t>
         </is>
       </c>
-      <c r="D159" s="41" t="inlineStr">
+      <c r="D209" s="41" t="inlineStr">
         <is>
           <t>Ability for Councillors to view the questions and answers of councillor questions for: a. Their own questions b. All other councillor questions</t>
         </is>
       </c>
-      <c r="E159" s="41" t="n"/>
-      <c r="F159" s="41" t="n"/>
-      <c r="G159" s="41" t="inlineStr">
+      <c r="E209" s="41" t="n"/>
+      <c r="F209" s="41" t="n"/>
+      <c r="G209" s="41" t="inlineStr">
         <is>
           <t>1. Check that you can see other councillor's requests 2. Check you can filter on the All Questions by Councillor and Status</t>
         </is>
       </c>
-      <c r="AG159" t="inlineStr">
+      <c r="AG209" t="inlineStr">
         <is>
           <t>CFSUITE-CP-004</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="40" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="40" t="inlineStr">
         <is>
           <t>Councillor Portal</t>
         </is>
       </c>
-      <c r="B160" s="40" t="inlineStr">
+      <c r="B210" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-113</t>
         </is>
       </c>
-      <c r="C160" s="40" t="inlineStr">
+      <c r="C210" s="40" t="inlineStr">
         <is>
           <t>Log a request for on behalf of resident</t>
         </is>
       </c>
-      <c r="D160" s="40" t="inlineStr">
+      <c r="D210" s="40" t="inlineStr">
         <is>
           <t>Ability for a Councillor to log a request on behalf of a resident</t>
         </is>
       </c>
-      <c r="E160" s="40" t="n"/>
-      <c r="F160" s="40" t="n"/>
-      <c r="G160" s="40" t="inlineStr">
+      <c r="E210" s="40" t="n"/>
+      <c r="F210" s="40" t="n"/>
+      <c r="G210" s="40" t="inlineStr">
         <is>
           <t>1. Check the request is created with the additional information about who requested it.</t>
         </is>
       </c>
-      <c r="AG160" t="inlineStr">
+      <c r="AG210" t="inlineStr">
         <is>
           <t>CFSUITE-CP-005</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="84" customHeight="1">
-      <c r="A161" s="42" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="42" t="inlineStr">
         <is>
           <t>Proposed - Councillor Portal</t>
         </is>
       </c>
-      <c r="B161" s="42" t="n"/>
-      <c r="C161" s="42" t="n"/>
-      <c r="D161" s="42" t="n"/>
-      <c r="E161" s="42" t="n"/>
-      <c r="F161" s="42" t="n"/>
-      <c r="G161" s="42" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="43" t="inlineStr">
+      <c r="B211" s="42" t="n"/>
+      <c r="C211" s="42" t="n"/>
+      <c r="D211" s="42" t="n"/>
+      <c r="E211" s="42" t="n"/>
+      <c r="F211" s="42" t="n"/>
+      <c r="G211" s="42" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="43" t="inlineStr">
         <is>
           <t>Proposed - Councillor Portal</t>
         </is>
       </c>
-      <c r="B162" s="43" t="inlineStr">
+      <c r="B212" s="43" t="inlineStr">
         <is>
           <t>PROP-049</t>
         </is>
       </c>
-      <c r="C162" s="43" t="inlineStr">
+      <c r="C212" s="43" t="inlineStr">
         <is>
           <t>Create Councillor Question Case</t>
         </is>
       </c>
-      <c r="D162" s="43" t="inlineStr">
+      <c r="D212" s="43" t="inlineStr">
         <is>
           <t>A case with Record Type 'Councillor Question' is created and routed to the correct queue</t>
         </is>
       </c>
-      <c r="E162" s="43" t="inlineStr">
+      <c r="E212" s="43" t="inlineStr">
         <is>
           <t>1. Log in as internal staff
 2. Create a new Case
@@ -6935,182 +8655,182 @@
 7. Verify case visible in Councillor Question list view</t>
         </is>
       </c>
-      <c r="F162" s="43" t="inlineStr">
+      <c r="F212" s="43" t="inlineStr">
         <is>
           <t>Subject=Councillor query about drainage on Elm St, Contact=test councillor contact</t>
         </is>
       </c>
-      <c r="G162" s="43" t="inlineStr">
+      <c r="G212" s="43" t="inlineStr">
         <is>
           <t>Case RecordType=Councillor_Question; CaseTriggerOperation assigns to configured queue; case appears in Councillor Question list view; notification sent to responsible officer</t>
         </is>
       </c>
-      <c r="AG162" t="inlineStr">
+      <c r="AG212" t="inlineStr">
         <is>
           <t>CFSUITE-CP-006</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="24" customHeight="1">
-      <c r="A163" s="42" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="42" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B163" s="42" t="n"/>
-      <c r="C163" s="42" t="n"/>
-      <c r="D163" s="42" t="n"/>
-      <c r="E163" s="42" t="n"/>
-      <c r="F163" s="42" t="n"/>
-      <c r="G163" s="42" t="n"/>
-    </row>
-    <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="40" t="inlineStr">
+      <c r="B213" s="42" t="n"/>
+      <c r="C213" s="42" t="n"/>
+      <c r="D213" s="42" t="n"/>
+      <c r="E213" s="42" t="n"/>
+      <c r="F213" s="42" t="n"/>
+      <c r="G213" s="42" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="40" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B164" s="40" t="inlineStr">
+      <c r="B214" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-120</t>
         </is>
       </c>
-      <c r="C164" s="40" t="inlineStr">
+      <c r="C214" s="40" t="inlineStr">
         <is>
           <t>Create Knowledge Article</t>
         </is>
       </c>
-      <c r="D164" s="40" t="n"/>
-      <c r="E164" s="40" t="inlineStr">
+      <c r="D214" s="40" t="n"/>
+      <c r="E214" s="40" t="inlineStr">
         <is>
           <t>https://scribehow.com/shared/Configure_a_Dynamic_Knowledge_Article__jX58ZzIuQdetSLJFfS5JAg</t>
         </is>
       </c>
-      <c r="F164" s="40" t="n"/>
-      <c r="G164" s="40" t="n"/>
-      <c r="AG164" t="inlineStr">
+      <c r="F214" s="40" t="n"/>
+      <c r="G214" s="40" t="n"/>
+      <c r="AG214" t="inlineStr">
         <is>
           <t>CFSUITE-CA-001</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="24" customHeight="1">
-      <c r="A165" s="41" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="41" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B165" s="41" t="inlineStr">
+      <c r="B215" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-121</t>
         </is>
       </c>
-      <c r="C165" s="41" t="inlineStr">
+      <c r="C215" s="41" t="inlineStr">
         <is>
           <t>View knowledge articles when creating requests</t>
         </is>
       </c>
-      <c r="D165" s="41" t="n"/>
-      <c r="E165" s="41" t="inlineStr">
+      <c r="D215" s="41" t="n"/>
+      <c r="E215" s="41" t="inlineStr">
         <is>
           <t>https://scribehow.com/shared/Configure_a_Dynamic_Knowledge_Article__jX58ZzIuQdetSLJFfS5JAg</t>
         </is>
       </c>
-      <c r="F165" s="41" t="n"/>
-      <c r="G165" s="41" t="n"/>
-      <c r="AG165" t="inlineStr">
+      <c r="F215" s="41" t="n"/>
+      <c r="G215" s="41" t="n"/>
+      <c r="AG215" t="inlineStr">
         <is>
           <t>CFSUITE-CA-002</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="40" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="40" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B166" s="40" t="inlineStr">
+      <c r="B216" s="40" t="inlineStr">
         <is>
           <t>CoM-Test-122</t>
         </is>
       </c>
-      <c r="C166" s="40" t="inlineStr">
+      <c r="C216" s="40" t="inlineStr">
         <is>
           <t>Create salesforce users through active directory</t>
         </is>
       </c>
-      <c r="D166" s="40" t="n"/>
-      <c r="E166" s="40" t="n"/>
-      <c r="F166" s="40" t="n"/>
-      <c r="G166" s="40" t="n"/>
-      <c r="AG166" t="inlineStr">
+      <c r="D216" s="40" t="n"/>
+      <c r="E216" s="40" t="n"/>
+      <c r="F216" s="40" t="n"/>
+      <c r="G216" s="40" t="n"/>
+      <c r="AG216" t="inlineStr">
         <is>
           <t>CFSUITE-CA-003</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="41" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="41" t="inlineStr">
         <is>
           <t>Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B167" s="41" t="inlineStr">
+      <c r="B217" s="41" t="inlineStr">
         <is>
           <t>CoM-Test-123</t>
         </is>
       </c>
-      <c r="C167" s="41" t="inlineStr">
+      <c r="C217" s="41" t="inlineStr">
         <is>
           <t>Create admin accounts with MFA</t>
         </is>
       </c>
-      <c r="D167" s="41" t="n"/>
-      <c r="E167" s="41" t="n"/>
-      <c r="F167" s="41" t="n"/>
-      <c r="G167" s="41" t="n"/>
-      <c r="AG167" t="inlineStr">
+      <c r="D217" s="41" t="n"/>
+      <c r="E217" s="41" t="n"/>
+      <c r="F217" s="41" t="n"/>
+      <c r="G217" s="41" t="n"/>
+      <c r="AG217" t="inlineStr">
         <is>
           <t>CFSUITE-CA-004</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="72" customHeight="1">
-      <c r="A168" s="42" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="42" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B168" s="42" t="n"/>
-      <c r="C168" s="42" t="n"/>
-      <c r="D168" s="42" t="n"/>
-      <c r="E168" s="42" t="n"/>
-      <c r="F168" s="42" t="n"/>
-      <c r="G168" s="42" t="n"/>
-    </row>
-    <row r="169" ht="72" customHeight="1">
-      <c r="A169" s="43" t="inlineStr">
+      <c r="B218" s="42" t="n"/>
+      <c r="C218" s="42" t="n"/>
+      <c r="D218" s="42" t="n"/>
+      <c r="E218" s="42" t="n"/>
+      <c r="F218" s="42" t="n"/>
+      <c r="G218" s="42" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B169" s="43" t="inlineStr">
+      <c r="B219" s="43" t="inlineStr">
         <is>
           <t>PROP-035</t>
         </is>
       </c>
-      <c r="C169" s="43" t="inlineStr">
+      <c r="C219" s="43" t="inlineStr">
         <is>
           <t>Display Category Visible in Community</t>
         </is>
       </c>
-      <c r="D169" s="43" t="inlineStr">
+      <c r="D219" s="43" t="inlineStr">
         <is>
           <t>A Display Category Request Flow record with Is_Hidden_From_Community=false appears in the community category list</t>
         </is>
       </c>
-      <c r="E169" s="43" t="inlineStr">
+      <c r="E219" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request'
@@ -7118,44 +8838,44 @@
 4. Verify categories with Is_Hidden_From_Community=true do NOT appear</t>
         </is>
       </c>
-      <c r="F169" s="43" t="inlineStr">
+      <c r="F219" s="43" t="inlineStr">
         <is>
           <t>At least one Display Category record with Is_Hidden_From_Community=false and one with =true</t>
         </is>
       </c>
-      <c r="G169" s="43" t="inlineStr">
+      <c r="G219" s="43" t="inlineStr">
         <is>
           <t>CommunityUserRequestFlowHelperClass filters correctly; hidden categories absent from list; category icons (Pin_Image) render from static resource</t>
         </is>
       </c>
-      <c r="AG169" t="inlineStr">
+      <c r="AG219" t="inlineStr">
         <is>
           <t>CFSUITE-CA-005</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" s="43" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B170" s="43" t="inlineStr">
+      <c r="B220" s="43" t="inlineStr">
         <is>
           <t>PROP-036</t>
         </is>
       </c>
-      <c r="C170" s="43" t="inlineStr">
+      <c r="C220" s="43" t="inlineStr">
         <is>
           <t>Category Search / Filter in Community</t>
         </is>
       </c>
-      <c r="D170" s="43" t="inlineStr">
+      <c r="D220" s="43" t="inlineStr">
         <is>
           <t>User can search for a category by keyword and results filter to matching categories</t>
         </is>
       </c>
-      <c r="E170" s="43" t="inlineStr">
+      <c r="E220" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Navigate to 'Make a Request'
@@ -7164,44 +8884,44 @@
 5. Clear the search and verify full category list returns</t>
         </is>
       </c>
-      <c r="F170" s="43" t="inlineStr">
+      <c r="F220" s="43" t="inlineStr">
         <is>
           <t>searchTerm=dog (should match multiple Animals categories)</t>
         </is>
       </c>
-      <c r="G170" s="43" t="inlineStr">
+      <c r="G220" s="43" t="inlineStr">
         <is>
           <t>Category search filters against category Name and cfsuite1__Search_Tag__c field; results update in real-time or on submit; no search returns full list</t>
         </is>
       </c>
-      <c r="AG170" t="inlineStr">
+      <c r="AG220" t="inlineStr">
         <is>
           <t>CFSUITE-CA-006</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" s="43" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B171" s="43" t="inlineStr">
+      <c r="B221" s="43" t="inlineStr">
         <is>
           <t>PROP-037</t>
         </is>
       </c>
-      <c r="C171" s="43" t="inlineStr">
+      <c r="C221" s="43" t="inlineStr">
         <is>
           <t>Deflection Journey - Category with Deflection Text</t>
         </is>
       </c>
-      <c r="D171" s="43" t="inlineStr">
+      <c r="D221" s="43" t="inlineStr">
         <is>
           <t>Selecting a category with Form_Type=Deflection shows informational text instead of a submission form</t>
         </is>
       </c>
-      <c r="E171" s="43" t="inlineStr">
+      <c r="E221" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category configured with Form_Type=Deflection
@@ -7209,44 +8929,44 @@
 4. Verify no case is created</t>
         </is>
       </c>
-      <c r="F171" s="43" t="inlineStr">
+      <c r="F221" s="43" t="inlineStr">
         <is>
           <t>A Display Category with Form_Type=Deflection and Deflection_Text populated</t>
         </is>
       </c>
-      <c r="G171" s="43" t="inlineStr">
+      <c r="G221" s="43" t="inlineStr">
         <is>
           <t>LWC renders Deflection_Text__c content; no Case record created; user presented with alternate resolution information (e.g. external link or phone number)</t>
         </is>
       </c>
-      <c r="AG171" t="inlineStr">
+      <c r="AG221" t="inlineStr">
         <is>
           <t>CFSUITE-CA-007</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="48" customHeight="1">
-      <c r="A172" s="43" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B172" s="43" t="inlineStr">
+      <c r="B222" s="43" t="inlineStr">
         <is>
           <t>PROP-050</t>
         </is>
       </c>
-      <c r="C172" s="43" t="inlineStr">
+      <c r="C222" s="43" t="inlineStr">
         <is>
           <t>Knowledge Article Surfaced in Community Category Journey</t>
         </is>
       </c>
-      <c r="D172" s="43" t="inlineStr">
+      <c r="D222" s="43" t="inlineStr">
         <is>
           <t>Relevant knowledge articles are presented to community users during the category journey before submission</t>
         </is>
       </c>
-      <c r="E172" s="43" t="inlineStr">
+      <c r="E222" s="43" t="inlineStr">
         <is>
           <t>1. Log in to community portal
 2. Select a category that has linked CFSuite_Article records
@@ -7254,44 +8974,44 @@
 4. Click an article link and verify it opens the full article</t>
         </is>
       </c>
-      <c r="F172" s="43" t="inlineStr">
+      <c r="F222" s="43" t="inlineStr">
         <is>
           <t>Category with linked cfsuite1__CFSuite_Article__c records</t>
         </is>
       </c>
-      <c r="G172" s="43" t="inlineStr">
+      <c r="G222" s="43" t="inlineStr">
         <is>
           <t>KnowledgeController returns articles matching the selected category; articles rendered in community LWC component; article click navigates correctly; deflection rate trackable</t>
         </is>
       </c>
-      <c r="AG172" t="inlineStr">
+      <c r="AG222" t="inlineStr">
         <is>
           <t>CFSUITE-CA-008</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="84" customHeight="1">
-      <c r="A173" s="43" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B173" s="43" t="inlineStr">
+      <c r="B223" s="43" t="inlineStr">
         <is>
           <t>PROP-051</t>
         </is>
       </c>
-      <c r="C173" s="43" t="inlineStr">
+      <c r="C223" s="43" t="inlineStr">
         <is>
           <t>Dynamic Banner Displays on Community Home</t>
         </is>
       </c>
-      <c r="D173" s="43" t="inlineStr">
+      <c r="D223" s="43" t="inlineStr">
         <is>
           <t>Active dynamic banner content is displayed on the community portal home page</t>
         </is>
       </c>
-      <c r="E173" s="43" t="inlineStr">
+      <c r="E223" s="43" t="inlineStr">
         <is>
           <t>1. Ensure at least one active banner is configured
 2. Log in (or browse as guest) to community portal home page
@@ -7299,44 +9019,44 @@
 4. Verify expired or inactive banners are NOT shown</t>
         </is>
       </c>
-      <c r="F173" s="43" t="inlineStr">
+      <c r="F223" s="43" t="inlineStr">
         <is>
           <t>Active banner record in community settings</t>
         </is>
       </c>
-      <c r="G173" s="43" t="inlineStr">
+      <c r="G223" s="43" t="inlineStr">
         <is>
           <t>DynamicBannerController returns active banner(s); banner renders in designated LWC slot on home page; expired banners filtered out by date</t>
         </is>
       </c>
-      <c r="AG173" t="inlineStr">
+      <c r="AG223" t="inlineStr">
         <is>
           <t>CFSUITE-CA-009</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="84" customHeight="1">
-      <c r="A174" s="43" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B174" s="43" t="inlineStr">
+      <c r="B224" s="43" t="inlineStr">
         <is>
           <t>PROP-056</t>
         </is>
       </c>
-      <c r="C174" s="43" t="inlineStr">
+      <c r="C224" s="43" t="inlineStr">
         <is>
           <t>CFSuite Settings - Integration Settings Persist</t>
         </is>
       </c>
-      <c r="D174" s="43" t="inlineStr">
+      <c r="D224" s="43" t="inlineStr">
         <is>
           <t>Admin can update CFSuite integration settings and the values are reflected in system behaviour</t>
         </is>
       </c>
-      <c r="E174" s="43" t="inlineStr">
+      <c r="E224" s="43" t="inlineStr">
         <is>
           <t>1. Log in as system administrator
 2. Navigate to CFSuite Integration Settings (cfsuite1__CFSuiteIntegrationSettings__c)
@@ -7345,44 +9065,44 @@
 5. Verify the CFSuiteIntegrationSettings Apex class returns the updated value</t>
         </is>
       </c>
-      <c r="F174" s="43" t="inlineStr">
+      <c r="F224" s="43" t="inlineStr">
         <is>
           <t>Any non-critical integration setting field</t>
         </is>
       </c>
-      <c r="G174" s="43" t="inlineStr">
+      <c r="G224" s="43" t="inlineStr">
         <is>
           <t>CFSuiteSettings / CFSuiteSettingsUtility Apex classes read updated value; no caching issues; setting change does not require org restart</t>
         </is>
       </c>
-      <c r="AG174" t="inlineStr">
+      <c r="AG224" t="inlineStr">
         <is>
           <t>CFSUITE-CA-010</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="72" customHeight="1">
-      <c r="A175" s="43" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B175" s="43" t="inlineStr">
+      <c r="B225" s="43" t="inlineStr">
         <is>
           <t>PROP-057</t>
         </is>
       </c>
-      <c r="C175" s="43" t="inlineStr">
+      <c r="C225" s="43" t="inlineStr">
         <is>
           <t>Batch Settings - Entitlement Update Scheduled Job</t>
         </is>
       </c>
-      <c r="D175" s="43" t="inlineStr">
+      <c r="D225" s="43" t="inlineStr">
         <is>
           <t>The scheduled entitlement update batch job runs successfully and updates overdue entitlements</t>
         </is>
       </c>
-      <c r="E175" s="43" t="inlineStr">
+      <c r="E225" s="43" t="inlineStr">
         <is>
           <t>1. Log in as system administrator
 2. Verify ScheduleEntitlementUpdate is scheduled via Scheduled Jobs
@@ -7391,44 +9111,44 @@
 5. Verify no Apex errors in the job log</t>
         </is>
       </c>
-      <c r="F175" s="43" t="inlineStr">
+      <c r="F225" s="43" t="inlineStr">
         <is>
           <t>Cases with milestone-driven entitlement processes and overdue milestones</t>
         </is>
       </c>
-      <c r="G175" s="43" t="inlineStr">
+      <c r="G225" s="43" t="inlineStr">
         <is>
           <t>ScheduleEntitlementUpdate batch executes without Apex exceptions; CaseMilestone IsCompleted updated for resolved cases; Batch_Settings__c configuration respected (batch size)</t>
         </is>
       </c>
-      <c r="AG175" t="inlineStr">
+      <c r="AG225" t="inlineStr">
         <is>
           <t>CFSUITE-CA-011</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="43" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="43" t="inlineStr">
         <is>
           <t>Proposed - Configuration &amp; Administration</t>
         </is>
       </c>
-      <c r="B176" s="43" t="inlineStr">
+      <c r="B226" s="43" t="inlineStr">
         <is>
           <t>PROP-058</t>
         </is>
       </c>
-      <c r="C176" s="43" t="inlineStr">
+      <c r="C226" s="43" t="inlineStr">
         <is>
           <t>MLG Community Link - Cross-Org Case Visibility</t>
         </is>
       </c>
-      <c r="D176" s="43" t="inlineStr">
+      <c r="D226" s="43" t="inlineStr">
         <is>
           <t>A case shared via MLG Community Link is visible to the linked partner council portal user</t>
         </is>
       </c>
-      <c r="E176" s="43" t="inlineStr">
+      <c r="E226" s="43" t="inlineStr">
         <is>
           <t>1. Create a case in the primary council org
 2. Create a CFSuite_MLG_Community_Link__c record linking the case to a partner council
@@ -7437,17 +9157,17 @@
 5. Verify case detail (but not restricted fields) is accessible</t>
         </is>
       </c>
-      <c r="F176" s="43" t="inlineStr">
+      <c r="F226" s="43" t="inlineStr">
         <is>
           <t>Two council orgs configured with MLG integration; test case in primary org</t>
         </is>
       </c>
-      <c r="G176" s="43" t="inlineStr">
+      <c r="G226" s="43" t="inlineStr">
         <is>
           <t>CommunityUserMLGQueryHelperClass returns linked cases; cfsuite1__CFSuite_MLG_Community_Link__c record drives visibility; confidential fields suppressed in cross-org view</t>
         </is>
       </c>
-      <c r="AG176" t="inlineStr">
+      <c r="AG226" t="inlineStr">
         <is>
           <t>CFSUITE-CA-012</t>
         </is>

--- a/documentation/Automated Testing CFSuite.xlsx
+++ b/documentation/Automated Testing CFSuite.xlsx
@@ -2412,11 +2412,6 @@
           <t>CFSUITE-AU-031</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-001_create_case_with_location.robot</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="135" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -2481,11 +2476,6 @@
       <c r="AG37" t="inlineStr">
         <is>
           <t>CFSUITE-AU-033</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-003_create_case_from_account.robot</t>
         </is>
       </c>
     </row>
@@ -2582,6 +2572,11 @@
           <t>CFSUITE-SR-002</t>
         </is>
       </c>
+      <c r="AH40" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-002 (robot/tests/requests/CFSUITE-SR-002_deflection_on_category.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="120" customHeight="1">
       <c r="A41" s="40" t="inlineStr">
@@ -2735,11 +2730,6 @@
           <t>CFSUITE-SR-006</t>
         </is>
       </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-010_calculate_request_due_date.robot</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="40" t="inlineStr">
@@ -2778,11 +2768,6 @@
           <t>CFSUITE-SR-007</t>
         </is>
       </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-011_create_child_case.robot</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="41" t="inlineStr">
@@ -2821,11 +2806,6 @@
           <t>CFSUITE-SR-008</t>
         </is>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-012_recategorise_case.robot</t>
-        </is>
-      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="40" t="inlineStr">
@@ -2864,9 +2844,9 @@
           <t>CFSUITE-SR-009</t>
         </is>
       </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-013_flag_request_as_emergency.robot</t>
+      <c r="AH47" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-009 (robot/tests/requests/CFSUITE-SR-009_auto_assign_by_business_rules.robot)</t>
         </is>
       </c>
     </row>
@@ -3581,11 +3561,6 @@
           <t>CFSUITE-SR-030</t>
         </is>
       </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-034_assign_case.robot</t>
-        </is>
-      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="40" t="inlineStr">
@@ -3616,11 +3591,6 @@
           <t>CFSUITE-SR-031</t>
         </is>
       </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-035_link_interested_parties.robot</t>
-        </is>
-      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="41" t="inlineStr">
@@ -3651,11 +3621,6 @@
           <t>CFSUITE-SR-032</t>
         </is>
       </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-036_provide_reason_for_due_date_change.robot</t>
-        </is>
-      </c>
     </row>
     <row r="71" ht="96" customHeight="1">
       <c r="A71" s="40" t="inlineStr">
@@ -4000,11 +3965,6 @@
           <t>CFSUITE-SR-041</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-045_provide_comment_when_closing.robot</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="41" t="inlineStr">
@@ -4037,11 +3997,6 @@
       <c r="AG80" t="inlineStr">
         <is>
           <t>CFSUITE-SR-042</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-046_create_tasks_on_case.robot</t>
         </is>
       </c>
     </row>
@@ -4693,6 +4648,11 @@
           <t>CFSUITE-SR-062</t>
         </is>
       </c>
+      <c r="AH100" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-062 (robot/tests/requests/CFSUITE-SR-062_configure_restricted_categories.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="40" t="inlineStr">
@@ -4729,11 +4689,6 @@
       <c r="AG101" t="inlineStr">
         <is>
           <t>CFSUITE-SR-063</t>
-        </is>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-067_enforce_comment_closing_complaint.robot</t>
         </is>
       </c>
     </row>
@@ -5177,11 +5132,6 @@
           <t>CFSUITE-SR-077</t>
         </is>
       </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-081_community_follow_case.robot</t>
-        </is>
-      </c>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="41" t="inlineStr">
@@ -5365,11 +5315,6 @@
           <t>CFSUITE-SR-082</t>
         </is>
       </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-086_customer_portal_login.robot</t>
-        </is>
-      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="40" t="inlineStr">
@@ -5470,11 +5415,6 @@
       <c r="AG123" t="inlineStr">
         <is>
           <t>CFSUITE-SR-085</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>robot/tests/requests/CFSUITE-SR-089_clone_case.robot</t>
         </is>
       </c>
     </row>
@@ -9182,29 +9122,32 @@
     <mergeCell ref="H1:T1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH35" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH37" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH44" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH45" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH46" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH47" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH48" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH49" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH68" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH69" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH70" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH72" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH73" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH74" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH39" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH40" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH41" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH47" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH48" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH49" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH50" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH51" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH52" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH53" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH72" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH73" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH74" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH76" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH77" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH79" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH80" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH81" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH78" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH81" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH83" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH84" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH101" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH115" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH120" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH123" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH85" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH88" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH100" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH105" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH119" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH124" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH127" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documentation/Automated Testing CFSuite.xlsx
+++ b/documentation/Automated Testing CFSuite.xlsx
@@ -4721,6 +4721,11 @@
           <t>CFSUITE-SR-064</t>
         </is>
       </c>
+      <c r="AH102" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-064 (robot/tests/requests/CFSUITE-SR-064_create_feedback_and_complaint_requests.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="40" t="inlineStr">
@@ -4753,6 +4758,11 @@
       <c r="AG103" t="inlineStr">
         <is>
           <t>CFSUITE-SR-065</t>
+        </is>
+      </c>
+      <c r="AH103" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-065 (robot/tests/requests/CFSUITE-SR-065_create_complaint_as_child_of_request.robot)</t>
         </is>
       </c>
     </row>
@@ -4848,6 +4858,11 @@
       <c r="AG106" t="inlineStr">
         <is>
           <t>CFSUITE-SR-068</t>
+        </is>
+      </c>
+      <c r="AH106" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-068 (robot/tests/requests/CFSUITE-SR-068_restricted_access_to_complaints.robot)</t>
         </is>
       </c>
     </row>
@@ -9144,10 +9159,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH85" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH88" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH100" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH105" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH119" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH124" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH127" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH102" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH103" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH105" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH106" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH119" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH124" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH127" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documentation/Automated Testing CFSuite.xlsx
+++ b/documentation/Automated Testing CFSuite.xlsx
@@ -5181,6 +5181,11 @@
           <t>CFSUITE-SR-078</t>
         </is>
       </c>
+      <c r="AH116" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-078 (robot/tests/requests/CFSUITE-SR-078_log_request_through_qanda_workflow.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="48" customHeight="1">
       <c r="A117" s="40" t="inlineStr">
@@ -5215,6 +5220,11 @@
           <t>CFSUITE-SR-079</t>
         </is>
       </c>
+      <c r="AH117" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-079 (robot/tests/requests/CFSUITE-SR-079_restrict_user_to_submit.robot)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="48" customHeight="1">
       <c r="A118" s="41" t="inlineStr">
@@ -5503,6 +5513,11 @@
       <c r="AG125" t="inlineStr">
         <is>
           <t>CFSUITE-SR-087</t>
+        </is>
+      </c>
+      <c r="AH125" s="47" t="inlineStr">
+        <is>
+          <t>CFSUITE-SR-087 (robot/tests/requests/CFSUITE-SR-087_raise_request_anonymously.robot)</t>
         </is>
       </c>
     </row>
@@ -9163,9 +9178,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH103" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH105" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH106" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH119" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH124" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH127" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH116" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH117" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH119" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH124" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH125" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH127" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
